--- a/Code/Inventor( ) Object Class Map.xlsx
+++ b/Code/Inventor( ) Object Class Map.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b0778c8abf470420/_Hobby/Robotics/_Inventor 2040 SMARS/Code/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b0778c8abf470420/_Hobby/Robotics/_Inventor 2040 SMARS/Code/Github Mirror/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2027" documentId="8_{AB2F4A40-CEDE-4481-A7CA-81FB681293B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C087B4DB-3871-4E28-92E5-76BB30BF74B9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{39FBCD36-3AA9-449E-B51D-EC944843B374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{8EFCF243-6549-4933-AAE3-AD4016C4DA94}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="1" activeTab="4" xr2:uid="{8EFCF243-6549-4933-AAE3-AD4016C4DA94}"/>
   </bookViews>
   <sheets>
     <sheet name=" Inventor 2040 W Function List" sheetId="1" r:id="rId1"/>
     <sheet name="HSV Color Reference Table" sheetId="3" r:id="rId2"/>
     <sheet name="Audio Tone Frequencies" sheetId="2" r:id="rId3"/>
     <sheet name="Audio Tones on Music Staves" sheetId="6" r:id="rId4"/>
+    <sheet name="Arcing Turn Calculations" sheetId="8" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">' Inventor 2040 W Function List'!$B$7:$G$7</definedName>
@@ -484,7 +485,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="523">
   <si>
     <t xml:space="preserve">  &lt;function __init__ at 0x20010350&gt;</t>
   </si>
@@ -2650,6 +2651,18 @@
   <si>
     <t xml:space="preserve">For tone/freq list: </t>
   </si>
+  <si>
+    <t>https://codingace.net/general/arduino_calculating_turn_degrees.html</t>
+  </si>
+  <si>
+    <t>codingace.net</t>
+  </si>
+  <si>
+    <t>Society of Robots</t>
+  </si>
+  <si>
+    <t>https://www.societyofrobots.com/programming_differentialdrive.shtml</t>
+  </si>
 </sst>
 </file>
 
@@ -2657,7 +2670,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="0\ &quot;Hz&quot;"/>
+    <numFmt numFmtId="165" formatCode="0\ &quot;Hz&quot;"/>
   </numFmts>
   <fonts count="30" x14ac:knownFonts="1">
     <font>
@@ -3160,7 +3173,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3381,19 +3394,6 @@
     <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
     </xf>
@@ -3456,39 +3456,40 @@
     <xf numFmtId="0" fontId="22" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="25" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="25" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="22" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="29" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="29" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3496,36 +3497,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="9">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment vertical="center"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -3668,13 +3639,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -3704,6 +3668,43 @@
       </font>
       <alignment vertical="center"/>
     </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment vertical="center"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3717,18 +3718,107 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>215900</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>502037</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>51155</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90AF5DA2-220A-B678-0DB9-FF3D3C63E60E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="215900" y="190500"/>
+          <a:ext cx="7525137" cy="6902805"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>463930</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>32111</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDA75704-093F-DC2C-525F-09B4CDD1C360}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="304800" y="7112000"/>
+          <a:ext cx="7398130" cy="7017111"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0CB92903-E67B-4A89-98BD-D767A6422AAC}" name="HSV_Color_Table" displayName="HSV_Color_Table" ref="B5:E14" totalsRowShown="0" headerRowDxfId="0" dataDxfId="8" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0CB92903-E67B-4A89-98BD-D767A6422AAC}" name="HSV_Color_Table" displayName="HSV_Color_Table" ref="B5:E14" totalsRowShown="0" headerRowDxfId="8" dataDxfId="6" headerRowBorderDxfId="7" tableBorderDxfId="5" totalsRowBorderDxfId="4">
   <autoFilter ref="B5:E14" xr:uid="{0CB92903-E67B-4A89-98BD-D767A6422AAC}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{AD15878B-D5C3-4F51-B2B0-4968D69D2AB4}" name="Color" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{443A376F-097B-4418-834A-12FF592203B4}" name="Hue (H)" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{917EA932-E5A8-45F8-A57B-AA25E4DE4942}" name="Saturation (S)" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{83F0E507-3582-41A8-8537-C1FBBD955917}" name="Value / Brightness (V)" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{AD15878B-D5C3-4F51-B2B0-4968D69D2AB4}" name="Color" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{443A376F-097B-4418-834A-12FF592203B4}" name="Hue (H)" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{917EA932-E5A8-45F8-A57B-AA25E4DE4942}" name="Saturation (S)" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{83F0E507-3582-41A8-8537-C1FBBD955917}" name="Value / Brightness (V)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4052,19 +4142,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9205D309-5084-44FF-91CB-A6FCDF0E6909}">
   <dimension ref="B1:H177"/>
-  <sheetFormatPr defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.9296875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.73046875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="27.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="28.53125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="24.46484375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="105.33203125" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.06640625" style="1"/>
+    <col min="1" max="1" width="2.36328125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.90625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.7265625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="27.36328125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="28.54296875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="24.453125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="105.36328125" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.08984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B1" s="6" t="s">
         <v>109</v>
       </c>
@@ -4074,7 +4164,7 @@
       <c r="E1" s="43"/>
       <c r="F1" s="43"/>
     </row>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B2" s="24" t="s">
         <v>160</v>
       </c>
@@ -4084,7 +4174,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B3" s="6" t="s">
         <v>161</v>
       </c>
@@ -4095,7 +4185,7 @@
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B4" s="6" t="s">
         <v>56</v>
       </c>
@@ -4105,7 +4195,7 @@
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.4">
       <c r="C5" s="1"/>
       <c r="D5" s="4" t="s">
         <v>38</v>
@@ -4113,11 +4203,11 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.4">
       <c r="C6" s="1"/>
       <c r="F6" s="7"/>
     </row>
-    <row r="7" spans="2:7" s="9" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:7" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B7" s="8" t="s">
         <v>45</v>
       </c>
@@ -4137,7 +4227,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B8" s="9" t="s">
         <v>36</v>
       </c>
@@ -4145,7 +4235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B9" s="9" t="s">
         <v>24</v>
       </c>
@@ -4153,7 +4243,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B10" s="9" t="s">
         <v>31</v>
       </c>
@@ -4161,7 +4251,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B11" s="9" t="s">
         <v>10</v>
       </c>
@@ -4169,7 +4259,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B12" s="9" t="s">
         <v>7</v>
       </c>
@@ -4177,7 +4267,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B13" s="53" t="s">
         <v>206</v>
       </c>
@@ -4189,7 +4279,7 @@
       <c r="F13" s="56"/>
       <c r="G13" s="54"/>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B14" s="21"/>
       <c r="C14" s="37"/>
       <c r="D14" s="21" t="s">
@@ -4201,7 +4291,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B15" s="76"/>
       <c r="C15" s="77"/>
       <c r="D15" s="21" t="s">
@@ -4217,7 +4307,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B16" s="76"/>
       <c r="C16" s="77"/>
       <c r="D16" s="21" t="s">
@@ -4229,7 +4319,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B17" s="21"/>
       <c r="C17" s="37"/>
       <c r="D17" s="21" t="s">
@@ -4241,7 +4331,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B18" s="21"/>
       <c r="C18" s="37"/>
       <c r="D18" s="21" t="s">
@@ -4253,7 +4343,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B19" s="21"/>
       <c r="C19" s="37"/>
       <c r="D19" s="21" t="s">
@@ -4267,7 +4357,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B20" s="21"/>
       <c r="C20" s="37"/>
       <c r="D20" s="21" t="s">
@@ -4279,7 +4369,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B21" s="76" t="s">
         <v>364</v>
       </c>
@@ -4291,7 +4381,7 @@
       <c r="F21" s="23"/>
       <c r="G21" s="22"/>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B22" s="76" t="s">
         <v>364</v>
       </c>
@@ -4303,11 +4393,11 @@
       <c r="F22" s="82" t="s">
         <v>518</v>
       </c>
-      <c r="G22" s="125" t="s">
+      <c r="G22" s="115" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B23" s="21"/>
       <c r="C23" s="37"/>
       <c r="D23" s="21"/>
@@ -4315,11 +4405,11 @@
       <c r="F23" s="82" t="s">
         <v>517</v>
       </c>
-      <c r="G23" s="125" t="s">
+      <c r="G23" s="115" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B24" s="9" t="s">
         <v>33</v>
       </c>
@@ -4327,7 +4417,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B25" s="9" t="s">
         <v>16</v>
       </c>
@@ -4335,7 +4425,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B26" s="65" t="s">
         <v>333</v>
       </c>
@@ -4345,7 +4435,7 @@
       <c r="F26" s="68"/>
       <c r="G26" s="69"/>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B27" s="29"/>
       <c r="C27" s="49"/>
       <c r="D27" s="31" t="s">
@@ -4357,7 +4447,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B28" s="29"/>
       <c r="C28" s="49"/>
       <c r="D28" s="31"/>
@@ -4367,7 +4457,7 @@
       <c r="F28" s="32"/>
       <c r="G28" s="31"/>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B29" s="29"/>
       <c r="C29" s="49"/>
       <c r="D29" s="31"/>
@@ -4375,7 +4465,7 @@
       <c r="F29" s="32"/>
       <c r="G29" s="31"/>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B30" s="29"/>
       <c r="C30" s="49"/>
       <c r="D30" s="31"/>
@@ -4385,7 +4475,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B31" s="29"/>
       <c r="C31" s="49"/>
       <c r="D31" s="31"/>
@@ -4395,7 +4485,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B32" s="29"/>
       <c r="C32" s="49"/>
       <c r="D32" s="31"/>
@@ -4405,7 +4495,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B33" s="29"/>
       <c r="C33" s="49"/>
       <c r="D33" s="31"/>
@@ -4415,7 +4505,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B34" s="29"/>
       <c r="C34" s="49"/>
       <c r="D34" s="31"/>
@@ -4423,7 +4513,7 @@
       <c r="F34" s="32"/>
       <c r="G34" s="31"/>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B35" s="9" t="s">
         <v>27</v>
       </c>
@@ -4431,7 +4521,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B36" s="53" t="s">
         <v>342</v>
       </c>
@@ -4443,7 +4533,7 @@
       <c r="F36" s="56"/>
       <c r="G36" s="54"/>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B37" s="21"/>
       <c r="C37" s="37"/>
       <c r="D37" s="22" t="s">
@@ -4459,7 +4549,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B38" s="21"/>
       <c r="C38" s="37"/>
       <c r="D38" s="22"/>
@@ -4469,7 +4559,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B39" s="76" t="s">
         <v>364</v>
       </c>
@@ -4481,7 +4571,7 @@
       <c r="F39" s="23"/>
       <c r="G39" s="73"/>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B40" s="21"/>
       <c r="C40" s="37"/>
       <c r="D40" s="22" t="s">
@@ -4497,7 +4587,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B41" s="21"/>
       <c r="C41" s="37"/>
       <c r="D41" s="22"/>
@@ -4507,7 +4597,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B42" s="21"/>
       <c r="C42" s="37"/>
       <c r="D42" s="22"/>
@@ -4517,7 +4607,7 @@
       <c r="F42" s="23"/>
       <c r="G42" s="73"/>
     </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B43" s="21"/>
       <c r="C43" s="37"/>
       <c r="D43" s="22" t="s">
@@ -4531,7 +4621,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B44" s="21"/>
       <c r="C44" s="37"/>
       <c r="D44" s="83"/>
@@ -4541,7 +4631,7 @@
       <c r="F44" s="23"/>
       <c r="G44" s="22"/>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B45" s="21"/>
       <c r="C45" s="74"/>
       <c r="D45" s="83" t="s">
@@ -4555,7 +4645,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B46" s="21"/>
       <c r="C46" s="37"/>
       <c r="D46" s="83"/>
@@ -4567,7 +4657,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B47" s="21"/>
       <c r="C47" s="37"/>
       <c r="D47" s="22"/>
@@ -4579,7 +4669,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B48" s="21"/>
       <c r="C48" s="37"/>
       <c r="D48" s="22"/>
@@ -4591,7 +4681,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B49" s="21"/>
       <c r="C49" s="37"/>
       <c r="D49" s="22"/>
@@ -4603,7 +4693,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B50" s="21"/>
       <c r="C50" s="37"/>
       <c r="D50" s="22"/>
@@ -4613,7 +4703,7 @@
       <c r="F50" s="23"/>
       <c r="G50" s="22"/>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B51" s="21"/>
       <c r="C51" s="37"/>
       <c r="D51" s="22"/>
@@ -4625,17 +4715,17 @@
         <v>404</v>
       </c>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B52" s="21"/>
       <c r="C52" s="37"/>
       <c r="D52" s="82"/>
       <c r="E52" s="84"/>
       <c r="F52" s="72"/>
-      <c r="G52" s="126" t="s">
+      <c r="G52" s="116" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B53" s="21"/>
       <c r="C53" s="37"/>
       <c r="D53" s="22"/>
@@ -4643,7 +4733,7 @@
       <c r="F53" s="23"/>
       <c r="G53" s="22"/>
     </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B54" s="9" t="s">
         <v>8</v>
       </c>
@@ -4651,7 +4741,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B55" s="57" t="s">
         <v>28</v>
       </c>
@@ -4663,7 +4753,7 @@
       <c r="F55" s="59"/>
       <c r="G55" s="59"/>
     </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B56" s="33"/>
       <c r="C56" s="34"/>
       <c r="D56" s="34" t="s">
@@ -4679,7 +4769,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B57" s="33"/>
       <c r="C57" s="34"/>
       <c r="D57" s="34"/>
@@ -4687,7 +4777,7 @@
       <c r="F57" s="35"/>
       <c r="G57" s="34"/>
     </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B58" s="33"/>
       <c r="C58" s="34"/>
       <c r="D58" s="34"/>
@@ -4697,7 +4787,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B59" s="33"/>
       <c r="C59" s="34"/>
       <c r="D59" s="34"/>
@@ -4707,7 +4797,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B60" s="33"/>
       <c r="C60" s="34"/>
       <c r="D60" s="34"/>
@@ -4717,7 +4807,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="61" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B61" s="33"/>
       <c r="C61" s="34"/>
       <c r="D61" s="34"/>
@@ -4727,7 +4817,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B62" s="33"/>
       <c r="C62" s="34"/>
       <c r="D62" s="34"/>
@@ -4737,7 +4827,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B63" s="33"/>
       <c r="C63" s="34"/>
       <c r="D63" s="34"/>
@@ -4745,7 +4835,7 @@
       <c r="F63" s="35"/>
       <c r="G63" s="34"/>
     </row>
-    <row r="64" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B64" s="33"/>
       <c r="C64" s="34"/>
       <c r="D64" s="34"/>
@@ -4755,7 +4845,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B65" s="33"/>
       <c r="C65" s="34"/>
       <c r="D65" s="34"/>
@@ -4765,7 +4855,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B66" s="33"/>
       <c r="C66" s="34"/>
       <c r="D66" s="34"/>
@@ -4775,7 +4865,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B67" s="33"/>
       <c r="C67" s="34"/>
       <c r="D67" s="34"/>
@@ -4785,7 +4875,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B68" s="33"/>
       <c r="C68" s="34"/>
       <c r="D68" s="34"/>
@@ -4793,7 +4883,7 @@
       <c r="F68" s="35"/>
       <c r="G68" s="62"/>
     </row>
-    <row r="69" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B69" s="33"/>
       <c r="C69" s="34"/>
       <c r="D69" s="34"/>
@@ -4803,7 +4893,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="70" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B70" s="33"/>
       <c r="C70" s="34"/>
       <c r="D70" s="34"/>
@@ -4813,7 +4903,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="71" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B71" s="33"/>
       <c r="C71" s="34"/>
       <c r="D71" s="34"/>
@@ -4823,7 +4913,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="72" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B72" s="33"/>
       <c r="C72" s="34"/>
       <c r="D72" s="34"/>
@@ -4833,7 +4923,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="73" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B73" s="33"/>
       <c r="C73" s="34"/>
       <c r="D73" s="34"/>
@@ -4843,7 +4933,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="74" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B74" s="33"/>
       <c r="C74" s="34"/>
       <c r="D74" s="34"/>
@@ -4853,7 +4943,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="75" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B75" s="33"/>
       <c r="C75" s="34"/>
       <c r="D75" s="34"/>
@@ -4863,7 +4953,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="76" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B76" s="33"/>
       <c r="C76" s="34"/>
       <c r="D76" s="34"/>
@@ -4871,7 +4961,7 @@
       <c r="F76" s="35"/>
       <c r="G76" s="34"/>
     </row>
-    <row r="77" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B77" s="9" t="s">
         <v>9</v>
       </c>
@@ -4879,7 +4969,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B78" s="9" t="s">
         <v>11</v>
       </c>
@@ -4887,7 +4977,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B79" s="38" t="s">
         <v>25</v>
       </c>
@@ -4907,7 +4997,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="80" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B80" s="11"/>
       <c r="C80" s="12"/>
       <c r="D80" s="13" t="s">
@@ -4921,7 +5011,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B81" s="38" t="s">
         <v>32</v>
       </c>
@@ -4941,7 +5031,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="82" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B82" s="11"/>
       <c r="C82" s="12"/>
       <c r="D82" s="13" t="s">
@@ -4955,7 +5045,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="83" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B83" s="38" t="s">
         <v>353</v>
       </c>
@@ -4965,7 +5055,7 @@
       <c r="F83" s="41"/>
       <c r="G83" s="42"/>
     </row>
-    <row r="84" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B84" s="11"/>
       <c r="C84" s="47" t="s">
         <v>178</v>
@@ -4981,7 +5071,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="85" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B85" s="11"/>
       <c r="C85" s="12"/>
       <c r="D85" s="13" t="s">
@@ -4995,7 +5085,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="86" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B86" s="75"/>
       <c r="C86" s="13"/>
       <c r="D86" s="13" t="s">
@@ -5007,7 +5097,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="87" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B87" s="11"/>
       <c r="C87" s="12"/>
       <c r="D87" s="13" t="s">
@@ -5019,7 +5109,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="88" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B88" s="11"/>
       <c r="C88" s="12"/>
       <c r="D88" s="13" t="s">
@@ -5031,7 +5121,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="89" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B89" s="11"/>
       <c r="C89" s="12"/>
       <c r="D89" s="13" t="s">
@@ -5045,7 +5135,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="90" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B90" s="11"/>
       <c r="C90" s="47" t="s">
         <v>178</v>
@@ -5061,7 +5151,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="91" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B91" s="11"/>
       <c r="C91" s="12"/>
       <c r="D91" s="13" t="s">
@@ -5073,7 +5163,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="92" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B92" s="11"/>
       <c r="C92" s="12"/>
       <c r="D92" s="13" t="s">
@@ -5085,7 +5175,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="93" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B93" s="11"/>
       <c r="C93" s="12"/>
       <c r="D93" s="13" t="s">
@@ -5097,7 +5187,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="94" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B94" s="11"/>
       <c r="C94" s="12"/>
       <c r="D94" s="13" t="s">
@@ -5109,7 +5199,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="95" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B95" s="11"/>
       <c r="C95" s="12"/>
       <c r="D95" s="13" t="s">
@@ -5125,7 +5215,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="96" spans="2:7" ht="15" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B96" s="11"/>
       <c r="C96" s="12"/>
       <c r="D96" s="13" t="s">
@@ -5139,7 +5229,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="97" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="97" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B97" s="11"/>
       <c r="C97" s="47" t="s">
         <v>178</v>
@@ -5153,7 +5243,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="98" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="98" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B98" s="11"/>
       <c r="C98" s="12"/>
       <c r="D98" s="13" t="s">
@@ -5167,7 +5257,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="99" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="99" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B99" s="13"/>
       <c r="C99" s="36"/>
       <c r="D99" s="13"/>
@@ -5181,7 +5271,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="100" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="100" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B100" s="13"/>
       <c r="C100" s="36"/>
       <c r="D100" s="13"/>
@@ -5195,7 +5285,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="101" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="101" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B101" s="13"/>
       <c r="C101" s="36"/>
       <c r="D101" s="13"/>
@@ -5209,7 +5299,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="102" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="102" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B102" s="13"/>
       <c r="C102" s="36"/>
       <c r="D102" s="13"/>
@@ -5223,7 +5313,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="103" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="103" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B103" s="13"/>
       <c r="C103" s="36"/>
       <c r="D103" s="13"/>
@@ -5237,7 +5327,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="104" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="104" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B104" s="13"/>
       <c r="C104" s="36"/>
       <c r="D104" s="13"/>
@@ -5251,7 +5341,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="105" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="105" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B105" s="13"/>
       <c r="C105" s="36"/>
       <c r="D105" s="13"/>
@@ -5265,7 +5355,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="106" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B106" s="13"/>
       <c r="C106" s="36"/>
       <c r="D106" s="13"/>
@@ -5279,7 +5369,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="107" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="107" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B107" s="13"/>
       <c r="C107" s="36"/>
       <c r="D107" s="13"/>
@@ -5293,7 +5383,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="108" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="108" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B108" s="13"/>
       <c r="C108" s="36"/>
       <c r="D108" s="13"/>
@@ -5305,7 +5395,7 @@
       </c>
       <c r="G108" s="13"/>
     </row>
-    <row r="109" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="109" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B109" s="78" t="s">
         <v>364</v>
       </c>
@@ -5321,7 +5411,7 @@
       </c>
       <c r="G109" s="13"/>
     </row>
-    <row r="110" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="110" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B110" s="13"/>
       <c r="C110" s="36"/>
       <c r="D110" s="13"/>
@@ -5333,7 +5423,7 @@
       </c>
       <c r="G110" s="13"/>
     </row>
-    <row r="111" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="111" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B111" s="13"/>
       <c r="C111" s="36"/>
       <c r="D111" s="13"/>
@@ -5345,7 +5435,7 @@
       </c>
       <c r="G111" s="13"/>
     </row>
-    <row r="112" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="112" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B112" s="11"/>
       <c r="C112" s="12"/>
       <c r="D112" s="13"/>
@@ -5353,7 +5443,7 @@
       <c r="F112" s="14"/>
       <c r="G112" s="13"/>
     </row>
-    <row r="113" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="113" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B113" s="9" t="s">
         <v>26</v>
       </c>
@@ -5361,7 +5451,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="114" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="114" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B114" s="9" t="s">
         <v>15</v>
       </c>
@@ -5371,7 +5461,7 @@
       <c r="E114" s="1"/>
       <c r="F114" s="1"/>
     </row>
-    <row r="115" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="115" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B115" s="25" t="s">
         <v>35</v>
       </c>
@@ -5391,7 +5481,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="116" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="116" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B116" s="15"/>
       <c r="C116" s="16"/>
       <c r="D116" s="17" t="s">
@@ -5405,7 +5495,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="117" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="117" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B117" s="25" t="s">
         <v>34</v>
       </c>
@@ -5425,7 +5515,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="118" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="118" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B118" s="15"/>
       <c r="C118" s="16"/>
       <c r="D118" s="17" t="s">
@@ -5439,7 +5529,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="119" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="119" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B119" s="25" t="s">
         <v>355</v>
       </c>
@@ -5449,7 +5539,7 @@
       <c r="F119" s="28"/>
       <c r="G119" s="27"/>
     </row>
-    <row r="120" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="120" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B120" s="15"/>
       <c r="C120" s="16"/>
       <c r="D120" s="17" t="s">
@@ -5461,7 +5551,7 @@
       <c r="F120" s="18"/>
       <c r="G120" s="17"/>
     </row>
-    <row r="121" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="121" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B121" s="80" t="s">
         <v>364</v>
       </c>
@@ -5477,7 +5567,7 @@
       <c r="F121" s="18"/>
       <c r="G121" s="17"/>
     </row>
-    <row r="122" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="122" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B122" s="15"/>
       <c r="C122" s="16"/>
       <c r="D122" s="17" t="s">
@@ -5491,7 +5581,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="123" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="123" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B123" s="15"/>
       <c r="C123" s="16"/>
       <c r="D123" s="17" t="s">
@@ -5503,7 +5593,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="124" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="124" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B124" s="15"/>
       <c r="C124" s="16"/>
       <c r="D124" s="17" t="s">
@@ -5517,7 +5607,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="125" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="125" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B125" s="15"/>
       <c r="C125" s="16"/>
       <c r="D125" s="17" t="s">
@@ -5529,7 +5619,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="126" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="126" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B126" s="15"/>
       <c r="C126" s="16"/>
       <c r="D126" s="17" t="s">
@@ -5543,7 +5633,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="127" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="127" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B127" s="15"/>
       <c r="C127" s="16"/>
       <c r="D127" s="17" t="s">
@@ -5555,7 +5645,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="128" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="128" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B128" s="15"/>
       <c r="C128" s="16"/>
       <c r="D128" s="17" t="s">
@@ -5571,7 +5661,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="129" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="129" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B129" s="15"/>
       <c r="C129" s="16"/>
       <c r="D129" s="17" t="s">
@@ -5583,7 +5673,7 @@
       <c r="F129" s="18"/>
       <c r="G129" s="17"/>
     </row>
-    <row r="130" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="130" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B130" s="15"/>
       <c r="C130" s="16"/>
       <c r="D130" s="17" t="s">
@@ -5595,7 +5685,7 @@
       <c r="F130" s="18"/>
       <c r="G130" s="17"/>
     </row>
-    <row r="131" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="131" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B131" s="15"/>
       <c r="C131" s="16"/>
       <c r="D131" s="17" t="s">
@@ -5607,7 +5697,7 @@
       <c r="F131" s="18"/>
       <c r="G131" s="17"/>
     </row>
-    <row r="132" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="132" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B132" s="17"/>
       <c r="C132" s="20"/>
       <c r="D132" s="17" t="s">
@@ -5619,7 +5709,7 @@
       <c r="F132" s="18"/>
       <c r="G132" s="17"/>
     </row>
-    <row r="133" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="133" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B133" s="17"/>
       <c r="C133" s="20"/>
       <c r="D133" s="17" t="s">
@@ -5631,7 +5721,7 @@
       <c r="F133" s="18"/>
       <c r="G133" s="17"/>
     </row>
-    <row r="134" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="134" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B134" s="17"/>
       <c r="C134" s="20"/>
       <c r="D134" s="17" t="s">
@@ -5643,7 +5733,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="135" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="135" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B135" s="17"/>
       <c r="C135" s="20"/>
       <c r="D135" s="17" t="s">
@@ -5655,7 +5745,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="136" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="136" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B136" s="17"/>
       <c r="C136" s="20"/>
       <c r="D136" s="17" t="s">
@@ -5667,7 +5757,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="137" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="137" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B137" s="15"/>
       <c r="C137" s="16"/>
       <c r="D137" s="17" t="s">
@@ -5679,7 +5769,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="138" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="138" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B138" s="15"/>
       <c r="C138" s="16"/>
       <c r="D138" s="17" t="s">
@@ -5695,7 +5785,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="139" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="139" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B139" s="15"/>
       <c r="C139" s="16"/>
       <c r="D139" s="17" t="s">
@@ -5709,7 +5799,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="140" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="140" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B140" s="15"/>
       <c r="C140" s="16"/>
       <c r="D140" s="17" t="s">
@@ -5723,7 +5813,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="141" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="141" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B141" s="17"/>
       <c r="C141" s="45" t="s">
         <v>178</v>
@@ -5739,7 +5829,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="142" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="142" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B142" s="17"/>
       <c r="C142" s="45" t="s">
         <v>178</v>
@@ -5755,7 +5845,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="143" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="143" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B143" s="15"/>
       <c r="C143" s="16"/>
       <c r="D143" s="17" t="s">
@@ -5769,7 +5859,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="144" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="144" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B144" s="15"/>
       <c r="C144" s="16"/>
       <c r="D144" s="17" t="s">
@@ -5786,7 +5876,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="145" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="145" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B145" s="15"/>
       <c r="C145" s="16"/>
       <c r="D145" s="17" t="s">
@@ -5798,7 +5888,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="146" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="146" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B146" s="15"/>
       <c r="C146" s="16"/>
       <c r="D146" s="17" t="s">
@@ -5814,7 +5904,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="147" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="147" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B147" s="15"/>
       <c r="C147" s="16"/>
       <c r="D147" s="17"/>
@@ -5822,175 +5912,151 @@
       <c r="F147" s="18"/>
       <c r="G147" s="17"/>
     </row>
-    <row r="148" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B148" s="86" t="s">
+    <row r="148" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B148" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C148" s="87">
+      <c r="C148" s="48">
         <v>10</v>
       </c>
-      <c r="D148" s="88"/>
-      <c r="E148" s="89"/>
-      <c r="F148" s="89"/>
-      <c r="G148" s="88"/>
-    </row>
-    <row r="149" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B149" s="86" t="s">
+    </row>
+    <row r="149" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B149" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C149" s="87">
+      <c r="C149" s="48">
         <v>11</v>
       </c>
-      <c r="D149" s="88"/>
-      <c r="E149" s="89"/>
-      <c r="F149" s="89"/>
-      <c r="G149" s="88"/>
-    </row>
-    <row r="150" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B150" s="86" t="s">
+    </row>
+    <row r="150" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B150" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C150" s="87">
+      <c r="C150" s="48">
         <v>12</v>
       </c>
-      <c r="D150" s="88"/>
-      <c r="E150" s="89"/>
-      <c r="F150" s="89"/>
-      <c r="G150" s="88"/>
-    </row>
-    <row r="151" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B151" s="90" t="s">
+    </row>
+    <row r="151" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B151" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C151" s="87">
+      <c r="C151" s="48">
         <v>13</v>
       </c>
-      <c r="D151" s="88"/>
-      <c r="E151" s="89"/>
-      <c r="F151" s="89"/>
-      <c r="G151" s="88"/>
-    </row>
-    <row r="152" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B152" s="86" t="s">
+    </row>
+    <row r="152" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B152" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C152" s="87">
+      <c r="C152" s="48">
         <v>14</v>
       </c>
-      <c r="D152" s="88"/>
-      <c r="E152" s="89"/>
-      <c r="F152" s="89"/>
-      <c r="G152" s="88"/>
-    </row>
-    <row r="153" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B153" s="86" t="s">
+    </row>
+    <row r="153" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B153" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C153" s="87">
+      <c r="C153" s="48">
         <v>15</v>
       </c>
-      <c r="D153" s="88"/>
-      <c r="E153" s="89"/>
-      <c r="F153" s="89"/>
-      <c r="G153" s="88"/>
-    </row>
-    <row r="154" spans="2:7" x14ac:dyDescent="0.45">
+    </row>
+    <row r="154" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B154" s="29" t="s">
         <v>17</v>
       </c>
       <c r="C154" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D154" s="91" t="s">
+      <c r="D154" s="86" t="s">
         <v>381</v>
       </c>
       <c r="E154" s="32"/>
       <c r="F154" s="32"/>
       <c r="G154" s="31"/>
     </row>
-    <row r="155" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="155" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B155" s="29" t="s">
         <v>18</v>
       </c>
       <c r="C155" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D155" s="91" t="s">
+      <c r="D155" s="86" t="s">
         <v>381</v>
       </c>
       <c r="E155" s="32"/>
       <c r="F155" s="32"/>
       <c r="G155" s="31"/>
     </row>
-    <row r="156" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="156" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B156" s="29" t="s">
         <v>19</v>
       </c>
       <c r="C156" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D156" s="91" t="s">
+      <c r="D156" s="86" t="s">
         <v>381</v>
       </c>
       <c r="E156" s="32"/>
       <c r="F156" s="32"/>
       <c r="G156" s="31"/>
     </row>
-    <row r="157" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="157" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B157" s="29" t="s">
         <v>20</v>
       </c>
       <c r="C157" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D157" s="91" t="s">
+      <c r="D157" s="86" t="s">
         <v>381</v>
       </c>
       <c r="E157" s="32"/>
       <c r="F157" s="32"/>
       <c r="G157" s="31"/>
     </row>
-    <row r="158" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="158" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B158" s="29" t="s">
         <v>21</v>
       </c>
       <c r="C158" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D158" s="91" t="s">
+      <c r="D158" s="86" t="s">
         <v>381</v>
       </c>
       <c r="E158" s="32"/>
       <c r="F158" s="32"/>
       <c r="G158" s="31"/>
     </row>
-    <row r="159" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="159" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B159" s="29" t="s">
         <v>22</v>
       </c>
       <c r="C159" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D159" s="91" t="s">
+      <c r="D159" s="86" t="s">
         <v>381</v>
       </c>
       <c r="E159" s="32"/>
       <c r="F159" s="32"/>
       <c r="G159" s="31"/>
     </row>
-    <row r="173" spans="5:5" x14ac:dyDescent="0.45">
+    <row r="173" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E173" s="2"/>
     </row>
-    <row r="174" spans="5:5" x14ac:dyDescent="0.45">
+    <row r="174" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E174" s="2"/>
     </row>
-    <row r="175" spans="5:5" x14ac:dyDescent="0.45">
+    <row r="175" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E175" s="2"/>
     </row>
-    <row r="176" spans="5:5" x14ac:dyDescent="0.45">
+    <row r="176" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E176" s="2"/>
     </row>
-    <row r="177" spans="5:5" x14ac:dyDescent="0.45">
+    <row r="177" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E177" s="2"/>
     </row>
   </sheetData>
@@ -6013,166 +6079,166 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="B3:E17"/>
-  <sheetFormatPr defaultRowHeight="16.149999999999999" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.06640625" style="50"/>
-    <col min="2" max="2" width="16.1328125" style="50" customWidth="1"/>
+    <col min="1" max="1" width="9.08984375" style="50"/>
+    <col min="2" max="2" width="16.08984375" style="50" customWidth="1"/>
     <col min="3" max="3" width="29" style="50" customWidth="1"/>
-    <col min="4" max="4" width="23.73046875" style="50" customWidth="1"/>
-    <col min="5" max="5" width="30.46484375" style="50" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="50"/>
+    <col min="4" max="4" width="23.7265625" style="50" customWidth="1"/>
+    <col min="5" max="5" width="30.453125" style="50" customWidth="1"/>
+    <col min="6" max="16384" width="9.08984375" style="50"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C3" s="111"/>
-    </row>
-    <row r="5" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="92" t="s">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="C3" s="106"/>
+    </row>
+    <row r="5" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="87" t="s">
         <v>382</v>
       </c>
-      <c r="C5" s="93" t="s">
+      <c r="C5" s="88" t="s">
         <v>383</v>
       </c>
-      <c r="D5" s="93" t="s">
+      <c r="D5" s="88" t="s">
         <v>384</v>
       </c>
-      <c r="E5" s="94" t="s">
+      <c r="E5" s="89" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="95" t="s">
+    <row r="6" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="90" t="s">
         <v>386</v>
       </c>
-      <c r="C6" s="96" t="s">
+      <c r="C6" s="91" t="s">
         <v>387</v>
       </c>
-      <c r="D6" s="97">
+      <c r="D6" s="92">
         <v>1</v>
       </c>
-      <c r="E6" s="98">
+      <c r="E6" s="93">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="99" t="s">
+    <row r="7" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="94" t="s">
         <v>388</v>
       </c>
-      <c r="C7" s="96" t="s">
+      <c r="C7" s="91" t="s">
         <v>389</v>
       </c>
-      <c r="D7" s="97">
+      <c r="D7" s="92">
         <v>1</v>
       </c>
-      <c r="E7" s="98">
+      <c r="E7" s="93">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="100" t="s">
+    <row r="8" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B8" s="95" t="s">
         <v>390</v>
       </c>
-      <c r="C8" s="96" t="s">
+      <c r="C8" s="91" t="s">
         <v>391</v>
       </c>
-      <c r="D8" s="97">
+      <c r="D8" s="92">
         <v>1</v>
       </c>
-      <c r="E8" s="98">
+      <c r="E8" s="93">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="101" t="s">
+    <row r="9" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="96" t="s">
         <v>392</v>
       </c>
-      <c r="C9" s="96" t="s">
+      <c r="C9" s="91" t="s">
         <v>393</v>
       </c>
-      <c r="D9" s="97">
+      <c r="D9" s="92">
         <v>1</v>
       </c>
-      <c r="E9" s="98">
+      <c r="E9" s="93">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="102" t="s">
+    <row r="10" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B10" s="97" t="s">
         <v>394</v>
       </c>
-      <c r="C10" s="96" t="s">
+      <c r="C10" s="91" t="s">
         <v>395</v>
       </c>
-      <c r="D10" s="97">
+      <c r="D10" s="92">
         <v>1</v>
       </c>
-      <c r="E10" s="98">
+      <c r="E10" s="93">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="103" t="s">
+    <row r="11" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="98" t="s">
         <v>396</v>
       </c>
-      <c r="C11" s="96" t="s">
+      <c r="C11" s="91" t="s">
         <v>397</v>
       </c>
-      <c r="D11" s="97">
+      <c r="D11" s="92">
         <v>1</v>
       </c>
-      <c r="E11" s="98">
+      <c r="E11" s="93">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="104" t="s">
+    <row r="12" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="99" t="s">
         <v>398</v>
       </c>
-      <c r="C12" s="96" t="s">
+      <c r="C12" s="91" t="s">
         <v>399</v>
       </c>
-      <c r="D12" s="97">
+      <c r="D12" s="92">
         <v>1</v>
       </c>
-      <c r="E12" s="98">
+      <c r="E12" s="93">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="105" t="s">
+    <row r="13" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B13" s="100" t="s">
         <v>400</v>
       </c>
-      <c r="C13" s="96" t="s">
+      <c r="C13" s="91" t="s">
         <v>401</v>
       </c>
-      <c r="D13" s="97">
+      <c r="D13" s="92">
         <v>0</v>
       </c>
-      <c r="E13" s="98">
+      <c r="E13" s="93">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="106" t="s">
+    <row r="14" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B14" s="101" t="s">
         <v>402</v>
       </c>
-      <c r="C14" s="107" t="s">
+      <c r="C14" s="102" t="s">
         <v>401</v>
       </c>
-      <c r="D14" s="108">
+      <c r="D14" s="103">
         <v>0</v>
       </c>
-      <c r="E14" s="109">
+      <c r="E14" s="104">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.4">
       <c r="C16" s="50" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="C17" s="110"/>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C17" s="105"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6188,469 +6254,469 @@
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="B2:B93"/>
-  <sheetFormatPr defaultRowHeight="13.15" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.06640625" style="118"/>
-    <col min="2" max="2" width="19.1328125" style="118" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.06640625" style="118"/>
+    <col min="1" max="1" width="9.08984375" style="111"/>
+    <col min="2" max="2" width="19.08984375" style="111" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.08984375" style="111"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="B2" s="124" t="s">
+    <row r="2" spans="2:2" ht="15" x14ac:dyDescent="0.4">
+      <c r="B2" s="114" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="3" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B3" s="1" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="4" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B4" s="1" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="5" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B5" s="1" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="6" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B6" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="7" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B7" s="1" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="8" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B8" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="9" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B9" s="1" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="10" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B10" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="11" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B11" s="1" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="12" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B12" s="1" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="13" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B13" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="14" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B14" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="15" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B15" s="1" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="16" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B16" s="1" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="17" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B17" s="1" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="18" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B18" s="1" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="19" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B19" s="1" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="20" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B20" s="1" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="21" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B21" s="1" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="22" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B22" s="1" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="23" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B23" s="1" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="24" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B24" s="1" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="25" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B25" s="1" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="26" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B26" s="1" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="27" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B27" s="1" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="28" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B28" s="1" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="29" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B29" s="1" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="30" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B30" s="1" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="31" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B31" s="1" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="32" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B32" s="1" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="33" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B33" s="1" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="34" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B34" s="1" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="35" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B35" s="1" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="36" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B36" s="1" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="37" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B37" s="1" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="38" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B38" s="1" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="39" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B39" s="1" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="40" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B40" s="1" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="41" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B41" s="1" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="42" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B42" s="1" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="43" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B43" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="44" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B44" s="1" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="45" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B45" s="1" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="46" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B46" s="1" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="47" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B47" s="1" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="48" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B48" s="1" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="49" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B49" s="1" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="50" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B50" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="51" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B51" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="52" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B52" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="53" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B53" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="54" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B54" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="55" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B55" s="1" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="56" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B56" s="1" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="57" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B57" s="1" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="58" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B58" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="59" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B59" s="1" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="60" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B60" s="1" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="61" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B61" s="1" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="62" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B62" s="1" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="63" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B63" s="1" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="64" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B64" s="1" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="65" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B65" s="1" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="66" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B66" s="1" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="67" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B67" s="1" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="68" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B68" s="1" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="69" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B69" s="1" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="70" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B70" s="1" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="71" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B71" s="1" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="72" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B72" s="1" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="73" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B73" s="1" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="74" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B74" s="1" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="75" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B75" s="1" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="76" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B76" s="1" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="77" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B77" s="1" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="78" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B78" s="1" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="79" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B79" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="80" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B80" s="1" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="81" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B81" s="1" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="82" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B82" s="1" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="83" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B83" s="1" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="84" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B84" s="1" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="85" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B85" s="1" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="86" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B86" s="1" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="87" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B87" s="1" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="88" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B88" s="1" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="89" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B89" s="1" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="90" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B90" s="1" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="91" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B91" s="1" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="92" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B92" s="1" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="93" spans="2:2" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:2" ht="15" x14ac:dyDescent="0.4">
       <c r="B93" s="1" t="s">
         <v>296</v>
       </c>
@@ -6666,3541 +6732,3536 @@
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:N184"/>
-  <sheetFormatPr defaultRowHeight="13.15" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.86328125" style="118" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" style="118" customWidth="1"/>
-    <col min="3" max="14" width="8.53125" style="118" customWidth="1"/>
-    <col min="15" max="16384" width="9.06640625" style="118"/>
+    <col min="1" max="1" width="2.81640625" style="111" customWidth="1"/>
+    <col min="2" max="2" width="13.36328125" style="111" customWidth="1"/>
+    <col min="3" max="14" width="8.54296875" style="111" customWidth="1"/>
+    <col min="15" max="16384" width="9.08984375" style="111"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="123" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="121"/>
-      <c r="B1" s="122" t="s">
+    <row r="1" spans="1:14" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="113"/>
+      <c r="B1" s="120" t="s">
         <v>406</v>
       </c>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-    </row>
-    <row r="2" spans="1:14" ht="21.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="112"/>
-      <c r="B2" s="119" t="s">
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+    </row>
+    <row r="2" spans="1:14" ht="21.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="107"/>
+      <c r="B2" s="121" t="s">
         <v>407</v>
       </c>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="119"/>
-      <c r="F2" s="119"/>
-      <c r="G2" s="119"/>
-      <c r="H2" s="119"/>
-      <c r="I2" s="119"/>
-      <c r="J2" s="119"/>
-      <c r="K2" s="119"/>
-      <c r="L2" s="119"/>
-      <c r="M2" s="119"/>
-      <c r="N2" s="119"/>
-    </row>
-    <row r="3" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="112"/>
-      <c r="B3" s="113" t="s">
+      <c r="C2" s="121"/>
+      <c r="D2" s="121"/>
+      <c r="E2" s="121"/>
+      <c r="F2" s="121"/>
+      <c r="G2" s="121"/>
+      <c r="H2" s="121"/>
+      <c r="I2" s="121"/>
+      <c r="J2" s="121"/>
+      <c r="K2" s="121"/>
+      <c r="L2" s="121"/>
+      <c r="M2" s="121"/>
+      <c r="N2" s="121"/>
+    </row>
+    <row r="3" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="107"/>
+      <c r="B3" s="122" t="s">
         <v>408</v>
       </c>
-      <c r="C3" s="113"/>
-      <c r="D3" s="113"/>
-      <c r="E3" s="113"/>
-      <c r="F3" s="113"/>
-      <c r="G3" s="113"/>
-      <c r="H3" s="113"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="113"/>
-      <c r="K3" s="113"/>
-      <c r="L3" s="113"/>
-      <c r="M3" s="113"/>
-      <c r="N3" s="113"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A4" s="112"/>
-      <c r="B4" s="112"/>
-      <c r="C4" s="112"/>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="112"/>
-      <c r="L4" s="112"/>
-      <c r="M4" s="112"/>
-      <c r="N4" s="112"/>
-    </row>
-    <row r="5" spans="1:14" ht="16.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="112"/>
-      <c r="B5" s="114" t="s">
+      <c r="C3" s="122"/>
+      <c r="D3" s="122"/>
+      <c r="E3" s="122"/>
+      <c r="F3" s="122"/>
+      <c r="G3" s="122"/>
+      <c r="H3" s="122"/>
+      <c r="I3" s="122"/>
+      <c r="J3" s="122"/>
+      <c r="K3" s="122"/>
+      <c r="L3" s="122"/>
+      <c r="M3" s="122"/>
+      <c r="N3" s="122"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="107"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="107"/>
+      <c r="K4" s="107"/>
+      <c r="L4" s="107"/>
+      <c r="M4" s="107"/>
+      <c r="N4" s="107"/>
+    </row>
+    <row r="5" spans="1:14" ht="16.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="107"/>
+      <c r="B5" s="119" t="s">
         <v>409</v>
       </c>
-      <c r="C5" s="114"/>
-      <c r="D5" s="114"/>
-      <c r="E5" s="114"/>
-      <c r="F5" s="114"/>
-      <c r="G5" s="114"/>
-      <c r="H5" s="114"/>
-      <c r="I5" s="114"/>
-      <c r="J5" s="114"/>
-      <c r="K5" s="114"/>
-      <c r="L5" s="114"/>
-      <c r="M5" s="114"/>
-      <c r="N5" s="114"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A6" s="112"/>
-      <c r="B6" s="112"/>
-      <c r="C6" s="112"/>
-      <c r="D6" s="112"/>
-      <c r="E6" s="112"/>
-      <c r="F6" s="112"/>
-      <c r="G6" s="112"/>
-      <c r="H6" s="112"/>
-      <c r="I6" s="112"/>
-      <c r="J6" s="112"/>
-      <c r="K6" s="112"/>
-      <c r="L6" s="112"/>
-      <c r="M6" s="112"/>
-      <c r="N6" s="112"/>
-    </row>
-    <row r="7" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="112"/>
-      <c r="B7" s="115"/>
-      <c r="C7" s="115"/>
-      <c r="D7" s="115"/>
-      <c r="E7" s="115"/>
-      <c r="F7" s="115"/>
-      <c r="G7" s="115"/>
-      <c r="H7" s="115"/>
-      <c r="I7" s="115"/>
-      <c r="J7" s="115"/>
-      <c r="K7" s="115"/>
-      <c r="L7" s="115"/>
-      <c r="M7" s="115"/>
-      <c r="N7" s="115"/>
-    </row>
-    <row r="8" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="112"/>
-      <c r="B8" s="115"/>
-      <c r="C8" s="115"/>
-      <c r="D8" s="115"/>
-      <c r="E8" s="115"/>
-      <c r="F8" s="115"/>
-      <c r="G8" s="115"/>
-      <c r="H8" s="115"/>
-      <c r="I8" s="115"/>
-      <c r="J8" s="115"/>
-      <c r="K8" s="115"/>
-      <c r="L8" s="115"/>
-      <c r="M8" s="115"/>
-      <c r="N8" s="115"/>
-    </row>
-    <row r="9" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="112"/>
-      <c r="B9" s="115"/>
-      <c r="C9" s="120"/>
-      <c r="D9" s="120"/>
-      <c r="E9" s="120"/>
-      <c r="F9" s="120"/>
-      <c r="G9" s="120"/>
-      <c r="H9" s="120"/>
-      <c r="I9" s="120"/>
-      <c r="J9" s="120"/>
-      <c r="K9" s="120"/>
-      <c r="L9" s="120"/>
-      <c r="M9" s="120"/>
-      <c r="N9" s="120"/>
-    </row>
-    <row r="10" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="112"/>
-      <c r="B10" s="115"/>
-      <c r="C10" s="115"/>
-      <c r="D10" s="115"/>
-      <c r="E10" s="115"/>
-      <c r="F10" s="115"/>
-      <c r="G10" s="115"/>
-      <c r="H10" s="115"/>
-      <c r="I10" s="115"/>
-      <c r="J10" s="115"/>
-      <c r="K10" s="115"/>
-      <c r="L10" s="115"/>
-      <c r="M10" s="115"/>
-      <c r="N10" s="115"/>
-    </row>
-    <row r="11" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="112"/>
-      <c r="B11" s="115"/>
-      <c r="C11" s="120"/>
-      <c r="D11" s="120"/>
-      <c r="E11" s="120"/>
-      <c r="F11" s="120"/>
-      <c r="G11" s="120"/>
-      <c r="H11" s="120"/>
-      <c r="I11" s="120"/>
-      <c r="J11" s="120"/>
-      <c r="K11" s="120"/>
-      <c r="L11" s="120"/>
-      <c r="M11" s="120"/>
-      <c r="N11" s="120"/>
-    </row>
-    <row r="12" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="112"/>
-      <c r="B12" s="115"/>
-      <c r="C12" s="115"/>
-      <c r="D12" s="115"/>
-      <c r="E12" s="115"/>
-      <c r="F12" s="115"/>
-      <c r="G12" s="115"/>
-      <c r="H12" s="115"/>
-      <c r="I12" s="115"/>
-      <c r="J12" s="115"/>
-      <c r="K12" s="115"/>
-      <c r="L12" s="115"/>
-      <c r="M12" s="115"/>
-      <c r="N12" s="115"/>
-    </row>
-    <row r="13" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="112"/>
-      <c r="B13" s="115"/>
-      <c r="C13" s="120"/>
-      <c r="D13" s="120"/>
-      <c r="E13" s="120"/>
-      <c r="F13" s="120"/>
-      <c r="G13" s="120"/>
-      <c r="H13" s="120"/>
-      <c r="I13" s="120"/>
-      <c r="J13" s="120"/>
-      <c r="K13" s="120"/>
-      <c r="L13" s="120"/>
-      <c r="M13" s="120"/>
-      <c r="N13" s="120"/>
-    </row>
-    <row r="14" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="112"/>
-      <c r="B14" s="115" t="s">
+      <c r="C5" s="119"/>
+      <c r="D5" s="119"/>
+      <c r="E5" s="119"/>
+      <c r="F5" s="119"/>
+      <c r="G5" s="119"/>
+      <c r="H5" s="119"/>
+      <c r="I5" s="119"/>
+      <c r="J5" s="119"/>
+      <c r="K5" s="119"/>
+      <c r="L5" s="119"/>
+      <c r="M5" s="119"/>
+      <c r="N5" s="119"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="107"/>
+      <c r="B6" s="107"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="107"/>
+      <c r="F6" s="107"/>
+      <c r="G6" s="107"/>
+      <c r="H6" s="107"/>
+      <c r="I6" s="107"/>
+      <c r="J6" s="107"/>
+      <c r="K6" s="107"/>
+      <c r="L6" s="107"/>
+      <c r="M6" s="107"/>
+      <c r="N6" s="107"/>
+    </row>
+    <row r="7" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="107"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="108"/>
+      <c r="F7" s="108"/>
+      <c r="G7" s="108"/>
+      <c r="H7" s="108"/>
+      <c r="I7" s="108"/>
+      <c r="J7" s="108"/>
+      <c r="K7" s="108"/>
+      <c r="L7" s="108"/>
+      <c r="M7" s="108"/>
+      <c r="N7" s="108"/>
+    </row>
+    <row r="8" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="107"/>
+      <c r="B8" s="108"/>
+      <c r="C8" s="108"/>
+      <c r="D8" s="108"/>
+      <c r="E8" s="108"/>
+      <c r="F8" s="108"/>
+      <c r="G8" s="108"/>
+      <c r="H8" s="108"/>
+      <c r="I8" s="108"/>
+      <c r="J8" s="108"/>
+      <c r="K8" s="108"/>
+      <c r="L8" s="108"/>
+      <c r="M8" s="108"/>
+      <c r="N8" s="108"/>
+    </row>
+    <row r="9" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="107"/>
+      <c r="B9" s="108"/>
+      <c r="C9" s="112"/>
+      <c r="D9" s="112"/>
+      <c r="E9" s="112"/>
+      <c r="F9" s="112"/>
+      <c r="G9" s="112"/>
+      <c r="H9" s="112"/>
+      <c r="I9" s="112"/>
+      <c r="J9" s="112"/>
+      <c r="K9" s="112"/>
+      <c r="L9" s="112"/>
+      <c r="M9" s="112"/>
+      <c r="N9" s="112"/>
+    </row>
+    <row r="10" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="107"/>
+      <c r="B10" s="108"/>
+      <c r="C10" s="108"/>
+      <c r="D10" s="108"/>
+      <c r="E10" s="108"/>
+      <c r="F10" s="108"/>
+      <c r="G10" s="108"/>
+      <c r="H10" s="108"/>
+      <c r="I10" s="108"/>
+      <c r="J10" s="108"/>
+      <c r="K10" s="108"/>
+      <c r="L10" s="108"/>
+      <c r="M10" s="108"/>
+      <c r="N10" s="108"/>
+    </row>
+    <row r="11" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="107"/>
+      <c r="B11" s="108"/>
+      <c r="C11" s="112"/>
+      <c r="D11" s="112"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="112"/>
+      <c r="H11" s="112"/>
+      <c r="I11" s="112"/>
+      <c r="J11" s="112"/>
+      <c r="K11" s="112"/>
+      <c r="L11" s="112"/>
+      <c r="M11" s="112"/>
+      <c r="N11" s="112"/>
+    </row>
+    <row r="12" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="107"/>
+      <c r="B12" s="108"/>
+      <c r="C12" s="108"/>
+      <c r="D12" s="108"/>
+      <c r="E12" s="108"/>
+      <c r="F12" s="108"/>
+      <c r="G12" s="108"/>
+      <c r="H12" s="108"/>
+      <c r="I12" s="108"/>
+      <c r="J12" s="108"/>
+      <c r="K12" s="108"/>
+      <c r="L12" s="108"/>
+      <c r="M12" s="108"/>
+      <c r="N12" s="108"/>
+    </row>
+    <row r="13" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="107"/>
+      <c r="B13" s="108"/>
+      <c r="C13" s="112"/>
+      <c r="D13" s="112"/>
+      <c r="E13" s="112"/>
+      <c r="F13" s="112"/>
+      <c r="G13" s="112"/>
+      <c r="H13" s="112"/>
+      <c r="I13" s="112"/>
+      <c r="J13" s="112"/>
+      <c r="K13" s="112"/>
+      <c r="L13" s="112"/>
+      <c r="M13" s="112"/>
+      <c r="N13" s="112"/>
+    </row>
+    <row r="14" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="107"/>
+      <c r="B14" s="108" t="s">
         <v>410</v>
       </c>
-      <c r="C14" s="115"/>
-      <c r="D14" s="115"/>
-      <c r="E14" s="115"/>
-      <c r="F14" s="115"/>
-      <c r="G14" s="115"/>
-      <c r="H14" s="115"/>
-      <c r="I14" s="115"/>
-      <c r="J14" s="115"/>
-      <c r="K14" s="115"/>
-      <c r="L14" s="115"/>
-      <c r="M14" s="115"/>
-      <c r="N14" s="115"/>
-    </row>
-    <row r="15" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="112"/>
-      <c r="B15" s="115"/>
-      <c r="C15" s="120"/>
-      <c r="D15" s="120"/>
-      <c r="E15" s="120"/>
-      <c r="F15" s="120"/>
-      <c r="G15" s="120"/>
-      <c r="H15" s="120"/>
-      <c r="I15" s="120"/>
-      <c r="J15" s="120"/>
-      <c r="K15" s="120"/>
-      <c r="L15" s="120"/>
-      <c r="M15" s="120"/>
-      <c r="N15" s="120" t="s">
+      <c r="C14" s="108"/>
+      <c r="D14" s="108"/>
+      <c r="E14" s="108"/>
+      <c r="F14" s="108"/>
+      <c r="G14" s="108"/>
+      <c r="H14" s="108"/>
+      <c r="I14" s="108"/>
+      <c r="J14" s="108"/>
+      <c r="K14" s="108"/>
+      <c r="L14" s="108"/>
+      <c r="M14" s="108"/>
+      <c r="N14" s="108"/>
+    </row>
+    <row r="15" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="107"/>
+      <c r="B15" s="108"/>
+      <c r="C15" s="112"/>
+      <c r="D15" s="112"/>
+      <c r="E15" s="112"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="112"/>
+      <c r="H15" s="112"/>
+      <c r="I15" s="112"/>
+      <c r="J15" s="112"/>
+      <c r="K15" s="112"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="112" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="112"/>
-      <c r="B16" s="115"/>
-      <c r="C16" s="115"/>
-      <c r="D16" s="115"/>
-      <c r="E16" s="115"/>
-      <c r="F16" s="115"/>
-      <c r="G16" s="115"/>
-      <c r="H16" s="115"/>
-      <c r="I16" s="115"/>
-      <c r="J16" s="115"/>
-      <c r="K16" s="115"/>
-      <c r="L16" s="115"/>
-      <c r="M16" s="115"/>
-      <c r="N16" s="115"/>
-    </row>
-    <row r="17" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="112"/>
-      <c r="B17" s="115"/>
-      <c r="C17" s="120"/>
-      <c r="D17" s="120"/>
-      <c r="E17" s="120"/>
-      <c r="F17" s="120"/>
-      <c r="G17" s="120"/>
-      <c r="H17" s="120"/>
-      <c r="I17" s="120"/>
-      <c r="J17" s="120"/>
-      <c r="K17" s="120"/>
-      <c r="L17" s="120"/>
-      <c r="M17" s="120"/>
-      <c r="N17" s="120"/>
-    </row>
-    <row r="18" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="112"/>
-      <c r="B18" s="115"/>
-      <c r="C18" s="115"/>
-      <c r="D18" s="115"/>
-      <c r="E18" s="115"/>
-      <c r="F18" s="115"/>
-      <c r="G18" s="115"/>
-      <c r="H18" s="115"/>
-      <c r="I18" s="115"/>
-      <c r="J18" s="115"/>
-      <c r="K18" s="115"/>
-      <c r="L18" s="115"/>
-      <c r="M18" s="115"/>
-      <c r="N18" s="115"/>
-    </row>
-    <row r="19" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="112"/>
-      <c r="B19" s="115"/>
-      <c r="C19" s="115"/>
-      <c r="D19" s="115"/>
-      <c r="E19" s="115"/>
-      <c r="F19" s="115"/>
-      <c r="G19" s="115"/>
-      <c r="H19" s="115"/>
-      <c r="I19" s="115"/>
-      <c r="J19" s="115"/>
-      <c r="K19" s="115"/>
-      <c r="L19" s="115"/>
-      <c r="M19" s="115"/>
-      <c r="N19" s="115"/>
-    </row>
-    <row r="20" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="112"/>
-      <c r="B20" s="115"/>
-      <c r="C20" s="115"/>
-      <c r="D20" s="115"/>
-      <c r="E20" s="115"/>
-      <c r="F20" s="115"/>
-      <c r="G20" s="115"/>
-      <c r="H20" s="115"/>
-      <c r="I20" s="115"/>
-      <c r="J20" s="115"/>
-      <c r="K20" s="115"/>
-      <c r="L20" s="115"/>
-      <c r="M20" s="115"/>
-      <c r="N20" s="115"/>
-    </row>
-    <row r="21" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="112"/>
-      <c r="B21" s="115"/>
-      <c r="C21" s="115"/>
-      <c r="D21" s="115"/>
-      <c r="E21" s="115"/>
-      <c r="F21" s="115"/>
-      <c r="G21" s="115"/>
-      <c r="H21" s="115"/>
-      <c r="I21" s="115"/>
-      <c r="J21" s="115"/>
-      <c r="K21" s="115"/>
-      <c r="L21" s="115"/>
-      <c r="M21" s="115"/>
-      <c r="N21" s="115"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A22" s="112"/>
-      <c r="B22" s="112"/>
-      <c r="C22" s="116"/>
-      <c r="D22" s="116"/>
-      <c r="E22" s="116"/>
-      <c r="F22" s="116"/>
-      <c r="G22" s="116"/>
-      <c r="H22" s="116"/>
-      <c r="I22" s="116"/>
-      <c r="J22" s="116"/>
-      <c r="K22" s="116"/>
-      <c r="L22" s="116"/>
-      <c r="M22" s="116"/>
-      <c r="N22" s="116" t="s">
+    <row r="16" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="107"/>
+      <c r="B16" s="108"/>
+      <c r="C16" s="108"/>
+      <c r="D16" s="108"/>
+      <c r="E16" s="108"/>
+      <c r="F16" s="108"/>
+      <c r="G16" s="108"/>
+      <c r="H16" s="108"/>
+      <c r="I16" s="108"/>
+      <c r="J16" s="108"/>
+      <c r="K16" s="108"/>
+      <c r="L16" s="108"/>
+      <c r="M16" s="108"/>
+      <c r="N16" s="108"/>
+    </row>
+    <row r="17" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="107"/>
+      <c r="B17" s="108"/>
+      <c r="C17" s="112"/>
+      <c r="D17" s="112"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="112"/>
+      <c r="G17" s="112"/>
+      <c r="H17" s="112"/>
+      <c r="I17" s="112"/>
+      <c r="J17" s="112"/>
+      <c r="K17" s="112"/>
+      <c r="L17" s="112"/>
+      <c r="M17" s="112"/>
+      <c r="N17" s="112"/>
+    </row>
+    <row r="18" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="107"/>
+      <c r="B18" s="108"/>
+      <c r="C18" s="108"/>
+      <c r="D18" s="108"/>
+      <c r="E18" s="108"/>
+      <c r="F18" s="108"/>
+      <c r="G18" s="108"/>
+      <c r="H18" s="108"/>
+      <c r="I18" s="108"/>
+      <c r="J18" s="108"/>
+      <c r="K18" s="108"/>
+      <c r="L18" s="108"/>
+      <c r="M18" s="108"/>
+      <c r="N18" s="108"/>
+    </row>
+    <row r="19" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="107"/>
+      <c r="B19" s="108"/>
+      <c r="C19" s="108"/>
+      <c r="D19" s="108"/>
+      <c r="E19" s="108"/>
+      <c r="F19" s="108"/>
+      <c r="G19" s="108"/>
+      <c r="H19" s="108"/>
+      <c r="I19" s="108"/>
+      <c r="J19" s="108"/>
+      <c r="K19" s="108"/>
+      <c r="L19" s="108"/>
+      <c r="M19" s="108"/>
+      <c r="N19" s="108"/>
+    </row>
+    <row r="20" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="107"/>
+      <c r="B20" s="108"/>
+      <c r="C20" s="108"/>
+      <c r="D20" s="108"/>
+      <c r="E20" s="108"/>
+      <c r="F20" s="108"/>
+      <c r="G20" s="108"/>
+      <c r="H20" s="108"/>
+      <c r="I20" s="108"/>
+      <c r="J20" s="108"/>
+      <c r="K20" s="108"/>
+      <c r="L20" s="108"/>
+      <c r="M20" s="108"/>
+      <c r="N20" s="108"/>
+    </row>
+    <row r="21" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="107"/>
+      <c r="B21" s="108"/>
+      <c r="C21" s="108"/>
+      <c r="D21" s="108"/>
+      <c r="E21" s="108"/>
+      <c r="F21" s="108"/>
+      <c r="G21" s="108"/>
+      <c r="H21" s="108"/>
+      <c r="I21" s="108"/>
+      <c r="J21" s="108"/>
+      <c r="K21" s="108"/>
+      <c r="L21" s="108"/>
+      <c r="M21" s="108"/>
+      <c r="N21" s="108"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" s="107"/>
+      <c r="B22" s="107"/>
+      <c r="C22" s="109"/>
+      <c r="D22" s="109"/>
+      <c r="E22" s="109"/>
+      <c r="F22" s="109"/>
+      <c r="G22" s="109"/>
+      <c r="H22" s="109"/>
+      <c r="I22" s="109"/>
+      <c r="J22" s="109"/>
+      <c r="K22" s="109"/>
+      <c r="L22" s="109"/>
+      <c r="M22" s="109"/>
+      <c r="N22" s="109" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A23" s="112"/>
-      <c r="B23" s="112"/>
-      <c r="C23" s="117"/>
-      <c r="D23" s="117"/>
-      <c r="E23" s="117"/>
-      <c r="F23" s="117"/>
-      <c r="G23" s="117"/>
-      <c r="H23" s="117"/>
-      <c r="I23" s="117"/>
-      <c r="J23" s="117"/>
-      <c r="K23" s="117"/>
-      <c r="L23" s="117"/>
-      <c r="M23" s="117"/>
-      <c r="N23" s="117">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" s="107"/>
+      <c r="B23" s="107"/>
+      <c r="C23" s="110"/>
+      <c r="D23" s="110"/>
+      <c r="E23" s="110"/>
+      <c r="F23" s="110"/>
+      <c r="G23" s="110"/>
+      <c r="H23" s="110"/>
+      <c r="I23" s="110"/>
+      <c r="J23" s="110"/>
+      <c r="K23" s="110"/>
+      <c r="L23" s="110"/>
+      <c r="M23" s="110"/>
+      <c r="N23" s="110">
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A24" s="112"/>
-      <c r="B24" s="112"/>
-      <c r="C24" s="112"/>
-      <c r="D24" s="112"/>
-      <c r="E24" s="112"/>
-      <c r="F24" s="112"/>
-      <c r="G24" s="112"/>
-      <c r="H24" s="112"/>
-      <c r="I24" s="112"/>
-      <c r="J24" s="112"/>
-      <c r="K24" s="112"/>
-      <c r="L24" s="112"/>
-      <c r="M24" s="112"/>
-      <c r="N24" s="112"/>
-    </row>
-    <row r="25" spans="1:14" ht="16.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="112"/>
-      <c r="B25" s="114" t="s">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" s="107"/>
+      <c r="B24" s="107"/>
+      <c r="C24" s="107"/>
+      <c r="D24" s="107"/>
+      <c r="E24" s="107"/>
+      <c r="F24" s="107"/>
+      <c r="G24" s="107"/>
+      <c r="H24" s="107"/>
+      <c r="I24" s="107"/>
+      <c r="J24" s="107"/>
+      <c r="K24" s="107"/>
+      <c r="L24" s="107"/>
+      <c r="M24" s="107"/>
+      <c r="N24" s="107"/>
+    </row>
+    <row r="25" spans="1:14" ht="16.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="107"/>
+      <c r="B25" s="119" t="s">
         <v>413</v>
       </c>
-      <c r="C25" s="114"/>
-      <c r="D25" s="114"/>
-      <c r="E25" s="114"/>
-      <c r="F25" s="114"/>
-      <c r="G25" s="114"/>
-      <c r="H25" s="114"/>
-      <c r="I25" s="114"/>
-      <c r="J25" s="114"/>
-      <c r="K25" s="114"/>
-      <c r="L25" s="114"/>
-      <c r="M25" s="114"/>
-      <c r="N25" s="114"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A26" s="112"/>
-      <c r="B26" s="112"/>
-      <c r="C26" s="112"/>
-      <c r="D26" s="112"/>
-      <c r="E26" s="112"/>
-      <c r="F26" s="112"/>
-      <c r="G26" s="112"/>
-      <c r="H26" s="112"/>
-      <c r="I26" s="112"/>
-      <c r="J26" s="112"/>
-      <c r="K26" s="112"/>
-      <c r="L26" s="112"/>
-      <c r="M26" s="112"/>
-      <c r="N26" s="112"/>
-    </row>
-    <row r="27" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="112"/>
-      <c r="B27" s="115"/>
-      <c r="C27" s="115"/>
-      <c r="D27" s="115"/>
-      <c r="E27" s="115"/>
-      <c r="F27" s="115"/>
-      <c r="G27" s="115"/>
-      <c r="H27" s="115"/>
-      <c r="I27" s="115"/>
-      <c r="J27" s="115"/>
-      <c r="K27" s="115"/>
-      <c r="L27" s="115"/>
-      <c r="M27" s="115"/>
-      <c r="N27" s="115"/>
-    </row>
-    <row r="28" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="112"/>
-      <c r="B28" s="115"/>
-      <c r="C28" s="115"/>
-      <c r="D28" s="115"/>
-      <c r="E28" s="115"/>
-      <c r="F28" s="115"/>
-      <c r="G28" s="115"/>
-      <c r="H28" s="115"/>
-      <c r="I28" s="115"/>
-      <c r="J28" s="115"/>
-      <c r="K28" s="115"/>
-      <c r="L28" s="115"/>
-      <c r="M28" s="115"/>
-      <c r="N28" s="115" t="s">
+      <c r="C25" s="119"/>
+      <c r="D25" s="119"/>
+      <c r="E25" s="119"/>
+      <c r="F25" s="119"/>
+      <c r="G25" s="119"/>
+      <c r="H25" s="119"/>
+      <c r="I25" s="119"/>
+      <c r="J25" s="119"/>
+      <c r="K25" s="119"/>
+      <c r="L25" s="119"/>
+      <c r="M25" s="119"/>
+      <c r="N25" s="119"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" s="107"/>
+      <c r="B26" s="107"/>
+      <c r="C26" s="107"/>
+      <c r="D26" s="107"/>
+      <c r="E26" s="107"/>
+      <c r="F26" s="107"/>
+      <c r="G26" s="107"/>
+      <c r="H26" s="107"/>
+      <c r="I26" s="107"/>
+      <c r="J26" s="107"/>
+      <c r="K26" s="107"/>
+      <c r="L26" s="107"/>
+      <c r="M26" s="107"/>
+      <c r="N26" s="107"/>
+    </row>
+    <row r="27" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="107"/>
+      <c r="B27" s="108"/>
+      <c r="C27" s="108"/>
+      <c r="D27" s="108"/>
+      <c r="E27" s="108"/>
+      <c r="F27" s="108"/>
+      <c r="G27" s="108"/>
+      <c r="H27" s="108"/>
+      <c r="I27" s="108"/>
+      <c r="J27" s="108"/>
+      <c r="K27" s="108"/>
+      <c r="L27" s="108"/>
+      <c r="M27" s="108"/>
+      <c r="N27" s="108"/>
+    </row>
+    <row r="28" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="107"/>
+      <c r="B28" s="108"/>
+      <c r="C28" s="108"/>
+      <c r="D28" s="108"/>
+      <c r="E28" s="108"/>
+      <c r="F28" s="108"/>
+      <c r="G28" s="108"/>
+      <c r="H28" s="108"/>
+      <c r="I28" s="108"/>
+      <c r="J28" s="108"/>
+      <c r="K28" s="108"/>
+      <c r="L28" s="108"/>
+      <c r="M28" s="108"/>
+      <c r="N28" s="108" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="112"/>
-      <c r="B29" s="115"/>
-      <c r="C29" s="120"/>
-      <c r="D29" s="120"/>
-      <c r="E29" s="120"/>
-      <c r="F29" s="120"/>
-      <c r="G29" s="120"/>
-      <c r="H29" s="120"/>
-      <c r="I29" s="120"/>
-      <c r="J29" s="120"/>
-      <c r="K29" s="120"/>
-      <c r="L29" s="120" t="s">
+    <row r="29" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="107"/>
+      <c r="B29" s="108"/>
+      <c r="C29" s="112"/>
+      <c r="D29" s="112"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="112"/>
+      <c r="G29" s="112"/>
+      <c r="H29" s="112"/>
+      <c r="I29" s="112"/>
+      <c r="J29" s="112"/>
+      <c r="K29" s="112"/>
+      <c r="L29" s="112" t="s">
         <v>411</v>
       </c>
-      <c r="M29" s="120" t="s">
+      <c r="M29" s="112" t="s">
         <v>414</v>
       </c>
-      <c r="N29" s="120"/>
-    </row>
-    <row r="30" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="112"/>
-      <c r="B30" s="115"/>
-      <c r="C30" s="115"/>
-      <c r="D30" s="115"/>
-      <c r="E30" s="115"/>
-      <c r="F30" s="115"/>
-      <c r="G30" s="115"/>
-      <c r="H30" s="115"/>
-      <c r="I30" s="115"/>
-      <c r="J30" s="115" t="s">
+      <c r="N29" s="112"/>
+    </row>
+    <row r="30" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="107"/>
+      <c r="B30" s="108"/>
+      <c r="C30" s="108"/>
+      <c r="D30" s="108"/>
+      <c r="E30" s="108"/>
+      <c r="F30" s="108"/>
+      <c r="G30" s="108"/>
+      <c r="H30" s="108"/>
+      <c r="I30" s="108"/>
+      <c r="J30" s="108" t="s">
         <v>411</v>
       </c>
-      <c r="K30" s="115" t="s">
+      <c r="K30" s="108" t="s">
         <v>414</v>
       </c>
-      <c r="L30" s="115"/>
-      <c r="M30" s="115"/>
-      <c r="N30" s="115"/>
-    </row>
-    <row r="31" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="112"/>
-      <c r="B31" s="115"/>
-      <c r="C31" s="120"/>
-      <c r="D31" s="120"/>
-      <c r="E31" s="120"/>
-      <c r="F31" s="120"/>
-      <c r="G31" s="120"/>
-      <c r="H31" s="120" t="s">
+      <c r="L30" s="108"/>
+      <c r="M30" s="108"/>
+      <c r="N30" s="108"/>
+    </row>
+    <row r="31" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="107"/>
+      <c r="B31" s="108"/>
+      <c r="C31" s="112"/>
+      <c r="D31" s="112"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="112"/>
+      <c r="H31" s="112" t="s">
         <v>411</v>
       </c>
-      <c r="I31" s="120" t="s">
+      <c r="I31" s="112" t="s">
         <v>414</v>
       </c>
-      <c r="J31" s="120"/>
-      <c r="K31" s="120"/>
-      <c r="L31" s="120"/>
-      <c r="M31" s="120"/>
-      <c r="N31" s="120"/>
-    </row>
-    <row r="32" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="112"/>
-      <c r="B32" s="115"/>
-      <c r="C32" s="115"/>
-      <c r="D32" s="115"/>
-      <c r="E32" s="115"/>
-      <c r="F32" s="115"/>
-      <c r="G32" s="115" t="s">
+      <c r="J31" s="112"/>
+      <c r="K31" s="112"/>
+      <c r="L31" s="112"/>
+      <c r="M31" s="112"/>
+      <c r="N31" s="112"/>
+    </row>
+    <row r="32" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="107"/>
+      <c r="B32" s="108"/>
+      <c r="C32" s="108"/>
+      <c r="D32" s="108"/>
+      <c r="E32" s="108"/>
+      <c r="F32" s="108"/>
+      <c r="G32" s="108" t="s">
         <v>411</v>
       </c>
-      <c r="H32" s="115"/>
-      <c r="I32" s="115"/>
-      <c r="J32" s="115"/>
-      <c r="K32" s="115"/>
-      <c r="L32" s="115"/>
-      <c r="M32" s="115"/>
-      <c r="N32" s="115"/>
-    </row>
-    <row r="33" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="112"/>
-      <c r="B33" s="115"/>
-      <c r="C33" s="120"/>
-      <c r="D33" s="120"/>
-      <c r="E33" s="120" t="s">
+      <c r="H32" s="108"/>
+      <c r="I32" s="108"/>
+      <c r="J32" s="108"/>
+      <c r="K32" s="108"/>
+      <c r="L32" s="108"/>
+      <c r="M32" s="108"/>
+      <c r="N32" s="108"/>
+    </row>
+    <row r="33" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="107"/>
+      <c r="B33" s="108"/>
+      <c r="C33" s="112"/>
+      <c r="D33" s="112"/>
+      <c r="E33" s="112" t="s">
         <v>411</v>
       </c>
-      <c r="F33" s="120" t="s">
+      <c r="F33" s="112" t="s">
         <v>414</v>
       </c>
-      <c r="G33" s="120"/>
-      <c r="H33" s="120"/>
-      <c r="I33" s="120"/>
-      <c r="J33" s="120"/>
-      <c r="K33" s="120"/>
-      <c r="L33" s="120"/>
-      <c r="M33" s="120"/>
-      <c r="N33" s="120"/>
-    </row>
-    <row r="34" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="112"/>
-      <c r="B34" s="115" t="s">
+      <c r="G33" s="112"/>
+      <c r="H33" s="112"/>
+      <c r="I33" s="112"/>
+      <c r="J33" s="112"/>
+      <c r="K33" s="112"/>
+      <c r="L33" s="112"/>
+      <c r="M33" s="112"/>
+      <c r="N33" s="112"/>
+    </row>
+    <row r="34" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="107"/>
+      <c r="B34" s="108" t="s">
         <v>410</v>
       </c>
-      <c r="C34" s="115" t="s">
+      <c r="C34" s="108" t="s">
         <v>411</v>
       </c>
-      <c r="D34" s="115" t="s">
+      <c r="D34" s="108" t="s">
         <v>414</v>
       </c>
-      <c r="E34" s="115"/>
-      <c r="F34" s="115"/>
-      <c r="G34" s="115"/>
-      <c r="H34" s="115"/>
-      <c r="I34" s="115"/>
-      <c r="J34" s="115"/>
-      <c r="K34" s="115"/>
-      <c r="L34" s="115"/>
-      <c r="M34" s="115"/>
-      <c r="N34" s="115"/>
-    </row>
-    <row r="35" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="112"/>
-      <c r="B35" s="115"/>
-      <c r="C35" s="120"/>
-      <c r="D35" s="120"/>
-      <c r="E35" s="120"/>
-      <c r="F35" s="120"/>
-      <c r="G35" s="120"/>
-      <c r="H35" s="120"/>
-      <c r="I35" s="120"/>
-      <c r="J35" s="120"/>
-      <c r="K35" s="120"/>
-      <c r="L35" s="120"/>
-      <c r="M35" s="120"/>
-      <c r="N35" s="120"/>
-    </row>
-    <row r="36" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="112"/>
-      <c r="B36" s="115"/>
-      <c r="C36" s="115"/>
-      <c r="D36" s="115"/>
-      <c r="E36" s="115"/>
-      <c r="F36" s="115"/>
-      <c r="G36" s="115"/>
-      <c r="H36" s="115"/>
-      <c r="I36" s="115"/>
-      <c r="J36" s="115"/>
-      <c r="K36" s="115"/>
-      <c r="L36" s="115"/>
-      <c r="M36" s="115"/>
-      <c r="N36" s="115"/>
-    </row>
-    <row r="37" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="112"/>
-      <c r="B37" s="115"/>
-      <c r="C37" s="120"/>
-      <c r="D37" s="120"/>
-      <c r="E37" s="120"/>
-      <c r="F37" s="120"/>
-      <c r="G37" s="120"/>
-      <c r="H37" s="120"/>
-      <c r="I37" s="120"/>
-      <c r="J37" s="120"/>
-      <c r="K37" s="120"/>
-      <c r="L37" s="120"/>
-      <c r="M37" s="120"/>
-      <c r="N37" s="120"/>
-    </row>
-    <row r="38" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="112"/>
-      <c r="B38" s="115"/>
-      <c r="C38" s="115"/>
-      <c r="D38" s="115"/>
-      <c r="E38" s="115"/>
-      <c r="F38" s="115"/>
-      <c r="G38" s="115"/>
-      <c r="H38" s="115"/>
-      <c r="I38" s="115"/>
-      <c r="J38" s="115"/>
-      <c r="K38" s="115"/>
-      <c r="L38" s="115"/>
-      <c r="M38" s="115"/>
-      <c r="N38" s="115"/>
-    </row>
-    <row r="39" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="112"/>
-      <c r="B39" s="115"/>
-      <c r="C39" s="115"/>
-      <c r="D39" s="115"/>
-      <c r="E39" s="115"/>
-      <c r="F39" s="115"/>
-      <c r="G39" s="115"/>
-      <c r="H39" s="115"/>
-      <c r="I39" s="115"/>
-      <c r="J39" s="115"/>
-      <c r="K39" s="115"/>
-      <c r="L39" s="115"/>
-      <c r="M39" s="115"/>
-      <c r="N39" s="115"/>
-    </row>
-    <row r="40" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="112"/>
-      <c r="B40" s="115"/>
-      <c r="C40" s="115"/>
-      <c r="D40" s="115"/>
-      <c r="E40" s="115"/>
-      <c r="F40" s="115"/>
-      <c r="G40" s="115"/>
-      <c r="H40" s="115"/>
-      <c r="I40" s="115"/>
-      <c r="J40" s="115"/>
-      <c r="K40" s="115"/>
-      <c r="L40" s="115"/>
-      <c r="M40" s="115"/>
-      <c r="N40" s="115"/>
-    </row>
-    <row r="41" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="112"/>
-      <c r="B41" s="115"/>
-      <c r="C41" s="115"/>
-      <c r="D41" s="115"/>
-      <c r="E41" s="115"/>
-      <c r="F41" s="115"/>
-      <c r="G41" s="115"/>
-      <c r="H41" s="115"/>
-      <c r="I41" s="115"/>
-      <c r="J41" s="115"/>
-      <c r="K41" s="115"/>
-      <c r="L41" s="115"/>
-      <c r="M41" s="115"/>
-      <c r="N41" s="115"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A42" s="112"/>
-      <c r="B42" s="112"/>
-      <c r="C42" s="116" t="s">
+      <c r="E34" s="108"/>
+      <c r="F34" s="108"/>
+      <c r="G34" s="108"/>
+      <c r="H34" s="108"/>
+      <c r="I34" s="108"/>
+      <c r="J34" s="108"/>
+      <c r="K34" s="108"/>
+      <c r="L34" s="108"/>
+      <c r="M34" s="108"/>
+      <c r="N34" s="108"/>
+    </row>
+    <row r="35" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="107"/>
+      <c r="B35" s="108"/>
+      <c r="C35" s="112"/>
+      <c r="D35" s="112"/>
+      <c r="E35" s="112"/>
+      <c r="F35" s="112"/>
+      <c r="G35" s="112"/>
+      <c r="H35" s="112"/>
+      <c r="I35" s="112"/>
+      <c r="J35" s="112"/>
+      <c r="K35" s="112"/>
+      <c r="L35" s="112"/>
+      <c r="M35" s="112"/>
+      <c r="N35" s="112"/>
+    </row>
+    <row r="36" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="107"/>
+      <c r="B36" s="108"/>
+      <c r="C36" s="108"/>
+      <c r="D36" s="108"/>
+      <c r="E36" s="108"/>
+      <c r="F36" s="108"/>
+      <c r="G36" s="108"/>
+      <c r="H36" s="108"/>
+      <c r="I36" s="108"/>
+      <c r="J36" s="108"/>
+      <c r="K36" s="108"/>
+      <c r="L36" s="108"/>
+      <c r="M36" s="108"/>
+      <c r="N36" s="108"/>
+    </row>
+    <row r="37" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="107"/>
+      <c r="B37" s="108"/>
+      <c r="C37" s="112"/>
+      <c r="D37" s="112"/>
+      <c r="E37" s="112"/>
+      <c r="F37" s="112"/>
+      <c r="G37" s="112"/>
+      <c r="H37" s="112"/>
+      <c r="I37" s="112"/>
+      <c r="J37" s="112"/>
+      <c r="K37" s="112"/>
+      <c r="L37" s="112"/>
+      <c r="M37" s="112"/>
+      <c r="N37" s="112"/>
+    </row>
+    <row r="38" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="107"/>
+      <c r="B38" s="108"/>
+      <c r="C38" s="108"/>
+      <c r="D38" s="108"/>
+      <c r="E38" s="108"/>
+      <c r="F38" s="108"/>
+      <c r="G38" s="108"/>
+      <c r="H38" s="108"/>
+      <c r="I38" s="108"/>
+      <c r="J38" s="108"/>
+      <c r="K38" s="108"/>
+      <c r="L38" s="108"/>
+      <c r="M38" s="108"/>
+      <c r="N38" s="108"/>
+    </row>
+    <row r="39" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="107"/>
+      <c r="B39" s="108"/>
+      <c r="C39" s="108"/>
+      <c r="D39" s="108"/>
+      <c r="E39" s="108"/>
+      <c r="F39" s="108"/>
+      <c r="G39" s="108"/>
+      <c r="H39" s="108"/>
+      <c r="I39" s="108"/>
+      <c r="J39" s="108"/>
+      <c r="K39" s="108"/>
+      <c r="L39" s="108"/>
+      <c r="M39" s="108"/>
+      <c r="N39" s="108"/>
+    </row>
+    <row r="40" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="107"/>
+      <c r="B40" s="108"/>
+      <c r="C40" s="108"/>
+      <c r="D40" s="108"/>
+      <c r="E40" s="108"/>
+      <c r="F40" s="108"/>
+      <c r="G40" s="108"/>
+      <c r="H40" s="108"/>
+      <c r="I40" s="108"/>
+      <c r="J40" s="108"/>
+      <c r="K40" s="108"/>
+      <c r="L40" s="108"/>
+      <c r="M40" s="108"/>
+      <c r="N40" s="108"/>
+    </row>
+    <row r="41" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="107"/>
+      <c r="B41" s="108"/>
+      <c r="C41" s="108"/>
+      <c r="D41" s="108"/>
+      <c r="E41" s="108"/>
+      <c r="F41" s="108"/>
+      <c r="G41" s="108"/>
+      <c r="H41" s="108"/>
+      <c r="I41" s="108"/>
+      <c r="J41" s="108"/>
+      <c r="K41" s="108"/>
+      <c r="L41" s="108"/>
+      <c r="M41" s="108"/>
+      <c r="N41" s="108"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A42" s="107"/>
+      <c r="B42" s="107"/>
+      <c r="C42" s="109" t="s">
         <v>415</v>
       </c>
-      <c r="D42" s="116" t="s">
+      <c r="D42" s="109" t="s">
         <v>416</v>
       </c>
-      <c r="E42" s="116" t="s">
+      <c r="E42" s="109" t="s">
         <v>417</v>
       </c>
-      <c r="F42" s="116" t="s">
+      <c r="F42" s="109" t="s">
         <v>418</v>
       </c>
-      <c r="G42" s="116" t="s">
+      <c r="G42" s="109" t="s">
         <v>419</v>
       </c>
-      <c r="H42" s="116" t="s">
+      <c r="H42" s="109" t="s">
         <v>420</v>
       </c>
-      <c r="I42" s="116" t="s">
+      <c r="I42" s="109" t="s">
         <v>421</v>
       </c>
-      <c r="J42" s="116" t="s">
+      <c r="J42" s="109" t="s">
         <v>422</v>
       </c>
-      <c r="K42" s="116" t="s">
+      <c r="K42" s="109" t="s">
         <v>423</v>
       </c>
-      <c r="L42" s="116" t="s">
+      <c r="L42" s="109" t="s">
         <v>424</v>
       </c>
-      <c r="M42" s="116" t="s">
+      <c r="M42" s="109" t="s">
         <v>425</v>
       </c>
-      <c r="N42" s="116" t="s">
+      <c r="N42" s="109" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A43" s="112"/>
-      <c r="B43" s="112"/>
-      <c r="C43" s="117">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A43" s="107"/>
+      <c r="B43" s="107"/>
+      <c r="C43" s="110">
         <v>33</v>
       </c>
-      <c r="D43" s="117">
+      <c r="D43" s="110">
         <v>35</v>
       </c>
-      <c r="E43" s="117">
+      <c r="E43" s="110">
         <v>37</v>
       </c>
-      <c r="F43" s="117">
+      <c r="F43" s="110">
         <v>39</v>
       </c>
-      <c r="G43" s="117">
+      <c r="G43" s="110">
         <v>41</v>
       </c>
-      <c r="H43" s="117">
+      <c r="H43" s="110">
         <v>44</v>
       </c>
-      <c r="I43" s="117">
+      <c r="I43" s="110">
         <v>46</v>
       </c>
-      <c r="J43" s="117">
+      <c r="J43" s="110">
         <v>49</v>
       </c>
-      <c r="K43" s="117">
+      <c r="K43" s="110">
         <v>52</v>
       </c>
-      <c r="L43" s="117">
+      <c r="L43" s="110">
         <v>55</v>
       </c>
-      <c r="M43" s="117">
+      <c r="M43" s="110">
         <v>58</v>
       </c>
-      <c r="N43" s="117">
+      <c r="N43" s="110">
         <v>62</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A44" s="112"/>
-      <c r="B44" s="112"/>
-      <c r="C44" s="112"/>
-      <c r="D44" s="112"/>
-      <c r="E44" s="112"/>
-      <c r="F44" s="112"/>
-      <c r="G44" s="112"/>
-      <c r="H44" s="112"/>
-      <c r="I44" s="112"/>
-      <c r="J44" s="112"/>
-      <c r="K44" s="112"/>
-      <c r="L44" s="112"/>
-      <c r="M44" s="112"/>
-      <c r="N44" s="112"/>
-    </row>
-    <row r="45" spans="1:14" ht="16.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="112"/>
-      <c r="B45" s="114" t="s">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A44" s="107"/>
+      <c r="B44" s="107"/>
+      <c r="C44" s="107"/>
+      <c r="D44" s="107"/>
+      <c r="E44" s="107"/>
+      <c r="F44" s="107"/>
+      <c r="G44" s="107"/>
+      <c r="H44" s="107"/>
+      <c r="I44" s="107"/>
+      <c r="J44" s="107"/>
+      <c r="K44" s="107"/>
+      <c r="L44" s="107"/>
+      <c r="M44" s="107"/>
+      <c r="N44" s="107"/>
+    </row>
+    <row r="45" spans="1:14" ht="16.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="107"/>
+      <c r="B45" s="119" t="s">
         <v>427</v>
       </c>
-      <c r="C45" s="114"/>
-      <c r="D45" s="114"/>
-      <c r="E45" s="114"/>
-      <c r="F45" s="114"/>
-      <c r="G45" s="114"/>
-      <c r="H45" s="114"/>
-      <c r="I45" s="114"/>
-      <c r="J45" s="114"/>
-      <c r="K45" s="114"/>
-      <c r="L45" s="114"/>
-      <c r="M45" s="114"/>
-      <c r="N45" s="114"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A46" s="112"/>
-      <c r="B46" s="112"/>
-      <c r="C46" s="112"/>
-      <c r="D46" s="112"/>
-      <c r="E46" s="112"/>
-      <c r="F46" s="112"/>
-      <c r="G46" s="112"/>
-      <c r="H46" s="112"/>
-      <c r="I46" s="112"/>
-      <c r="J46" s="112"/>
-      <c r="K46" s="112"/>
-      <c r="L46" s="112"/>
-      <c r="M46" s="112"/>
-      <c r="N46" s="112"/>
-    </row>
-    <row r="47" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="112"/>
-      <c r="B47" s="115"/>
-      <c r="C47" s="115"/>
-      <c r="D47" s="115"/>
-      <c r="E47" s="115"/>
-      <c r="F47" s="115"/>
-      <c r="G47" s="115"/>
-      <c r="H47" s="115"/>
-      <c r="I47" s="115"/>
-      <c r="J47" s="115"/>
-      <c r="K47" s="115"/>
-      <c r="L47" s="115"/>
-      <c r="M47" s="115"/>
-      <c r="N47" s="115"/>
-    </row>
-    <row r="48" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="112"/>
-      <c r="B48" s="115"/>
-      <c r="C48" s="115"/>
-      <c r="D48" s="115"/>
-      <c r="E48" s="115"/>
-      <c r="F48" s="115"/>
-      <c r="G48" s="115"/>
-      <c r="H48" s="115"/>
-      <c r="I48" s="115"/>
-      <c r="J48" s="115"/>
-      <c r="K48" s="115"/>
-      <c r="L48" s="115"/>
-      <c r="M48" s="115"/>
-      <c r="N48" s="115"/>
-    </row>
-    <row r="49" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="112"/>
-      <c r="B49" s="115"/>
-      <c r="C49" s="120"/>
-      <c r="D49" s="120"/>
-      <c r="E49" s="120"/>
-      <c r="F49" s="120"/>
-      <c r="G49" s="120"/>
-      <c r="H49" s="120"/>
-      <c r="I49" s="120"/>
-      <c r="J49" s="120"/>
-      <c r="K49" s="120"/>
-      <c r="L49" s="120"/>
-      <c r="M49" s="120"/>
-      <c r="N49" s="120"/>
-    </row>
-    <row r="50" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="112"/>
-      <c r="B50" s="115"/>
-      <c r="C50" s="115"/>
-      <c r="D50" s="115"/>
-      <c r="E50" s="115"/>
-      <c r="F50" s="115"/>
-      <c r="G50" s="115"/>
-      <c r="H50" s="115"/>
-      <c r="I50" s="115"/>
-      <c r="J50" s="115"/>
-      <c r="K50" s="115"/>
-      <c r="L50" s="115"/>
-      <c r="M50" s="115"/>
-      <c r="N50" s="115"/>
-    </row>
-    <row r="51" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="112"/>
-      <c r="B51" s="115"/>
-      <c r="C51" s="120"/>
-      <c r="D51" s="120"/>
-      <c r="E51" s="120"/>
-      <c r="F51" s="120"/>
-      <c r="G51" s="120"/>
-      <c r="H51" s="120"/>
-      <c r="I51" s="120"/>
-      <c r="J51" s="120"/>
-      <c r="K51" s="120"/>
-      <c r="L51" s="120"/>
-      <c r="M51" s="120"/>
-      <c r="N51" s="120"/>
-    </row>
-    <row r="52" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="112"/>
-      <c r="B52" s="115"/>
-      <c r="C52" s="115"/>
-      <c r="D52" s="115"/>
-      <c r="E52" s="115"/>
-      <c r="F52" s="115"/>
-      <c r="G52" s="115"/>
-      <c r="H52" s="115"/>
-      <c r="I52" s="115"/>
-      <c r="J52" s="115"/>
-      <c r="K52" s="115"/>
-      <c r="L52" s="115"/>
-      <c r="M52" s="115"/>
-      <c r="N52" s="115"/>
-    </row>
-    <row r="53" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="112"/>
-      <c r="B53" s="115"/>
-      <c r="C53" s="120"/>
-      <c r="D53" s="120"/>
-      <c r="E53" s="120"/>
-      <c r="F53" s="120"/>
-      <c r="G53" s="120"/>
-      <c r="H53" s="120"/>
-      <c r="I53" s="120"/>
-      <c r="J53" s="120"/>
-      <c r="K53" s="120"/>
-      <c r="L53" s="120"/>
-      <c r="M53" s="120"/>
-      <c r="N53" s="120"/>
-    </row>
-    <row r="54" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="112"/>
-      <c r="B54" s="115" t="s">
+      <c r="C45" s="119"/>
+      <c r="D45" s="119"/>
+      <c r="E45" s="119"/>
+      <c r="F45" s="119"/>
+      <c r="G45" s="119"/>
+      <c r="H45" s="119"/>
+      <c r="I45" s="119"/>
+      <c r="J45" s="119"/>
+      <c r="K45" s="119"/>
+      <c r="L45" s="119"/>
+      <c r="M45" s="119"/>
+      <c r="N45" s="119"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A46" s="107"/>
+      <c r="B46" s="107"/>
+      <c r="C46" s="107"/>
+      <c r="D46" s="107"/>
+      <c r="E46" s="107"/>
+      <c r="F46" s="107"/>
+      <c r="G46" s="107"/>
+      <c r="H46" s="107"/>
+      <c r="I46" s="107"/>
+      <c r="J46" s="107"/>
+      <c r="K46" s="107"/>
+      <c r="L46" s="107"/>
+      <c r="M46" s="107"/>
+      <c r="N46" s="107"/>
+    </row>
+    <row r="47" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="107"/>
+      <c r="B47" s="108"/>
+      <c r="C47" s="108"/>
+      <c r="D47" s="108"/>
+      <c r="E47" s="108"/>
+      <c r="F47" s="108"/>
+      <c r="G47" s="108"/>
+      <c r="H47" s="108"/>
+      <c r="I47" s="108"/>
+      <c r="J47" s="108"/>
+      <c r="K47" s="108"/>
+      <c r="L47" s="108"/>
+      <c r="M47" s="108"/>
+      <c r="N47" s="108"/>
+    </row>
+    <row r="48" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="107"/>
+      <c r="B48" s="108"/>
+      <c r="C48" s="108"/>
+      <c r="D48" s="108"/>
+      <c r="E48" s="108"/>
+      <c r="F48" s="108"/>
+      <c r="G48" s="108"/>
+      <c r="H48" s="108"/>
+      <c r="I48" s="108"/>
+      <c r="J48" s="108"/>
+      <c r="K48" s="108"/>
+      <c r="L48" s="108"/>
+      <c r="M48" s="108"/>
+      <c r="N48" s="108"/>
+    </row>
+    <row r="49" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="107"/>
+      <c r="B49" s="108"/>
+      <c r="C49" s="112"/>
+      <c r="D49" s="112"/>
+      <c r="E49" s="112"/>
+      <c r="F49" s="112"/>
+      <c r="G49" s="112"/>
+      <c r="H49" s="112"/>
+      <c r="I49" s="112"/>
+      <c r="J49" s="112"/>
+      <c r="K49" s="112"/>
+      <c r="L49" s="112"/>
+      <c r="M49" s="112"/>
+      <c r="N49" s="112"/>
+    </row>
+    <row r="50" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="107"/>
+      <c r="B50" s="108"/>
+      <c r="C50" s="108"/>
+      <c r="D50" s="108"/>
+      <c r="E50" s="108"/>
+      <c r="F50" s="108"/>
+      <c r="G50" s="108"/>
+      <c r="H50" s="108"/>
+      <c r="I50" s="108"/>
+      <c r="J50" s="108"/>
+      <c r="K50" s="108"/>
+      <c r="L50" s="108"/>
+      <c r="M50" s="108"/>
+      <c r="N50" s="108"/>
+    </row>
+    <row r="51" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="107"/>
+      <c r="B51" s="108"/>
+      <c r="C51" s="112"/>
+      <c r="D51" s="112"/>
+      <c r="E51" s="112"/>
+      <c r="F51" s="112"/>
+      <c r="G51" s="112"/>
+      <c r="H51" s="112"/>
+      <c r="I51" s="112"/>
+      <c r="J51" s="112"/>
+      <c r="K51" s="112"/>
+      <c r="L51" s="112"/>
+      <c r="M51" s="112"/>
+      <c r="N51" s="112"/>
+    </row>
+    <row r="52" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="107"/>
+      <c r="B52" s="108"/>
+      <c r="C52" s="108"/>
+      <c r="D52" s="108"/>
+      <c r="E52" s="108"/>
+      <c r="F52" s="108"/>
+      <c r="G52" s="108"/>
+      <c r="H52" s="108"/>
+      <c r="I52" s="108"/>
+      <c r="J52" s="108"/>
+      <c r="K52" s="108"/>
+      <c r="L52" s="108"/>
+      <c r="M52" s="108"/>
+      <c r="N52" s="108"/>
+    </row>
+    <row r="53" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="107"/>
+      <c r="B53" s="108"/>
+      <c r="C53" s="112"/>
+      <c r="D53" s="112"/>
+      <c r="E53" s="112"/>
+      <c r="F53" s="112"/>
+      <c r="G53" s="112"/>
+      <c r="H53" s="112"/>
+      <c r="I53" s="112"/>
+      <c r="J53" s="112"/>
+      <c r="K53" s="112"/>
+      <c r="L53" s="112"/>
+      <c r="M53" s="112"/>
+      <c r="N53" s="112"/>
+    </row>
+    <row r="54" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="107"/>
+      <c r="B54" s="108" t="s">
         <v>428</v>
       </c>
-      <c r="C54" s="115"/>
-      <c r="D54" s="115"/>
-      <c r="E54" s="115"/>
-      <c r="F54" s="115"/>
-      <c r="G54" s="115"/>
-      <c r="H54" s="115"/>
-      <c r="I54" s="115"/>
-      <c r="J54" s="115"/>
-      <c r="K54" s="115"/>
-      <c r="L54" s="115"/>
-      <c r="M54" s="115"/>
-      <c r="N54" s="115"/>
-    </row>
-    <row r="55" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="112"/>
-      <c r="B55" s="115"/>
-      <c r="C55" s="120"/>
-      <c r="D55" s="120"/>
-      <c r="E55" s="120"/>
-      <c r="F55" s="120"/>
-      <c r="G55" s="120"/>
-      <c r="H55" s="120"/>
-      <c r="I55" s="120"/>
-      <c r="J55" s="120"/>
-      <c r="K55" s="120"/>
-      <c r="L55" s="120"/>
-      <c r="M55" s="120"/>
-      <c r="N55" s="120" t="s">
+      <c r="C54" s="108"/>
+      <c r="D54" s="108"/>
+      <c r="E54" s="108"/>
+      <c r="F54" s="108"/>
+      <c r="G54" s="108"/>
+      <c r="H54" s="108"/>
+      <c r="I54" s="108"/>
+      <c r="J54" s="108"/>
+      <c r="K54" s="108"/>
+      <c r="L54" s="108"/>
+      <c r="M54" s="108"/>
+      <c r="N54" s="108"/>
+    </row>
+    <row r="55" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="107"/>
+      <c r="B55" s="108"/>
+      <c r="C55" s="112"/>
+      <c r="D55" s="112"/>
+      <c r="E55" s="112"/>
+      <c r="F55" s="112"/>
+      <c r="G55" s="112"/>
+      <c r="H55" s="112"/>
+      <c r="I55" s="112"/>
+      <c r="J55" s="112"/>
+      <c r="K55" s="112"/>
+      <c r="L55" s="112"/>
+      <c r="M55" s="112"/>
+      <c r="N55" s="112" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="112"/>
-      <c r="B56" s="115"/>
-      <c r="C56" s="115"/>
-      <c r="D56" s="115"/>
-      <c r="E56" s="115"/>
-      <c r="F56" s="115"/>
-      <c r="G56" s="115"/>
-      <c r="H56" s="115"/>
-      <c r="I56" s="115"/>
-      <c r="J56" s="115"/>
-      <c r="K56" s="115"/>
-      <c r="L56" s="115" t="s">
+    <row r="56" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="107"/>
+      <c r="B56" s="108"/>
+      <c r="C56" s="108"/>
+      <c r="D56" s="108"/>
+      <c r="E56" s="108"/>
+      <c r="F56" s="108"/>
+      <c r="G56" s="108"/>
+      <c r="H56" s="108"/>
+      <c r="I56" s="108"/>
+      <c r="J56" s="108"/>
+      <c r="K56" s="108"/>
+      <c r="L56" s="108" t="s">
         <v>411</v>
       </c>
-      <c r="M56" s="115" t="s">
+      <c r="M56" s="108" t="s">
         <v>414</v>
       </c>
-      <c r="N56" s="115"/>
-    </row>
-    <row r="57" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="112"/>
-      <c r="B57" s="115"/>
-      <c r="C57" s="120"/>
-      <c r="D57" s="120"/>
-      <c r="E57" s="120"/>
-      <c r="F57" s="120"/>
-      <c r="G57" s="120"/>
-      <c r="H57" s="120"/>
-      <c r="I57" s="120"/>
-      <c r="J57" s="120" t="s">
+      <c r="N56" s="108"/>
+    </row>
+    <row r="57" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="107"/>
+      <c r="B57" s="108"/>
+      <c r="C57" s="112"/>
+      <c r="D57" s="112"/>
+      <c r="E57" s="112"/>
+      <c r="F57" s="112"/>
+      <c r="G57" s="112"/>
+      <c r="H57" s="112"/>
+      <c r="I57" s="112"/>
+      <c r="J57" s="112" t="s">
         <v>411</v>
       </c>
-      <c r="K57" s="120" t="s">
+      <c r="K57" s="112" t="s">
         <v>414</v>
       </c>
-      <c r="L57" s="120"/>
-      <c r="M57" s="120"/>
-      <c r="N57" s="120"/>
-    </row>
-    <row r="58" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="112"/>
-      <c r="B58" s="115"/>
-      <c r="C58" s="115"/>
-      <c r="D58" s="115"/>
-      <c r="E58" s="115"/>
-      <c r="F58" s="115"/>
-      <c r="G58" s="115"/>
-      <c r="H58" s="115" t="s">
+      <c r="L57" s="112"/>
+      <c r="M57" s="112"/>
+      <c r="N57" s="112"/>
+    </row>
+    <row r="58" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="107"/>
+      <c r="B58" s="108"/>
+      <c r="C58" s="108"/>
+      <c r="D58" s="108"/>
+      <c r="E58" s="108"/>
+      <c r="F58" s="108"/>
+      <c r="G58" s="108"/>
+      <c r="H58" s="108" t="s">
         <v>411</v>
       </c>
-      <c r="I58" s="115" t="s">
+      <c r="I58" s="108" t="s">
         <v>414</v>
       </c>
-      <c r="J58" s="115"/>
-      <c r="K58" s="115"/>
-      <c r="L58" s="115"/>
-      <c r="M58" s="115"/>
-      <c r="N58" s="115"/>
-    </row>
-    <row r="59" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="112"/>
-      <c r="B59" s="115"/>
-      <c r="C59" s="115"/>
-      <c r="D59" s="115"/>
-      <c r="E59" s="115"/>
-      <c r="F59" s="115"/>
-      <c r="G59" s="120" t="s">
+      <c r="J58" s="108"/>
+      <c r="K58" s="108"/>
+      <c r="L58" s="108"/>
+      <c r="M58" s="108"/>
+      <c r="N58" s="108"/>
+    </row>
+    <row r="59" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="107"/>
+      <c r="B59" s="108"/>
+      <c r="C59" s="108"/>
+      <c r="D59" s="108"/>
+      <c r="E59" s="108"/>
+      <c r="F59" s="108"/>
+      <c r="G59" s="112" t="s">
         <v>411</v>
       </c>
-      <c r="H59" s="115"/>
-      <c r="I59" s="115"/>
-      <c r="J59" s="115"/>
-      <c r="K59" s="115"/>
-      <c r="L59" s="115"/>
-      <c r="M59" s="115"/>
-      <c r="N59" s="115"/>
-    </row>
-    <row r="60" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="112"/>
-      <c r="B60" s="115"/>
-      <c r="C60" s="115"/>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115" t="s">
+      <c r="H59" s="108"/>
+      <c r="I59" s="108"/>
+      <c r="J59" s="108"/>
+      <c r="K59" s="108"/>
+      <c r="L59" s="108"/>
+      <c r="M59" s="108"/>
+      <c r="N59" s="108"/>
+    </row>
+    <row r="60" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="107"/>
+      <c r="B60" s="108"/>
+      <c r="C60" s="108"/>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108" t="s">
         <v>411</v>
       </c>
-      <c r="F60" s="115" t="s">
+      <c r="F60" s="108" t="s">
         <v>414</v>
       </c>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="115"/>
-      <c r="L60" s="115"/>
-      <c r="M60" s="115"/>
-      <c r="N60" s="115"/>
-    </row>
-    <row r="61" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="112"/>
-      <c r="B61" s="115"/>
-      <c r="C61" s="120" t="s">
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="108"/>
+      <c r="L60" s="108"/>
+      <c r="M60" s="108"/>
+      <c r="N60" s="108"/>
+    </row>
+    <row r="61" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="107"/>
+      <c r="B61" s="108"/>
+      <c r="C61" s="112" t="s">
         <v>411</v>
       </c>
-      <c r="D61" s="120" t="s">
+      <c r="D61" s="112" t="s">
         <v>414</v>
       </c>
-      <c r="E61" s="115"/>
-      <c r="F61" s="115"/>
-      <c r="G61" s="115"/>
-      <c r="H61" s="115"/>
-      <c r="I61" s="115"/>
-      <c r="J61" s="115"/>
-      <c r="K61" s="115"/>
-      <c r="L61" s="115"/>
-      <c r="M61" s="115"/>
-      <c r="N61" s="115"/>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A62" s="112"/>
-      <c r="B62" s="112"/>
-      <c r="C62" s="116" t="s">
+      <c r="E61" s="108"/>
+      <c r="F61" s="108"/>
+      <c r="G61" s="108"/>
+      <c r="H61" s="108"/>
+      <c r="I61" s="108"/>
+      <c r="J61" s="108"/>
+      <c r="K61" s="108"/>
+      <c r="L61" s="108"/>
+      <c r="M61" s="108"/>
+      <c r="N61" s="108"/>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A62" s="107"/>
+      <c r="B62" s="107"/>
+      <c r="C62" s="109" t="s">
         <v>429</v>
       </c>
-      <c r="D62" s="116" t="s">
+      <c r="D62" s="109" t="s">
         <v>430</v>
       </c>
-      <c r="E62" s="116" t="s">
+      <c r="E62" s="109" t="s">
         <v>431</v>
       </c>
-      <c r="F62" s="116" t="s">
+      <c r="F62" s="109" t="s">
         <v>432</v>
       </c>
-      <c r="G62" s="116" t="s">
+      <c r="G62" s="109" t="s">
         <v>433</v>
       </c>
-      <c r="H62" s="116" t="s">
+      <c r="H62" s="109" t="s">
         <v>434</v>
       </c>
-      <c r="I62" s="116" t="s">
+      <c r="I62" s="109" t="s">
         <v>435</v>
       </c>
-      <c r="J62" s="116" t="s">
+      <c r="J62" s="109" t="s">
         <v>436</v>
       </c>
-      <c r="K62" s="116" t="s">
+      <c r="K62" s="109" t="s">
         <v>437</v>
       </c>
-      <c r="L62" s="116" t="s">
+      <c r="L62" s="109" t="s">
         <v>438</v>
       </c>
-      <c r="M62" s="116" t="s">
+      <c r="M62" s="109" t="s">
         <v>439</v>
       </c>
-      <c r="N62" s="116" t="s">
+      <c r="N62" s="109" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A63" s="112"/>
-      <c r="B63" s="112"/>
-      <c r="C63" s="117">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A63" s="107"/>
+      <c r="B63" s="107"/>
+      <c r="C63" s="110">
         <v>65</v>
       </c>
-      <c r="D63" s="117">
+      <c r="D63" s="110">
         <v>69</v>
       </c>
-      <c r="E63" s="117">
+      <c r="E63" s="110">
         <v>73</v>
       </c>
-      <c r="F63" s="117">
+      <c r="F63" s="110">
         <v>78</v>
       </c>
-      <c r="G63" s="117">
+      <c r="G63" s="110">
         <v>82</v>
       </c>
-      <c r="H63" s="117">
+      <c r="H63" s="110">
         <v>87</v>
       </c>
-      <c r="I63" s="117">
+      <c r="I63" s="110">
         <v>93</v>
       </c>
-      <c r="J63" s="117">
+      <c r="J63" s="110">
         <v>98</v>
       </c>
-      <c r="K63" s="117">
+      <c r="K63" s="110">
         <v>104</v>
       </c>
-      <c r="L63" s="117">
+      <c r="L63" s="110">
         <v>110</v>
       </c>
-      <c r="M63" s="117">
+      <c r="M63" s="110">
         <v>117</v>
       </c>
-      <c r="N63" s="117">
+      <c r="N63" s="110">
         <v>123</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A64" s="112"/>
-      <c r="B64" s="112"/>
-      <c r="C64" s="112"/>
-      <c r="D64" s="112"/>
-      <c r="E64" s="112"/>
-      <c r="F64" s="112"/>
-      <c r="G64" s="112"/>
-      <c r="H64" s="112"/>
-      <c r="I64" s="112"/>
-      <c r="J64" s="112"/>
-      <c r="K64" s="112"/>
-      <c r="L64" s="112"/>
-      <c r="M64" s="112"/>
-      <c r="N64" s="112"/>
-    </row>
-    <row r="65" spans="1:14" ht="16.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="112"/>
-      <c r="B65" s="114" t="s">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A64" s="107"/>
+      <c r="B64" s="107"/>
+      <c r="C64" s="107"/>
+      <c r="D64" s="107"/>
+      <c r="E64" s="107"/>
+      <c r="F64" s="107"/>
+      <c r="G64" s="107"/>
+      <c r="H64" s="107"/>
+      <c r="I64" s="107"/>
+      <c r="J64" s="107"/>
+      <c r="K64" s="107"/>
+      <c r="L64" s="107"/>
+      <c r="M64" s="107"/>
+      <c r="N64" s="107"/>
+    </row>
+    <row r="65" spans="1:14" ht="16.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="107"/>
+      <c r="B65" s="119" t="s">
         <v>441</v>
       </c>
-      <c r="C65" s="114"/>
-      <c r="D65" s="114"/>
-      <c r="E65" s="114"/>
-      <c r="F65" s="114"/>
-      <c r="G65" s="114"/>
-      <c r="H65" s="114"/>
-      <c r="I65" s="114"/>
-      <c r="J65" s="114"/>
-      <c r="K65" s="114"/>
-      <c r="L65" s="114"/>
-      <c r="M65" s="114"/>
-      <c r="N65" s="114"/>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A66" s="112"/>
-      <c r="B66" s="112"/>
-      <c r="C66" s="112"/>
-      <c r="D66" s="112"/>
-      <c r="E66" s="112"/>
-      <c r="F66" s="112"/>
-      <c r="G66" s="112"/>
-      <c r="H66" s="112"/>
-      <c r="I66" s="112"/>
-      <c r="J66" s="112"/>
-      <c r="K66" s="112"/>
-      <c r="L66" s="112"/>
-      <c r="M66" s="112"/>
-      <c r="N66" s="112"/>
-    </row>
-    <row r="67" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="112"/>
-      <c r="B67" s="115"/>
-      <c r="C67" s="115"/>
-      <c r="D67" s="115"/>
-      <c r="E67" s="115"/>
-      <c r="F67" s="115"/>
-      <c r="G67" s="115"/>
-      <c r="H67" s="115"/>
-      <c r="I67" s="115"/>
-      <c r="J67" s="115"/>
-      <c r="K67" s="115"/>
-      <c r="L67" s="115"/>
-      <c r="M67" s="115"/>
-      <c r="N67" s="115"/>
-    </row>
-    <row r="68" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="112"/>
-      <c r="B68" s="115"/>
-      <c r="C68" s="115"/>
-      <c r="D68" s="115"/>
-      <c r="E68" s="115"/>
-      <c r="F68" s="115"/>
-      <c r="G68" s="115"/>
-      <c r="H68" s="115"/>
-      <c r="I68" s="115"/>
-      <c r="J68" s="115"/>
-      <c r="K68" s="115"/>
-      <c r="L68" s="115"/>
-      <c r="M68" s="115"/>
-      <c r="N68" s="115" t="s">
+      <c r="C65" s="119"/>
+      <c r="D65" s="119"/>
+      <c r="E65" s="119"/>
+      <c r="F65" s="119"/>
+      <c r="G65" s="119"/>
+      <c r="H65" s="119"/>
+      <c r="I65" s="119"/>
+      <c r="J65" s="119"/>
+      <c r="K65" s="119"/>
+      <c r="L65" s="119"/>
+      <c r="M65" s="119"/>
+      <c r="N65" s="119"/>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A66" s="107"/>
+      <c r="B66" s="107"/>
+      <c r="C66" s="107"/>
+      <c r="D66" s="107"/>
+      <c r="E66" s="107"/>
+      <c r="F66" s="107"/>
+      <c r="G66" s="107"/>
+      <c r="H66" s="107"/>
+      <c r="I66" s="107"/>
+      <c r="J66" s="107"/>
+      <c r="K66" s="107"/>
+      <c r="L66" s="107"/>
+      <c r="M66" s="107"/>
+      <c r="N66" s="107"/>
+    </row>
+    <row r="67" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="107"/>
+      <c r="B67" s="108"/>
+      <c r="C67" s="108"/>
+      <c r="D67" s="108"/>
+      <c r="E67" s="108"/>
+      <c r="F67" s="108"/>
+      <c r="G67" s="108"/>
+      <c r="H67" s="108"/>
+      <c r="I67" s="108"/>
+      <c r="J67" s="108"/>
+      <c r="K67" s="108"/>
+      <c r="L67" s="108"/>
+      <c r="M67" s="108"/>
+      <c r="N67" s="108"/>
+    </row>
+    <row r="68" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="107"/>
+      <c r="B68" s="108"/>
+      <c r="C68" s="108"/>
+      <c r="D68" s="108"/>
+      <c r="E68" s="108"/>
+      <c r="F68" s="108"/>
+      <c r="G68" s="108"/>
+      <c r="H68" s="108"/>
+      <c r="I68" s="108"/>
+      <c r="J68" s="108"/>
+      <c r="K68" s="108"/>
+      <c r="L68" s="108"/>
+      <c r="M68" s="108"/>
+      <c r="N68" s="108" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="112"/>
-      <c r="B69" s="115"/>
-      <c r="C69" s="120"/>
-      <c r="D69" s="120"/>
-      <c r="E69" s="120"/>
-      <c r="F69" s="120"/>
-      <c r="G69" s="120"/>
-      <c r="H69" s="120"/>
-      <c r="I69" s="120"/>
-      <c r="J69" s="120"/>
-      <c r="K69" s="120"/>
-      <c r="L69" s="120" t="s">
+    <row r="69" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="107"/>
+      <c r="B69" s="108"/>
+      <c r="C69" s="112"/>
+      <c r="D69" s="112"/>
+      <c r="E69" s="112"/>
+      <c r="F69" s="112"/>
+      <c r="G69" s="112"/>
+      <c r="H69" s="112"/>
+      <c r="I69" s="112"/>
+      <c r="J69" s="112"/>
+      <c r="K69" s="112"/>
+      <c r="L69" s="112" t="s">
         <v>411</v>
       </c>
-      <c r="M69" s="120" t="s">
+      <c r="M69" s="112" t="s">
         <v>414</v>
       </c>
-      <c r="N69" s="120"/>
-    </row>
-    <row r="70" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="112"/>
-      <c r="B70" s="115"/>
-      <c r="C70" s="115"/>
-      <c r="D70" s="115"/>
-      <c r="E70" s="115"/>
-      <c r="F70" s="115"/>
-      <c r="G70" s="115"/>
-      <c r="H70" s="115"/>
-      <c r="I70" s="115"/>
-      <c r="J70" s="115" t="s">
+      <c r="N69" s="112"/>
+    </row>
+    <row r="70" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="107"/>
+      <c r="B70" s="108"/>
+      <c r="C70" s="108"/>
+      <c r="D70" s="108"/>
+      <c r="E70" s="108"/>
+      <c r="F70" s="108"/>
+      <c r="G70" s="108"/>
+      <c r="H70" s="108"/>
+      <c r="I70" s="108"/>
+      <c r="J70" s="108" t="s">
         <v>411</v>
       </c>
-      <c r="K70" s="115" t="s">
+      <c r="K70" s="108" t="s">
         <v>414</v>
       </c>
-      <c r="L70" s="115"/>
-      <c r="M70" s="115"/>
-      <c r="N70" s="115"/>
-    </row>
-    <row r="71" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="112"/>
-      <c r="B71" s="115"/>
-      <c r="C71" s="120"/>
-      <c r="D71" s="120"/>
-      <c r="E71" s="120"/>
-      <c r="F71" s="120"/>
-      <c r="G71" s="120"/>
-      <c r="H71" s="120" t="s">
+      <c r="L70" s="108"/>
+      <c r="M70" s="108"/>
+      <c r="N70" s="108"/>
+    </row>
+    <row r="71" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="107"/>
+      <c r="B71" s="108"/>
+      <c r="C71" s="112"/>
+      <c r="D71" s="112"/>
+      <c r="E71" s="112"/>
+      <c r="F71" s="112"/>
+      <c r="G71" s="112"/>
+      <c r="H71" s="112" t="s">
         <v>411</v>
       </c>
-      <c r="I71" s="120" t="s">
+      <c r="I71" s="112" t="s">
         <v>414</v>
       </c>
-      <c r="J71" s="120"/>
-      <c r="K71" s="120"/>
-      <c r="L71" s="120"/>
-      <c r="M71" s="120"/>
-      <c r="N71" s="120"/>
-    </row>
-    <row r="72" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="112"/>
-      <c r="B72" s="115"/>
-      <c r="C72" s="115"/>
-      <c r="D72" s="115"/>
-      <c r="E72" s="115"/>
-      <c r="F72" s="115"/>
-      <c r="G72" s="115" t="s">
+      <c r="J71" s="112"/>
+      <c r="K71" s="112"/>
+      <c r="L71" s="112"/>
+      <c r="M71" s="112"/>
+      <c r="N71" s="112"/>
+    </row>
+    <row r="72" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="107"/>
+      <c r="B72" s="108"/>
+      <c r="C72" s="108"/>
+      <c r="D72" s="108"/>
+      <c r="E72" s="108"/>
+      <c r="F72" s="108"/>
+      <c r="G72" s="108" t="s">
         <v>411</v>
       </c>
-      <c r="H72" s="115"/>
-      <c r="I72" s="115"/>
-      <c r="J72" s="115"/>
-      <c r="K72" s="115"/>
-      <c r="L72" s="115"/>
-      <c r="M72" s="115"/>
-      <c r="N72" s="115"/>
-    </row>
-    <row r="73" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="112"/>
-      <c r="B73" s="115"/>
-      <c r="C73" s="120"/>
-      <c r="D73" s="120"/>
-      <c r="E73" s="120" t="s">
+      <c r="H72" s="108"/>
+      <c r="I72" s="108"/>
+      <c r="J72" s="108"/>
+      <c r="K72" s="108"/>
+      <c r="L72" s="108"/>
+      <c r="M72" s="108"/>
+      <c r="N72" s="108"/>
+    </row>
+    <row r="73" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="107"/>
+      <c r="B73" s="108"/>
+      <c r="C73" s="112"/>
+      <c r="D73" s="112"/>
+      <c r="E73" s="112" t="s">
         <v>411</v>
       </c>
-      <c r="F73" s="120" t="s">
+      <c r="F73" s="112" t="s">
         <v>414</v>
       </c>
-      <c r="G73" s="120"/>
-      <c r="H73" s="120"/>
-      <c r="I73" s="120"/>
-      <c r="J73" s="120"/>
-      <c r="K73" s="120"/>
-      <c r="L73" s="120"/>
-      <c r="M73" s="120"/>
-      <c r="N73" s="120"/>
-    </row>
-    <row r="74" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="112"/>
-      <c r="B74" s="115" t="s">
+      <c r="G73" s="112"/>
+      <c r="H73" s="112"/>
+      <c r="I73" s="112"/>
+      <c r="J73" s="112"/>
+      <c r="K73" s="112"/>
+      <c r="L73" s="112"/>
+      <c r="M73" s="112"/>
+      <c r="N73" s="112"/>
+    </row>
+    <row r="74" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="107"/>
+      <c r="B74" s="108" t="s">
         <v>428</v>
       </c>
-      <c r="C74" s="115" t="s">
+      <c r="C74" s="108" t="s">
         <v>411</v>
       </c>
-      <c r="D74" s="115" t="s">
+      <c r="D74" s="108" t="s">
         <v>414</v>
       </c>
-      <c r="E74" s="115"/>
-      <c r="F74" s="115"/>
-      <c r="G74" s="115"/>
-      <c r="H74" s="115"/>
-      <c r="I74" s="115"/>
-      <c r="J74" s="115"/>
-      <c r="K74" s="115"/>
-      <c r="L74" s="115"/>
-      <c r="M74" s="115"/>
-      <c r="N74" s="115"/>
-    </row>
-    <row r="75" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="112"/>
-      <c r="B75" s="115"/>
-      <c r="C75" s="120"/>
-      <c r="D75" s="120"/>
-      <c r="E75" s="120"/>
-      <c r="F75" s="120"/>
-      <c r="G75" s="120"/>
-      <c r="H75" s="120"/>
-      <c r="I75" s="120"/>
-      <c r="J75" s="120"/>
-      <c r="K75" s="120"/>
-      <c r="L75" s="120"/>
-      <c r="M75" s="120"/>
-      <c r="N75" s="120"/>
-    </row>
-    <row r="76" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="112"/>
-      <c r="B76" s="115"/>
-      <c r="C76" s="115"/>
-      <c r="D76" s="115"/>
-      <c r="E76" s="115"/>
-      <c r="F76" s="115"/>
-      <c r="G76" s="115"/>
-      <c r="H76" s="115"/>
-      <c r="I76" s="115"/>
-      <c r="J76" s="115"/>
-      <c r="K76" s="115"/>
-      <c r="L76" s="115"/>
-      <c r="M76" s="115"/>
-      <c r="N76" s="115"/>
-    </row>
-    <row r="77" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="112"/>
-      <c r="B77" s="115"/>
-      <c r="C77" s="120"/>
-      <c r="D77" s="120"/>
-      <c r="E77" s="120"/>
-      <c r="F77" s="120"/>
-      <c r="G77" s="120"/>
-      <c r="H77" s="120"/>
-      <c r="I77" s="120"/>
-      <c r="J77" s="120"/>
-      <c r="K77" s="120"/>
-      <c r="L77" s="120"/>
-      <c r="M77" s="120"/>
-      <c r="N77" s="120"/>
-    </row>
-    <row r="78" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="112"/>
-      <c r="B78" s="115"/>
-      <c r="C78" s="115"/>
-      <c r="D78" s="115"/>
-      <c r="E78" s="115"/>
-      <c r="F78" s="115"/>
-      <c r="G78" s="115"/>
-      <c r="H78" s="115"/>
-      <c r="I78" s="115"/>
-      <c r="J78" s="115"/>
-      <c r="K78" s="115"/>
-      <c r="L78" s="115"/>
-      <c r="M78" s="115"/>
-      <c r="N78" s="115"/>
-    </row>
-    <row r="79" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="112"/>
-      <c r="B79" s="115"/>
-      <c r="C79" s="115"/>
-      <c r="D79" s="115"/>
-      <c r="E79" s="115"/>
-      <c r="F79" s="115"/>
-      <c r="G79" s="115"/>
-      <c r="H79" s="115"/>
-      <c r="I79" s="115"/>
-      <c r="J79" s="115"/>
-      <c r="K79" s="115"/>
-      <c r="L79" s="115"/>
-      <c r="M79" s="115"/>
-      <c r="N79" s="115"/>
-    </row>
-    <row r="80" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="112"/>
-      <c r="B80" s="115"/>
-      <c r="C80" s="115"/>
-      <c r="D80" s="115"/>
-      <c r="E80" s="115"/>
-      <c r="F80" s="115"/>
-      <c r="G80" s="115"/>
-      <c r="H80" s="115"/>
-      <c r="I80" s="115"/>
-      <c r="J80" s="115"/>
-      <c r="K80" s="115"/>
-      <c r="L80" s="115"/>
-      <c r="M80" s="115"/>
-      <c r="N80" s="115"/>
-    </row>
-    <row r="81" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="112"/>
-      <c r="B81" s="115"/>
-      <c r="C81" s="115"/>
-      <c r="D81" s="115"/>
-      <c r="E81" s="115"/>
-      <c r="F81" s="115"/>
-      <c r="G81" s="115"/>
-      <c r="H81" s="115"/>
-      <c r="I81" s="115"/>
-      <c r="J81" s="115"/>
-      <c r="K81" s="115"/>
-      <c r="L81" s="115"/>
-      <c r="M81" s="115"/>
-      <c r="N81" s="115"/>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A82" s="112"/>
-      <c r="B82" s="112"/>
-      <c r="C82" s="116" t="s">
+      <c r="E74" s="108"/>
+      <c r="F74" s="108"/>
+      <c r="G74" s="108"/>
+      <c r="H74" s="108"/>
+      <c r="I74" s="108"/>
+      <c r="J74" s="108"/>
+      <c r="K74" s="108"/>
+      <c r="L74" s="108"/>
+      <c r="M74" s="108"/>
+      <c r="N74" s="108"/>
+    </row>
+    <row r="75" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="107"/>
+      <c r="B75" s="108"/>
+      <c r="C75" s="112"/>
+      <c r="D75" s="112"/>
+      <c r="E75" s="112"/>
+      <c r="F75" s="112"/>
+      <c r="G75" s="112"/>
+      <c r="H75" s="112"/>
+      <c r="I75" s="112"/>
+      <c r="J75" s="112"/>
+      <c r="K75" s="112"/>
+      <c r="L75" s="112"/>
+      <c r="M75" s="112"/>
+      <c r="N75" s="112"/>
+    </row>
+    <row r="76" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="107"/>
+      <c r="B76" s="108"/>
+      <c r="C76" s="108"/>
+      <c r="D76" s="108"/>
+      <c r="E76" s="108"/>
+      <c r="F76" s="108"/>
+      <c r="G76" s="108"/>
+      <c r="H76" s="108"/>
+      <c r="I76" s="108"/>
+      <c r="J76" s="108"/>
+      <c r="K76" s="108"/>
+      <c r="L76" s="108"/>
+      <c r="M76" s="108"/>
+      <c r="N76" s="108"/>
+    </row>
+    <row r="77" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="107"/>
+      <c r="B77" s="108"/>
+      <c r="C77" s="112"/>
+      <c r="D77" s="112"/>
+      <c r="E77" s="112"/>
+      <c r="F77" s="112"/>
+      <c r="G77" s="112"/>
+      <c r="H77" s="112"/>
+      <c r="I77" s="112"/>
+      <c r="J77" s="112"/>
+      <c r="K77" s="112"/>
+      <c r="L77" s="112"/>
+      <c r="M77" s="112"/>
+      <c r="N77" s="112"/>
+    </row>
+    <row r="78" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="107"/>
+      <c r="B78" s="108"/>
+      <c r="C78" s="108"/>
+      <c r="D78" s="108"/>
+      <c r="E78" s="108"/>
+      <c r="F78" s="108"/>
+      <c r="G78" s="108"/>
+      <c r="H78" s="108"/>
+      <c r="I78" s="108"/>
+      <c r="J78" s="108"/>
+      <c r="K78" s="108"/>
+      <c r="L78" s="108"/>
+      <c r="M78" s="108"/>
+      <c r="N78" s="108"/>
+    </row>
+    <row r="79" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="107"/>
+      <c r="B79" s="108"/>
+      <c r="C79" s="108"/>
+      <c r="D79" s="108"/>
+      <c r="E79" s="108"/>
+      <c r="F79" s="108"/>
+      <c r="G79" s="108"/>
+      <c r="H79" s="108"/>
+      <c r="I79" s="108"/>
+      <c r="J79" s="108"/>
+      <c r="K79" s="108"/>
+      <c r="L79" s="108"/>
+      <c r="M79" s="108"/>
+      <c r="N79" s="108"/>
+    </row>
+    <row r="80" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="107"/>
+      <c r="B80" s="108"/>
+      <c r="C80" s="108"/>
+      <c r="D80" s="108"/>
+      <c r="E80" s="108"/>
+      <c r="F80" s="108"/>
+      <c r="G80" s="108"/>
+      <c r="H80" s="108"/>
+      <c r="I80" s="108"/>
+      <c r="J80" s="108"/>
+      <c r="K80" s="108"/>
+      <c r="L80" s="108"/>
+      <c r="M80" s="108"/>
+      <c r="N80" s="108"/>
+    </row>
+    <row r="81" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="107"/>
+      <c r="B81" s="108"/>
+      <c r="C81" s="108"/>
+      <c r="D81" s="108"/>
+      <c r="E81" s="108"/>
+      <c r="F81" s="108"/>
+      <c r="G81" s="108"/>
+      <c r="H81" s="108"/>
+      <c r="I81" s="108"/>
+      <c r="J81" s="108"/>
+      <c r="K81" s="108"/>
+      <c r="L81" s="108"/>
+      <c r="M81" s="108"/>
+      <c r="N81" s="108"/>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A82" s="107"/>
+      <c r="B82" s="107"/>
+      <c r="C82" s="109" t="s">
         <v>442</v>
       </c>
-      <c r="D82" s="116" t="s">
+      <c r="D82" s="109" t="s">
         <v>443</v>
       </c>
-      <c r="E82" s="116" t="s">
+      <c r="E82" s="109" t="s">
         <v>444</v>
       </c>
-      <c r="F82" s="116" t="s">
+      <c r="F82" s="109" t="s">
         <v>445</v>
       </c>
-      <c r="G82" s="116" t="s">
+      <c r="G82" s="109" t="s">
         <v>446</v>
       </c>
-      <c r="H82" s="116" t="s">
+      <c r="H82" s="109" t="s">
         <v>447</v>
       </c>
-      <c r="I82" s="116" t="s">
+      <c r="I82" s="109" t="s">
         <v>448</v>
       </c>
-      <c r="J82" s="116" t="s">
+      <c r="J82" s="109" t="s">
         <v>449</v>
       </c>
-      <c r="K82" s="116" t="s">
+      <c r="K82" s="109" t="s">
         <v>450</v>
       </c>
-      <c r="L82" s="116" t="s">
+      <c r="L82" s="109" t="s">
         <v>451</v>
       </c>
-      <c r="M82" s="116" t="s">
+      <c r="M82" s="109" t="s">
         <v>452</v>
       </c>
-      <c r="N82" s="116" t="s">
+      <c r="N82" s="109" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A83" s="112"/>
-      <c r="B83" s="112"/>
-      <c r="C83" s="117">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A83" s="107"/>
+      <c r="B83" s="107"/>
+      <c r="C83" s="110">
         <v>131</v>
       </c>
-      <c r="D83" s="117">
+      <c r="D83" s="110">
         <v>139</v>
       </c>
-      <c r="E83" s="117">
+      <c r="E83" s="110">
         <v>147</v>
       </c>
-      <c r="F83" s="117">
+      <c r="F83" s="110">
         <v>156</v>
       </c>
-      <c r="G83" s="117">
+      <c r="G83" s="110">
         <v>165</v>
       </c>
-      <c r="H83" s="117">
+      <c r="H83" s="110">
         <v>175</v>
       </c>
-      <c r="I83" s="117">
+      <c r="I83" s="110">
         <v>185</v>
       </c>
-      <c r="J83" s="117">
+      <c r="J83" s="110">
         <v>196</v>
       </c>
-      <c r="K83" s="117">
+      <c r="K83" s="110">
         <v>208</v>
       </c>
-      <c r="L83" s="117">
+      <c r="L83" s="110">
         <v>220</v>
       </c>
-      <c r="M83" s="117">
+      <c r="M83" s="110">
         <v>233</v>
       </c>
-      <c r="N83" s="117">
+      <c r="N83" s="110">
         <v>247</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A84" s="112"/>
-      <c r="B84" s="112"/>
-      <c r="C84" s="112"/>
-      <c r="D84" s="112"/>
-      <c r="E84" s="112"/>
-      <c r="F84" s="112"/>
-      <c r="G84" s="112"/>
-      <c r="H84" s="112"/>
-      <c r="I84" s="112"/>
-      <c r="J84" s="112"/>
-      <c r="K84" s="112"/>
-      <c r="L84" s="112"/>
-      <c r="M84" s="112"/>
-      <c r="N84" s="112"/>
-    </row>
-    <row r="85" spans="1:14" ht="16.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="112"/>
-      <c r="B85" s="114" t="s">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A84" s="107"/>
+      <c r="B84" s="107"/>
+      <c r="C84" s="107"/>
+      <c r="D84" s="107"/>
+      <c r="E84" s="107"/>
+      <c r="F84" s="107"/>
+      <c r="G84" s="107"/>
+      <c r="H84" s="107"/>
+      <c r="I84" s="107"/>
+      <c r="J84" s="107"/>
+      <c r="K84" s="107"/>
+      <c r="L84" s="107"/>
+      <c r="M84" s="107"/>
+      <c r="N84" s="107"/>
+    </row>
+    <row r="85" spans="1:14" ht="16.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="107"/>
+      <c r="B85" s="119" t="s">
         <v>454</v>
       </c>
-      <c r="C85" s="114"/>
-      <c r="D85" s="114"/>
-      <c r="E85" s="114"/>
-      <c r="F85" s="114"/>
-      <c r="G85" s="114"/>
-      <c r="H85" s="114"/>
-      <c r="I85" s="114"/>
-      <c r="J85" s="114"/>
-      <c r="K85" s="114"/>
-      <c r="L85" s="114"/>
-      <c r="M85" s="114"/>
-      <c r="N85" s="114"/>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A86" s="112"/>
-      <c r="B86" s="112"/>
-      <c r="C86" s="112"/>
-      <c r="D86" s="112"/>
-      <c r="E86" s="112"/>
-      <c r="F86" s="112"/>
-      <c r="G86" s="112"/>
-      <c r="H86" s="112"/>
-      <c r="I86" s="112"/>
-      <c r="J86" s="112"/>
-      <c r="K86" s="112"/>
-      <c r="L86" s="112"/>
-      <c r="M86" s="112"/>
-      <c r="N86" s="112"/>
-    </row>
-    <row r="87" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A87" s="112"/>
-      <c r="B87" s="115"/>
-      <c r="C87" s="115"/>
-      <c r="D87" s="115"/>
-      <c r="E87" s="115"/>
-      <c r="F87" s="115"/>
-      <c r="G87" s="115"/>
-      <c r="H87" s="115"/>
-      <c r="I87" s="115"/>
-      <c r="J87" s="115"/>
-      <c r="K87" s="115"/>
-      <c r="L87" s="115"/>
-      <c r="M87" s="115"/>
-      <c r="N87" s="115"/>
-    </row>
-    <row r="88" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A88" s="112"/>
-      <c r="B88" s="115"/>
-      <c r="C88" s="115"/>
-      <c r="D88" s="115"/>
-      <c r="E88" s="115"/>
-      <c r="F88" s="115"/>
-      <c r="G88" s="115"/>
-      <c r="H88" s="115"/>
-      <c r="I88" s="115"/>
-      <c r="J88" s="115"/>
-      <c r="K88" s="115"/>
-      <c r="L88" s="115"/>
-      <c r="M88" s="115"/>
-      <c r="N88" s="115"/>
-    </row>
-    <row r="89" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A89" s="112"/>
-      <c r="B89" s="115"/>
-      <c r="C89" s="115"/>
-      <c r="D89" s="115"/>
-      <c r="E89" s="115"/>
-      <c r="F89" s="115"/>
-      <c r="G89" s="115"/>
-      <c r="H89" s="115"/>
-      <c r="I89" s="115"/>
-      <c r="J89" s="115"/>
-      <c r="K89" s="115"/>
-      <c r="L89" s="115"/>
-      <c r="M89" s="115"/>
-      <c r="N89" s="115"/>
-    </row>
-    <row r="90" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A90" s="112"/>
-      <c r="B90" s="115"/>
-      <c r="C90" s="115"/>
-      <c r="D90" s="115"/>
-      <c r="E90" s="115"/>
-      <c r="F90" s="115"/>
-      <c r="G90" s="115"/>
-      <c r="H90" s="115"/>
-      <c r="I90" s="115"/>
-      <c r="J90" s="115"/>
-      <c r="K90" s="115"/>
-      <c r="L90" s="115"/>
-      <c r="M90" s="115"/>
-      <c r="N90" s="115"/>
-    </row>
-    <row r="91" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="112"/>
-      <c r="B91" s="115"/>
-      <c r="C91" s="120"/>
-      <c r="D91" s="120"/>
-      <c r="E91" s="120"/>
-      <c r="F91" s="120"/>
-      <c r="G91" s="120"/>
-      <c r="H91" s="120"/>
-      <c r="I91" s="120"/>
-      <c r="J91" s="120"/>
-      <c r="K91" s="120"/>
-      <c r="L91" s="120"/>
-      <c r="M91" s="120"/>
-      <c r="N91" s="120"/>
-    </row>
-    <row r="92" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A92" s="112"/>
-      <c r="B92" s="115"/>
-      <c r="C92" s="115"/>
-      <c r="D92" s="115"/>
-      <c r="E92" s="115"/>
-      <c r="F92" s="115"/>
-      <c r="G92" s="115"/>
-      <c r="H92" s="115"/>
-      <c r="I92" s="115"/>
-      <c r="J92" s="115"/>
-      <c r="K92" s="115"/>
-      <c r="L92" s="115"/>
-      <c r="M92" s="115"/>
-      <c r="N92" s="115"/>
-    </row>
-    <row r="93" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A93" s="112"/>
-      <c r="B93" s="115"/>
-      <c r="C93" s="120"/>
-      <c r="D93" s="120"/>
-      <c r="E93" s="120"/>
-      <c r="F93" s="120"/>
-      <c r="G93" s="120"/>
-      <c r="H93" s="120"/>
-      <c r="I93" s="120"/>
-      <c r="J93" s="120"/>
-      <c r="K93" s="120"/>
-      <c r="L93" s="120"/>
-      <c r="M93" s="120"/>
-      <c r="N93" s="120"/>
-    </row>
-    <row r="94" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A94" s="112"/>
-      <c r="B94" s="115" t="s">
+      <c r="C85" s="119"/>
+      <c r="D85" s="119"/>
+      <c r="E85" s="119"/>
+      <c r="F85" s="119"/>
+      <c r="G85" s="119"/>
+      <c r="H85" s="119"/>
+      <c r="I85" s="119"/>
+      <c r="J85" s="119"/>
+      <c r="K85" s="119"/>
+      <c r="L85" s="119"/>
+      <c r="M85" s="119"/>
+      <c r="N85" s="119"/>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A86" s="107"/>
+      <c r="B86" s="107"/>
+      <c r="C86" s="107"/>
+      <c r="D86" s="107"/>
+      <c r="E86" s="107"/>
+      <c r="F86" s="107"/>
+      <c r="G86" s="107"/>
+      <c r="H86" s="107"/>
+      <c r="I86" s="107"/>
+      <c r="J86" s="107"/>
+      <c r="K86" s="107"/>
+      <c r="L86" s="107"/>
+      <c r="M86" s="107"/>
+      <c r="N86" s="107"/>
+    </row>
+    <row r="87" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="107"/>
+      <c r="B87" s="108"/>
+      <c r="C87" s="108"/>
+      <c r="D87" s="108"/>
+      <c r="E87" s="108"/>
+      <c r="F87" s="108"/>
+      <c r="G87" s="108"/>
+      <c r="H87" s="108"/>
+      <c r="I87" s="108"/>
+      <c r="J87" s="108"/>
+      <c r="K87" s="108"/>
+      <c r="L87" s="108"/>
+      <c r="M87" s="108"/>
+      <c r="N87" s="108"/>
+    </row>
+    <row r="88" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="107"/>
+      <c r="B88" s="108"/>
+      <c r="C88" s="108"/>
+      <c r="D88" s="108"/>
+      <c r="E88" s="108"/>
+      <c r="F88" s="108"/>
+      <c r="G88" s="108"/>
+      <c r="H88" s="108"/>
+      <c r="I88" s="108"/>
+      <c r="J88" s="108"/>
+      <c r="K88" s="108"/>
+      <c r="L88" s="108"/>
+      <c r="M88" s="108"/>
+      <c r="N88" s="108"/>
+    </row>
+    <row r="89" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="107"/>
+      <c r="B89" s="108"/>
+      <c r="C89" s="108"/>
+      <c r="D89" s="108"/>
+      <c r="E89" s="108"/>
+      <c r="F89" s="108"/>
+      <c r="G89" s="108"/>
+      <c r="H89" s="108"/>
+      <c r="I89" s="108"/>
+      <c r="J89" s="108"/>
+      <c r="K89" s="108"/>
+      <c r="L89" s="108"/>
+      <c r="M89" s="108"/>
+      <c r="N89" s="108"/>
+    </row>
+    <row r="90" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="107"/>
+      <c r="B90" s="108"/>
+      <c r="C90" s="108"/>
+      <c r="D90" s="108"/>
+      <c r="E90" s="108"/>
+      <c r="F90" s="108"/>
+      <c r="G90" s="108"/>
+      <c r="H90" s="108"/>
+      <c r="I90" s="108"/>
+      <c r="J90" s="108"/>
+      <c r="K90" s="108"/>
+      <c r="L90" s="108"/>
+      <c r="M90" s="108"/>
+      <c r="N90" s="108"/>
+    </row>
+    <row r="91" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="107"/>
+      <c r="B91" s="108"/>
+      <c r="C91" s="112"/>
+      <c r="D91" s="112"/>
+      <c r="E91" s="112"/>
+      <c r="F91" s="112"/>
+      <c r="G91" s="112"/>
+      <c r="H91" s="112"/>
+      <c r="I91" s="112"/>
+      <c r="J91" s="112"/>
+      <c r="K91" s="112"/>
+      <c r="L91" s="112"/>
+      <c r="M91" s="112"/>
+      <c r="N91" s="112"/>
+    </row>
+    <row r="92" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="107"/>
+      <c r="B92" s="108"/>
+      <c r="C92" s="108"/>
+      <c r="D92" s="108"/>
+      <c r="E92" s="108"/>
+      <c r="F92" s="108"/>
+      <c r="G92" s="108"/>
+      <c r="H92" s="108"/>
+      <c r="I92" s="108"/>
+      <c r="J92" s="108"/>
+      <c r="K92" s="108"/>
+      <c r="L92" s="108"/>
+      <c r="M92" s="108"/>
+      <c r="N92" s="108"/>
+    </row>
+    <row r="93" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="107"/>
+      <c r="B93" s="108"/>
+      <c r="C93" s="112"/>
+      <c r="D93" s="112"/>
+      <c r="E93" s="112"/>
+      <c r="F93" s="112"/>
+      <c r="G93" s="112"/>
+      <c r="H93" s="112"/>
+      <c r="I93" s="112"/>
+      <c r="J93" s="112"/>
+      <c r="K93" s="112"/>
+      <c r="L93" s="112"/>
+      <c r="M93" s="112"/>
+      <c r="N93" s="112"/>
+    </row>
+    <row r="94" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="107"/>
+      <c r="B94" s="108" t="s">
         <v>455</v>
       </c>
-      <c r="C94" s="115"/>
-      <c r="D94" s="115"/>
-      <c r="E94" s="115"/>
-      <c r="F94" s="115"/>
-      <c r="G94" s="115"/>
-      <c r="H94" s="115"/>
-      <c r="I94" s="115"/>
-      <c r="J94" s="115"/>
-      <c r="K94" s="115"/>
-      <c r="L94" s="115"/>
-      <c r="M94" s="115"/>
-      <c r="N94" s="115"/>
-    </row>
-    <row r="95" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A95" s="112"/>
-      <c r="B95" s="115"/>
-      <c r="C95" s="120"/>
-      <c r="D95" s="120"/>
-      <c r="E95" s="120"/>
-      <c r="F95" s="120"/>
-      <c r="G95" s="120"/>
-      <c r="H95" s="120"/>
-      <c r="I95" s="120"/>
-      <c r="J95" s="120"/>
-      <c r="K95" s="120"/>
-      <c r="L95" s="120"/>
-      <c r="M95" s="120"/>
-      <c r="N95" s="120" t="s">
+      <c r="C94" s="108"/>
+      <c r="D94" s="108"/>
+      <c r="E94" s="108"/>
+      <c r="F94" s="108"/>
+      <c r="G94" s="108"/>
+      <c r="H94" s="108"/>
+      <c r="I94" s="108"/>
+      <c r="J94" s="108"/>
+      <c r="K94" s="108"/>
+      <c r="L94" s="108"/>
+      <c r="M94" s="108"/>
+      <c r="N94" s="108"/>
+    </row>
+    <row r="95" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="107"/>
+      <c r="B95" s="108"/>
+      <c r="C95" s="112"/>
+      <c r="D95" s="112"/>
+      <c r="E95" s="112"/>
+      <c r="F95" s="112"/>
+      <c r="G95" s="112"/>
+      <c r="H95" s="112"/>
+      <c r="I95" s="112"/>
+      <c r="J95" s="112"/>
+      <c r="K95" s="112"/>
+      <c r="L95" s="112"/>
+      <c r="M95" s="112"/>
+      <c r="N95" s="112" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="96" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="112"/>
-      <c r="B96" s="115"/>
-      <c r="C96" s="115"/>
-      <c r="D96" s="115"/>
-      <c r="E96" s="115"/>
-      <c r="F96" s="115"/>
-      <c r="G96" s="115"/>
-      <c r="H96" s="115"/>
-      <c r="I96" s="115"/>
-      <c r="J96" s="115"/>
-      <c r="K96" s="115"/>
-      <c r="L96" s="115" t="s">
+    <row r="96" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="107"/>
+      <c r="B96" s="108"/>
+      <c r="C96" s="108"/>
+      <c r="D96" s="108"/>
+      <c r="E96" s="108"/>
+      <c r="F96" s="108"/>
+      <c r="G96" s="108"/>
+      <c r="H96" s="108"/>
+      <c r="I96" s="108"/>
+      <c r="J96" s="108"/>
+      <c r="K96" s="108"/>
+      <c r="L96" s="108" t="s">
         <v>411</v>
       </c>
-      <c r="M96" s="115" t="s">
+      <c r="M96" s="108" t="s">
         <v>414</v>
       </c>
-      <c r="N96" s="115"/>
-    </row>
-    <row r="97" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A97" s="112"/>
-      <c r="B97" s="115"/>
-      <c r="C97" s="120"/>
-      <c r="D97" s="120"/>
-      <c r="E97" s="120"/>
-      <c r="F97" s="120"/>
-      <c r="G97" s="120"/>
-      <c r="H97" s="120"/>
-      <c r="I97" s="120"/>
-      <c r="J97" s="120" t="s">
+      <c r="N96" s="108"/>
+    </row>
+    <row r="97" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="107"/>
+      <c r="B97" s="108"/>
+      <c r="C97" s="112"/>
+      <c r="D97" s="112"/>
+      <c r="E97" s="112"/>
+      <c r="F97" s="112"/>
+      <c r="G97" s="112"/>
+      <c r="H97" s="112"/>
+      <c r="I97" s="112"/>
+      <c r="J97" s="112" t="s">
         <v>411</v>
       </c>
-      <c r="K97" s="120" t="s">
+      <c r="K97" s="112" t="s">
         <v>414</v>
       </c>
-      <c r="L97" s="120"/>
-      <c r="M97" s="120"/>
-      <c r="N97" s="120"/>
-    </row>
-    <row r="98" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A98" s="112"/>
-      <c r="B98" s="115"/>
-      <c r="C98" s="115"/>
-      <c r="D98" s="115"/>
-      <c r="E98" s="115"/>
-      <c r="F98" s="115"/>
-      <c r="G98" s="115"/>
-      <c r="H98" s="115" t="s">
+      <c r="L97" s="112"/>
+      <c r="M97" s="112"/>
+      <c r="N97" s="112"/>
+    </row>
+    <row r="98" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="107"/>
+      <c r="B98" s="108"/>
+      <c r="C98" s="108"/>
+      <c r="D98" s="108"/>
+      <c r="E98" s="108"/>
+      <c r="F98" s="108"/>
+      <c r="G98" s="108"/>
+      <c r="H98" s="108" t="s">
         <v>411</v>
       </c>
-      <c r="I98" s="115" t="s">
+      <c r="I98" s="108" t="s">
         <v>414</v>
       </c>
-      <c r="J98" s="115"/>
-      <c r="K98" s="115"/>
-      <c r="L98" s="115"/>
-      <c r="M98" s="115"/>
-      <c r="N98" s="115"/>
-    </row>
-    <row r="99" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A99" s="112"/>
-      <c r="B99" s="115"/>
-      <c r="C99" s="120"/>
-      <c r="D99" s="120"/>
-      <c r="E99" s="120"/>
-      <c r="F99" s="120"/>
-      <c r="G99" s="120" t="s">
+      <c r="J98" s="108"/>
+      <c r="K98" s="108"/>
+      <c r="L98" s="108"/>
+      <c r="M98" s="108"/>
+      <c r="N98" s="108"/>
+    </row>
+    <row r="99" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="107"/>
+      <c r="B99" s="108"/>
+      <c r="C99" s="112"/>
+      <c r="D99" s="112"/>
+      <c r="E99" s="112"/>
+      <c r="F99" s="112"/>
+      <c r="G99" s="112" t="s">
         <v>411</v>
       </c>
-      <c r="H99" s="120"/>
-      <c r="I99" s="120"/>
-      <c r="J99" s="120"/>
-      <c r="K99" s="120"/>
-      <c r="L99" s="120"/>
-      <c r="M99" s="120"/>
-      <c r="N99" s="120"/>
-    </row>
-    <row r="100" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A100" s="112"/>
-      <c r="B100" s="115"/>
-      <c r="C100" s="115"/>
-      <c r="D100" s="115"/>
-      <c r="E100" s="115" t="s">
+      <c r="H99" s="112"/>
+      <c r="I99" s="112"/>
+      <c r="J99" s="112"/>
+      <c r="K99" s="112"/>
+      <c r="L99" s="112"/>
+      <c r="M99" s="112"/>
+      <c r="N99" s="112"/>
+    </row>
+    <row r="100" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="107"/>
+      <c r="B100" s="108"/>
+      <c r="C100" s="108"/>
+      <c r="D100" s="108"/>
+      <c r="E100" s="108" t="s">
         <v>411</v>
       </c>
-      <c r="F100" s="115" t="s">
+      <c r="F100" s="108" t="s">
         <v>414</v>
       </c>
-      <c r="G100" s="115"/>
-      <c r="H100" s="115"/>
-      <c r="I100" s="115"/>
-      <c r="J100" s="115"/>
-      <c r="K100" s="115"/>
-      <c r="L100" s="115"/>
-      <c r="M100" s="115"/>
-      <c r="N100" s="115"/>
-    </row>
-    <row r="101" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A101" s="112"/>
-      <c r="B101" s="115"/>
-      <c r="C101" s="120" t="s">
+      <c r="G100" s="108"/>
+      <c r="H100" s="108"/>
+      <c r="I100" s="108"/>
+      <c r="J100" s="108"/>
+      <c r="K100" s="108"/>
+      <c r="L100" s="108"/>
+      <c r="M100" s="108"/>
+      <c r="N100" s="108"/>
+    </row>
+    <row r="101" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="107"/>
+      <c r="B101" s="108"/>
+      <c r="C101" s="112" t="s">
         <v>411</v>
       </c>
-      <c r="D101" s="120" t="s">
+      <c r="D101" s="112" t="s">
         <v>414</v>
       </c>
-      <c r="E101" s="115"/>
-      <c r="F101" s="115"/>
-      <c r="G101" s="115"/>
-      <c r="H101" s="115"/>
-      <c r="I101" s="115"/>
-      <c r="J101" s="115"/>
-      <c r="K101" s="115"/>
-      <c r="L101" s="115"/>
-      <c r="M101" s="115"/>
-      <c r="N101" s="115"/>
-    </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A102" s="112"/>
-      <c r="B102" s="112"/>
-      <c r="C102" s="116" t="s">
+      <c r="E101" s="108"/>
+      <c r="F101" s="108"/>
+      <c r="G101" s="108"/>
+      <c r="H101" s="108"/>
+      <c r="I101" s="108"/>
+      <c r="J101" s="108"/>
+      <c r="K101" s="108"/>
+      <c r="L101" s="108"/>
+      <c r="M101" s="108"/>
+      <c r="N101" s="108"/>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A102" s="107"/>
+      <c r="B102" s="107"/>
+      <c r="C102" s="109" t="s">
         <v>456</v>
       </c>
-      <c r="D102" s="116" t="s">
+      <c r="D102" s="109" t="s">
         <v>457</v>
       </c>
-      <c r="E102" s="116" t="s">
+      <c r="E102" s="109" t="s">
         <v>458</v>
       </c>
-      <c r="F102" s="116" t="s">
+      <c r="F102" s="109" t="s">
         <v>459</v>
       </c>
-      <c r="G102" s="116" t="s">
+      <c r="G102" s="109" t="s">
         <v>460</v>
       </c>
-      <c r="H102" s="116" t="s">
+      <c r="H102" s="109" t="s">
         <v>461</v>
       </c>
-      <c r="I102" s="116" t="s">
+      <c r="I102" s="109" t="s">
         <v>462</v>
       </c>
-      <c r="J102" s="116" t="s">
+      <c r="J102" s="109" t="s">
         <v>463</v>
       </c>
-      <c r="K102" s="116" t="s">
+      <c r="K102" s="109" t="s">
         <v>464</v>
       </c>
-      <c r="L102" s="116" t="s">
+      <c r="L102" s="109" t="s">
         <v>465</v>
       </c>
-      <c r="M102" s="116" t="s">
+      <c r="M102" s="109" t="s">
         <v>466</v>
       </c>
-      <c r="N102" s="116" t="s">
+      <c r="N102" s="109" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A103" s="112"/>
-      <c r="B103" s="112"/>
-      <c r="C103" s="117">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A103" s="107"/>
+      <c r="B103" s="107"/>
+      <c r="C103" s="110">
         <v>262</v>
       </c>
-      <c r="D103" s="117">
+      <c r="D103" s="110">
         <v>277</v>
       </c>
-      <c r="E103" s="117">
+      <c r="E103" s="110">
         <v>294</v>
       </c>
-      <c r="F103" s="117">
+      <c r="F103" s="110">
         <v>311</v>
       </c>
-      <c r="G103" s="117">
+      <c r="G103" s="110">
         <v>330</v>
       </c>
-      <c r="H103" s="117">
+      <c r="H103" s="110">
         <v>349</v>
       </c>
-      <c r="I103" s="117">
+      <c r="I103" s="110">
         <v>370</v>
       </c>
-      <c r="J103" s="117">
+      <c r="J103" s="110">
         <v>392</v>
       </c>
-      <c r="K103" s="117">
+      <c r="K103" s="110">
         <v>415</v>
       </c>
-      <c r="L103" s="117">
+      <c r="L103" s="110">
         <v>440</v>
       </c>
-      <c r="M103" s="117">
+      <c r="M103" s="110">
         <v>466</v>
       </c>
-      <c r="N103" s="117">
+      <c r="N103" s="110">
         <v>494</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A104" s="112"/>
-      <c r="B104" s="112"/>
-      <c r="C104" s="112"/>
-      <c r="D104" s="112"/>
-      <c r="E104" s="112"/>
-      <c r="F104" s="112"/>
-      <c r="G104" s="112"/>
-      <c r="H104" s="112"/>
-      <c r="I104" s="112"/>
-      <c r="J104" s="112"/>
-      <c r="K104" s="112"/>
-      <c r="L104" s="112"/>
-      <c r="M104" s="112"/>
-      <c r="N104" s="112"/>
-    </row>
-    <row r="105" spans="1:14" ht="16.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A105" s="112"/>
-      <c r="B105" s="114" t="s">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A104" s="107"/>
+      <c r="B104" s="107"/>
+      <c r="C104" s="107"/>
+      <c r="D104" s="107"/>
+      <c r="E104" s="107"/>
+      <c r="F104" s="107"/>
+      <c r="G104" s="107"/>
+      <c r="H104" s="107"/>
+      <c r="I104" s="107"/>
+      <c r="J104" s="107"/>
+      <c r="K104" s="107"/>
+      <c r="L104" s="107"/>
+      <c r="M104" s="107"/>
+      <c r="N104" s="107"/>
+    </row>
+    <row r="105" spans="1:14" ht="16.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="107"/>
+      <c r="B105" s="119" t="s">
         <v>468</v>
       </c>
-      <c r="C105" s="114"/>
-      <c r="D105" s="114"/>
-      <c r="E105" s="114"/>
-      <c r="F105" s="114"/>
-      <c r="G105" s="114"/>
-      <c r="H105" s="114"/>
-      <c r="I105" s="114"/>
-      <c r="J105" s="114"/>
-      <c r="K105" s="114"/>
-      <c r="L105" s="114"/>
-      <c r="M105" s="114"/>
-      <c r="N105" s="114"/>
-    </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A106" s="112"/>
-      <c r="B106" s="112"/>
-      <c r="C106" s="112"/>
-      <c r="D106" s="112"/>
-      <c r="E106" s="112"/>
-      <c r="F106" s="112"/>
-      <c r="G106" s="112"/>
-      <c r="H106" s="112"/>
-      <c r="I106" s="112"/>
-      <c r="J106" s="112"/>
-      <c r="K106" s="112"/>
-      <c r="L106" s="112"/>
-      <c r="M106" s="112"/>
-      <c r="N106" s="112"/>
-    </row>
-    <row r="107" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A107" s="112"/>
-      <c r="B107" s="115"/>
-      <c r="C107" s="115"/>
-      <c r="D107" s="115"/>
-      <c r="E107" s="115"/>
-      <c r="F107" s="115"/>
-      <c r="G107" s="115"/>
-      <c r="H107" s="115"/>
-      <c r="I107" s="115"/>
-      <c r="J107" s="115"/>
-      <c r="K107" s="115"/>
-      <c r="L107" s="115"/>
-      <c r="M107" s="115"/>
-      <c r="N107" s="115"/>
-    </row>
-    <row r="108" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A108" s="112"/>
-      <c r="B108" s="115"/>
-      <c r="C108" s="115"/>
-      <c r="D108" s="115"/>
-      <c r="E108" s="115"/>
-      <c r="F108" s="115"/>
-      <c r="G108" s="115"/>
-      <c r="H108" s="115"/>
-      <c r="I108" s="115"/>
-      <c r="J108" s="115"/>
-      <c r="K108" s="115"/>
-      <c r="L108" s="115"/>
-      <c r="M108" s="115"/>
-      <c r="N108" s="115" t="s">
+      <c r="C105" s="119"/>
+      <c r="D105" s="119"/>
+      <c r="E105" s="119"/>
+      <c r="F105" s="119"/>
+      <c r="G105" s="119"/>
+      <c r="H105" s="119"/>
+      <c r="I105" s="119"/>
+      <c r="J105" s="119"/>
+      <c r="K105" s="119"/>
+      <c r="L105" s="119"/>
+      <c r="M105" s="119"/>
+      <c r="N105" s="119"/>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A106" s="107"/>
+      <c r="B106" s="107"/>
+      <c r="C106" s="107"/>
+      <c r="D106" s="107"/>
+      <c r="E106" s="107"/>
+      <c r="F106" s="107"/>
+      <c r="G106" s="107"/>
+      <c r="H106" s="107"/>
+      <c r="I106" s="107"/>
+      <c r="J106" s="107"/>
+      <c r="K106" s="107"/>
+      <c r="L106" s="107"/>
+      <c r="M106" s="107"/>
+      <c r="N106" s="107"/>
+    </row>
+    <row r="107" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="107"/>
+      <c r="B107" s="108"/>
+      <c r="C107" s="108"/>
+      <c r="D107" s="108"/>
+      <c r="E107" s="108"/>
+      <c r="F107" s="108"/>
+      <c r="G107" s="108"/>
+      <c r="H107" s="108"/>
+      <c r="I107" s="108"/>
+      <c r="J107" s="108"/>
+      <c r="K107" s="108"/>
+      <c r="L107" s="108"/>
+      <c r="M107" s="108"/>
+      <c r="N107" s="108"/>
+    </row>
+    <row r="108" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="107"/>
+      <c r="B108" s="108"/>
+      <c r="C108" s="108"/>
+      <c r="D108" s="108"/>
+      <c r="E108" s="108"/>
+      <c r="F108" s="108"/>
+      <c r="G108" s="108"/>
+      <c r="H108" s="108"/>
+      <c r="I108" s="108"/>
+      <c r="J108" s="108"/>
+      <c r="K108" s="108"/>
+      <c r="L108" s="108"/>
+      <c r="M108" s="108"/>
+      <c r="N108" s="108" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="109" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A109" s="112"/>
-      <c r="B109" s="115"/>
-      <c r="C109" s="115"/>
-      <c r="D109" s="115"/>
-      <c r="E109" s="115"/>
-      <c r="F109" s="115"/>
-      <c r="G109" s="115"/>
-      <c r="H109" s="115"/>
-      <c r="I109" s="115"/>
-      <c r="J109" s="115"/>
-      <c r="K109" s="115"/>
-      <c r="L109" s="120" t="s">
+    <row r="109" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="107"/>
+      <c r="B109" s="108"/>
+      <c r="C109" s="108"/>
+      <c r="D109" s="108"/>
+      <c r="E109" s="108"/>
+      <c r="F109" s="108"/>
+      <c r="G109" s="108"/>
+      <c r="H109" s="108"/>
+      <c r="I109" s="108"/>
+      <c r="J109" s="108"/>
+      <c r="K109" s="108"/>
+      <c r="L109" s="112" t="s">
         <v>411</v>
       </c>
-      <c r="M109" s="120" t="s">
+      <c r="M109" s="112" t="s">
         <v>414</v>
       </c>
-      <c r="N109" s="115"/>
-    </row>
-    <row r="110" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A110" s="112"/>
-      <c r="B110" s="115"/>
-      <c r="C110" s="115"/>
-      <c r="D110" s="115"/>
-      <c r="E110" s="115"/>
-      <c r="F110" s="115"/>
-      <c r="G110" s="115"/>
-      <c r="H110" s="115"/>
-      <c r="I110" s="115"/>
-      <c r="J110" s="115" t="s">
+      <c r="N109" s="108"/>
+    </row>
+    <row r="110" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="107"/>
+      <c r="B110" s="108"/>
+      <c r="C110" s="108"/>
+      <c r="D110" s="108"/>
+      <c r="E110" s="108"/>
+      <c r="F110" s="108"/>
+      <c r="G110" s="108"/>
+      <c r="H110" s="108"/>
+      <c r="I110" s="108"/>
+      <c r="J110" s="108" t="s">
         <v>411</v>
       </c>
-      <c r="K110" s="115" t="s">
+      <c r="K110" s="108" t="s">
         <v>414</v>
       </c>
-      <c r="L110" s="115"/>
-      <c r="M110" s="115"/>
-      <c r="N110" s="115"/>
-    </row>
-    <row r="111" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A111" s="112"/>
-      <c r="B111" s="115"/>
-      <c r="C111" s="120"/>
-      <c r="D111" s="120"/>
-      <c r="E111" s="120"/>
-      <c r="F111" s="120"/>
-      <c r="G111" s="120"/>
-      <c r="H111" s="120" t="s">
+      <c r="L110" s="108"/>
+      <c r="M110" s="108"/>
+      <c r="N110" s="108"/>
+    </row>
+    <row r="111" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="107"/>
+      <c r="B111" s="108"/>
+      <c r="C111" s="112"/>
+      <c r="D111" s="112"/>
+      <c r="E111" s="112"/>
+      <c r="F111" s="112"/>
+      <c r="G111" s="112"/>
+      <c r="H111" s="112" t="s">
         <v>411</v>
       </c>
-      <c r="I111" s="120" t="s">
+      <c r="I111" s="112" t="s">
         <v>414</v>
       </c>
-      <c r="J111" s="120"/>
-      <c r="K111" s="120"/>
-      <c r="L111" s="120"/>
-      <c r="M111" s="120"/>
-      <c r="N111" s="120"/>
-    </row>
-    <row r="112" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A112" s="112"/>
-      <c r="B112" s="115"/>
-      <c r="C112" s="115"/>
-      <c r="D112" s="115"/>
-      <c r="E112" s="115"/>
-      <c r="F112" s="115"/>
-      <c r="G112" s="115" t="s">
+      <c r="J111" s="112"/>
+      <c r="K111" s="112"/>
+      <c r="L111" s="112"/>
+      <c r="M111" s="112"/>
+      <c r="N111" s="112"/>
+    </row>
+    <row r="112" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="107"/>
+      <c r="B112" s="108"/>
+      <c r="C112" s="108"/>
+      <c r="D112" s="108"/>
+      <c r="E112" s="108"/>
+      <c r="F112" s="108"/>
+      <c r="G112" s="108" t="s">
         <v>411</v>
       </c>
-      <c r="H112" s="115"/>
-      <c r="I112" s="115"/>
-      <c r="J112" s="115"/>
-      <c r="K112" s="115"/>
-      <c r="L112" s="115"/>
-      <c r="M112" s="115"/>
-      <c r="N112" s="115"/>
-    </row>
-    <row r="113" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A113" s="112"/>
-      <c r="B113" s="115"/>
-      <c r="C113" s="120"/>
-      <c r="D113" s="120"/>
-      <c r="E113" s="120" t="s">
+      <c r="H112" s="108"/>
+      <c r="I112" s="108"/>
+      <c r="J112" s="108"/>
+      <c r="K112" s="108"/>
+      <c r="L112" s="108"/>
+      <c r="M112" s="108"/>
+      <c r="N112" s="108"/>
+    </row>
+    <row r="113" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="107"/>
+      <c r="B113" s="108"/>
+      <c r="C113" s="112"/>
+      <c r="D113" s="112"/>
+      <c r="E113" s="112" t="s">
         <v>411</v>
       </c>
-      <c r="F113" s="120" t="s">
+      <c r="F113" s="112" t="s">
         <v>414</v>
       </c>
-      <c r="G113" s="120"/>
-      <c r="H113" s="120"/>
-      <c r="I113" s="120"/>
-      <c r="J113" s="120"/>
-      <c r="K113" s="120"/>
-      <c r="L113" s="120"/>
-      <c r="M113" s="120"/>
-      <c r="N113" s="120"/>
-    </row>
-    <row r="114" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A114" s="112"/>
-      <c r="B114" s="115" t="s">
+      <c r="G113" s="112"/>
+      <c r="H113" s="112"/>
+      <c r="I113" s="112"/>
+      <c r="J113" s="112"/>
+      <c r="K113" s="112"/>
+      <c r="L113" s="112"/>
+      <c r="M113" s="112"/>
+      <c r="N113" s="112"/>
+    </row>
+    <row r="114" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="107"/>
+      <c r="B114" s="108" t="s">
         <v>455</v>
       </c>
-      <c r="C114" s="115" t="s">
+      <c r="C114" s="108" t="s">
         <v>411</v>
       </c>
-      <c r="D114" s="115" t="s">
+      <c r="D114" s="108" t="s">
         <v>414</v>
       </c>
-      <c r="E114" s="115"/>
-      <c r="F114" s="115"/>
-      <c r="G114" s="115"/>
-      <c r="H114" s="115"/>
-      <c r="I114" s="115"/>
-      <c r="J114" s="115"/>
-      <c r="K114" s="115"/>
-      <c r="L114" s="115"/>
-      <c r="M114" s="115"/>
-      <c r="N114" s="115"/>
-    </row>
-    <row r="115" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A115" s="112"/>
-      <c r="B115" s="115"/>
-      <c r="C115" s="120"/>
-      <c r="D115" s="120"/>
-      <c r="E115" s="120"/>
-      <c r="F115" s="120"/>
-      <c r="G115" s="120"/>
-      <c r="H115" s="120"/>
-      <c r="I115" s="120"/>
-      <c r="J115" s="120"/>
-      <c r="K115" s="120"/>
-      <c r="L115" s="120"/>
-      <c r="M115" s="120"/>
-      <c r="N115" s="120"/>
-    </row>
-    <row r="116" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A116" s="112"/>
-      <c r="B116" s="115"/>
-      <c r="C116" s="115"/>
-      <c r="D116" s="115"/>
-      <c r="E116" s="115"/>
-      <c r="F116" s="115"/>
-      <c r="G116" s="115"/>
-      <c r="H116" s="115"/>
-      <c r="I116" s="115"/>
-      <c r="J116" s="115"/>
-      <c r="K116" s="115"/>
-      <c r="L116" s="115"/>
-      <c r="M116" s="115"/>
-      <c r="N116" s="115"/>
-    </row>
-    <row r="117" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A117" s="112"/>
-      <c r="B117" s="115"/>
-      <c r="C117" s="120"/>
-      <c r="D117" s="120"/>
-      <c r="E117" s="120"/>
-      <c r="F117" s="120"/>
-      <c r="G117" s="120"/>
-      <c r="H117" s="120"/>
-      <c r="I117" s="120"/>
-      <c r="J117" s="120"/>
-      <c r="K117" s="120"/>
-      <c r="L117" s="120"/>
-      <c r="M117" s="120"/>
-      <c r="N117" s="120"/>
-    </row>
-    <row r="118" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A118" s="112"/>
-      <c r="B118" s="115"/>
-      <c r="C118" s="115"/>
-      <c r="D118" s="115"/>
-      <c r="E118" s="115"/>
-      <c r="F118" s="115"/>
-      <c r="G118" s="115"/>
-      <c r="H118" s="115"/>
-      <c r="I118" s="115"/>
-      <c r="J118" s="115"/>
-      <c r="K118" s="115"/>
-      <c r="L118" s="115"/>
-      <c r="M118" s="115"/>
-      <c r="N118" s="115"/>
-    </row>
-    <row r="119" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A119" s="112"/>
-      <c r="B119" s="115"/>
-      <c r="C119" s="120"/>
-      <c r="D119" s="120"/>
-      <c r="E119" s="120"/>
-      <c r="F119" s="120"/>
-      <c r="G119" s="120"/>
-      <c r="H119" s="120"/>
-      <c r="I119" s="120"/>
-      <c r="J119" s="120"/>
-      <c r="K119" s="120"/>
-      <c r="L119" s="120"/>
-      <c r="M119" s="120"/>
-      <c r="N119" s="120"/>
-    </row>
-    <row r="120" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A120" s="112"/>
-      <c r="B120" s="115"/>
-      <c r="C120" s="115"/>
-      <c r="D120" s="115"/>
-      <c r="E120" s="115"/>
-      <c r="F120" s="115"/>
-      <c r="G120" s="115"/>
-      <c r="H120" s="115"/>
-      <c r="I120" s="115"/>
-      <c r="J120" s="115"/>
-      <c r="K120" s="115"/>
-      <c r="L120" s="115"/>
-      <c r="M120" s="115"/>
-      <c r="N120" s="115"/>
-    </row>
-    <row r="121" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A121" s="112"/>
-      <c r="B121" s="115"/>
-      <c r="C121" s="115"/>
-      <c r="D121" s="115"/>
-      <c r="E121" s="115"/>
-      <c r="F121" s="115"/>
-      <c r="G121" s="115"/>
-      <c r="H121" s="115"/>
-      <c r="I121" s="115"/>
-      <c r="J121" s="115"/>
-      <c r="K121" s="115"/>
-      <c r="L121" s="115"/>
-      <c r="M121" s="115"/>
-      <c r="N121" s="115"/>
-    </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A122" s="112"/>
-      <c r="B122" s="112"/>
-      <c r="C122" s="116" t="s">
+      <c r="E114" s="108"/>
+      <c r="F114" s="108"/>
+      <c r="G114" s="108"/>
+      <c r="H114" s="108"/>
+      <c r="I114" s="108"/>
+      <c r="J114" s="108"/>
+      <c r="K114" s="108"/>
+      <c r="L114" s="108"/>
+      <c r="M114" s="108"/>
+      <c r="N114" s="108"/>
+    </row>
+    <row r="115" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="107"/>
+      <c r="B115" s="108"/>
+      <c r="C115" s="112"/>
+      <c r="D115" s="112"/>
+      <c r="E115" s="112"/>
+      <c r="F115" s="112"/>
+      <c r="G115" s="112"/>
+      <c r="H115" s="112"/>
+      <c r="I115" s="112"/>
+      <c r="J115" s="112"/>
+      <c r="K115" s="112"/>
+      <c r="L115" s="112"/>
+      <c r="M115" s="112"/>
+      <c r="N115" s="112"/>
+    </row>
+    <row r="116" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="107"/>
+      <c r="B116" s="108"/>
+      <c r="C116" s="108"/>
+      <c r="D116" s="108"/>
+      <c r="E116" s="108"/>
+      <c r="F116" s="108"/>
+      <c r="G116" s="108"/>
+      <c r="H116" s="108"/>
+      <c r="I116" s="108"/>
+      <c r="J116" s="108"/>
+      <c r="K116" s="108"/>
+      <c r="L116" s="108"/>
+      <c r="M116" s="108"/>
+      <c r="N116" s="108"/>
+    </row>
+    <row r="117" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="107"/>
+      <c r="B117" s="108"/>
+      <c r="C117" s="112"/>
+      <c r="D117" s="112"/>
+      <c r="E117" s="112"/>
+      <c r="F117" s="112"/>
+      <c r="G117" s="112"/>
+      <c r="H117" s="112"/>
+      <c r="I117" s="112"/>
+      <c r="J117" s="112"/>
+      <c r="K117" s="112"/>
+      <c r="L117" s="112"/>
+      <c r="M117" s="112"/>
+      <c r="N117" s="112"/>
+    </row>
+    <row r="118" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="107"/>
+      <c r="B118" s="108"/>
+      <c r="C118" s="108"/>
+      <c r="D118" s="108"/>
+      <c r="E118" s="108"/>
+      <c r="F118" s="108"/>
+      <c r="G118" s="108"/>
+      <c r="H118" s="108"/>
+      <c r="I118" s="108"/>
+      <c r="J118" s="108"/>
+      <c r="K118" s="108"/>
+      <c r="L118" s="108"/>
+      <c r="M118" s="108"/>
+      <c r="N118" s="108"/>
+    </row>
+    <row r="119" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="107"/>
+      <c r="B119" s="108"/>
+      <c r="C119" s="112"/>
+      <c r="D119" s="112"/>
+      <c r="E119" s="112"/>
+      <c r="F119" s="112"/>
+      <c r="G119" s="112"/>
+      <c r="H119" s="112"/>
+      <c r="I119" s="112"/>
+      <c r="J119" s="112"/>
+      <c r="K119" s="112"/>
+      <c r="L119" s="112"/>
+      <c r="M119" s="112"/>
+      <c r="N119" s="112"/>
+    </row>
+    <row r="120" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="107"/>
+      <c r="B120" s="108"/>
+      <c r="C120" s="108"/>
+      <c r="D120" s="108"/>
+      <c r="E120" s="108"/>
+      <c r="F120" s="108"/>
+      <c r="G120" s="108"/>
+      <c r="H120" s="108"/>
+      <c r="I120" s="108"/>
+      <c r="J120" s="108"/>
+      <c r="K120" s="108"/>
+      <c r="L120" s="108"/>
+      <c r="M120" s="108"/>
+      <c r="N120" s="108"/>
+    </row>
+    <row r="121" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="107"/>
+      <c r="B121" s="108"/>
+      <c r="C121" s="108"/>
+      <c r="D121" s="108"/>
+      <c r="E121" s="108"/>
+      <c r="F121" s="108"/>
+      <c r="G121" s="108"/>
+      <c r="H121" s="108"/>
+      <c r="I121" s="108"/>
+      <c r="J121" s="108"/>
+      <c r="K121" s="108"/>
+      <c r="L121" s="108"/>
+      <c r="M121" s="108"/>
+      <c r="N121" s="108"/>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A122" s="107"/>
+      <c r="B122" s="107"/>
+      <c r="C122" s="109" t="s">
         <v>469</v>
       </c>
-      <c r="D122" s="116" t="s">
+      <c r="D122" s="109" t="s">
         <v>470</v>
       </c>
-      <c r="E122" s="116" t="s">
+      <c r="E122" s="109" t="s">
         <v>471</v>
       </c>
-      <c r="F122" s="116" t="s">
+      <c r="F122" s="109" t="s">
         <v>472</v>
       </c>
-      <c r="G122" s="116" t="s">
+      <c r="G122" s="109" t="s">
         <v>473</v>
       </c>
-      <c r="H122" s="116" t="s">
+      <c r="H122" s="109" t="s">
         <v>474</v>
       </c>
-      <c r="I122" s="116" t="s">
+      <c r="I122" s="109" t="s">
         <v>475</v>
       </c>
-      <c r="J122" s="116" t="s">
+      <c r="J122" s="109" t="s">
         <v>476</v>
       </c>
-      <c r="K122" s="116" t="s">
+      <c r="K122" s="109" t="s">
         <v>477</v>
       </c>
-      <c r="L122" s="116" t="s">
+      <c r="L122" s="109" t="s">
         <v>478</v>
       </c>
-      <c r="M122" s="116" t="s">
+      <c r="M122" s="109" t="s">
         <v>479</v>
       </c>
-      <c r="N122" s="116" t="s">
+      <c r="N122" s="109" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A123" s="112"/>
-      <c r="B123" s="112"/>
-      <c r="C123" s="117">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A123" s="107"/>
+      <c r="B123" s="107"/>
+      <c r="C123" s="110">
         <v>523</v>
       </c>
-      <c r="D123" s="117">
+      <c r="D123" s="110">
         <v>554</v>
       </c>
-      <c r="E123" s="117">
+      <c r="E123" s="110">
         <v>587</v>
       </c>
-      <c r="F123" s="117">
+      <c r="F123" s="110">
         <v>622</v>
       </c>
-      <c r="G123" s="117">
+      <c r="G123" s="110">
         <v>659</v>
       </c>
-      <c r="H123" s="117">
+      <c r="H123" s="110">
         <v>698</v>
       </c>
-      <c r="I123" s="117">
+      <c r="I123" s="110">
         <v>740</v>
       </c>
-      <c r="J123" s="117">
+      <c r="J123" s="110">
         <v>784</v>
       </c>
-      <c r="K123" s="117">
+      <c r="K123" s="110">
         <v>831</v>
       </c>
-      <c r="L123" s="117">
+      <c r="L123" s="110">
         <v>880</v>
       </c>
-      <c r="M123" s="117">
+      <c r="M123" s="110">
         <v>932</v>
       </c>
-      <c r="N123" s="117">
+      <c r="N123" s="110">
         <v>988</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A124" s="112"/>
-      <c r="B124" s="112"/>
-      <c r="C124" s="112"/>
-      <c r="D124" s="112"/>
-      <c r="E124" s="112"/>
-      <c r="F124" s="112"/>
-      <c r="G124" s="112"/>
-      <c r="H124" s="112"/>
-      <c r="I124" s="112"/>
-      <c r="J124" s="112"/>
-      <c r="K124" s="112"/>
-      <c r="L124" s="112"/>
-      <c r="M124" s="112"/>
-      <c r="N124" s="112"/>
-    </row>
-    <row r="125" spans="1:14" ht="16.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A125" s="112"/>
-      <c r="B125" s="114" t="s">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A124" s="107"/>
+      <c r="B124" s="107"/>
+      <c r="C124" s="107"/>
+      <c r="D124" s="107"/>
+      <c r="E124" s="107"/>
+      <c r="F124" s="107"/>
+      <c r="G124" s="107"/>
+      <c r="H124" s="107"/>
+      <c r="I124" s="107"/>
+      <c r="J124" s="107"/>
+      <c r="K124" s="107"/>
+      <c r="L124" s="107"/>
+      <c r="M124" s="107"/>
+      <c r="N124" s="107"/>
+    </row>
+    <row r="125" spans="1:14" ht="16.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="107"/>
+      <c r="B125" s="119" t="s">
         <v>481</v>
       </c>
-      <c r="C125" s="114"/>
-      <c r="D125" s="114"/>
-      <c r="E125" s="114"/>
-      <c r="F125" s="114"/>
-      <c r="G125" s="114"/>
-      <c r="H125" s="114"/>
-      <c r="I125" s="114"/>
-      <c r="J125" s="114"/>
-      <c r="K125" s="114"/>
-      <c r="L125" s="114"/>
-      <c r="M125" s="114"/>
-      <c r="N125" s="114"/>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A126" s="112"/>
-      <c r="B126" s="112"/>
-      <c r="C126" s="112"/>
-      <c r="D126" s="112"/>
-      <c r="E126" s="112"/>
-      <c r="F126" s="112"/>
-      <c r="G126" s="112"/>
-      <c r="H126" s="112"/>
-      <c r="I126" s="112"/>
-      <c r="J126" s="112"/>
-      <c r="K126" s="112"/>
-      <c r="L126" s="112"/>
-      <c r="M126" s="112"/>
-      <c r="N126" s="112"/>
-    </row>
-    <row r="127" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A127" s="112"/>
-      <c r="B127" s="115"/>
-      <c r="C127" s="115"/>
-      <c r="D127" s="115"/>
-      <c r="E127" s="115"/>
-      <c r="F127" s="115"/>
-      <c r="G127" s="115"/>
-      <c r="H127" s="115"/>
-      <c r="I127" s="115"/>
-      <c r="J127" s="115"/>
-      <c r="K127" s="115"/>
-      <c r="L127" s="115"/>
-      <c r="M127" s="115"/>
-      <c r="N127" s="115"/>
-    </row>
-    <row r="128" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A128" s="112"/>
-      <c r="B128" s="115"/>
-      <c r="C128" s="115"/>
-      <c r="D128" s="115"/>
-      <c r="E128" s="115"/>
-      <c r="F128" s="115"/>
-      <c r="G128" s="115"/>
-      <c r="H128" s="115"/>
-      <c r="I128" s="115"/>
-      <c r="J128" s="115"/>
-      <c r="K128" s="115"/>
-      <c r="L128" s="115"/>
-      <c r="M128" s="115"/>
-      <c r="N128" s="115" t="s">
+      <c r="C125" s="119"/>
+      <c r="D125" s="119"/>
+      <c r="E125" s="119"/>
+      <c r="F125" s="119"/>
+      <c r="G125" s="119"/>
+      <c r="H125" s="119"/>
+      <c r="I125" s="119"/>
+      <c r="J125" s="119"/>
+      <c r="K125" s="119"/>
+      <c r="L125" s="119"/>
+      <c r="M125" s="119"/>
+      <c r="N125" s="119"/>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A126" s="107"/>
+      <c r="B126" s="107"/>
+      <c r="C126" s="107"/>
+      <c r="D126" s="107"/>
+      <c r="E126" s="107"/>
+      <c r="F126" s="107"/>
+      <c r="G126" s="107"/>
+      <c r="H126" s="107"/>
+      <c r="I126" s="107"/>
+      <c r="J126" s="107"/>
+      <c r="K126" s="107"/>
+      <c r="L126" s="107"/>
+      <c r="M126" s="107"/>
+      <c r="N126" s="107"/>
+    </row>
+    <row r="127" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="107"/>
+      <c r="B127" s="108"/>
+      <c r="C127" s="108"/>
+      <c r="D127" s="108"/>
+      <c r="E127" s="108"/>
+      <c r="F127" s="108"/>
+      <c r="G127" s="108"/>
+      <c r="H127" s="108"/>
+      <c r="I127" s="108"/>
+      <c r="J127" s="108"/>
+      <c r="K127" s="108"/>
+      <c r="L127" s="108"/>
+      <c r="M127" s="108"/>
+      <c r="N127" s="108"/>
+    </row>
+    <row r="128" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="107"/>
+      <c r="B128" s="108"/>
+      <c r="C128" s="108"/>
+      <c r="D128" s="108"/>
+      <c r="E128" s="108"/>
+      <c r="F128" s="108"/>
+      <c r="G128" s="108"/>
+      <c r="H128" s="108"/>
+      <c r="I128" s="108"/>
+      <c r="J128" s="108"/>
+      <c r="K128" s="108"/>
+      <c r="L128" s="108"/>
+      <c r="M128" s="108"/>
+      <c r="N128" s="108" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="129" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A129" s="112"/>
-      <c r="B129" s="115"/>
-      <c r="C129" s="115"/>
-      <c r="D129" s="115"/>
-      <c r="E129" s="115"/>
-      <c r="F129" s="115"/>
-      <c r="G129" s="115"/>
-      <c r="H129" s="115"/>
-      <c r="I129" s="115"/>
-      <c r="J129" s="115"/>
-      <c r="K129" s="115"/>
-      <c r="L129" s="120" t="s">
+    <row r="129" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="107"/>
+      <c r="B129" s="108"/>
+      <c r="C129" s="108"/>
+      <c r="D129" s="108"/>
+      <c r="E129" s="108"/>
+      <c r="F129" s="108"/>
+      <c r="G129" s="108"/>
+      <c r="H129" s="108"/>
+      <c r="I129" s="108"/>
+      <c r="J129" s="108"/>
+      <c r="K129" s="108"/>
+      <c r="L129" s="112" t="s">
         <v>411</v>
       </c>
-      <c r="M129" s="120" t="s">
+      <c r="M129" s="112" t="s">
         <v>414</v>
       </c>
-      <c r="N129" s="115"/>
-    </row>
-    <row r="130" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A130" s="112"/>
-      <c r="B130" s="115"/>
-      <c r="C130" s="115"/>
-      <c r="D130" s="115"/>
-      <c r="E130" s="115"/>
-      <c r="F130" s="115"/>
-      <c r="G130" s="115"/>
-      <c r="H130" s="115"/>
-      <c r="I130" s="115"/>
-      <c r="J130" s="115" t="s">
+      <c r="N129" s="108"/>
+    </row>
+    <row r="130" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="107"/>
+      <c r="B130" s="108"/>
+      <c r="C130" s="108"/>
+      <c r="D130" s="108"/>
+      <c r="E130" s="108"/>
+      <c r="F130" s="108"/>
+      <c r="G130" s="108"/>
+      <c r="H130" s="108"/>
+      <c r="I130" s="108"/>
+      <c r="J130" s="108" t="s">
         <v>411</v>
       </c>
-      <c r="K130" s="115" t="s">
+      <c r="K130" s="108" t="s">
         <v>414</v>
       </c>
-      <c r="L130" s="115"/>
-      <c r="M130" s="115"/>
-      <c r="N130" s="115"/>
-    </row>
-    <row r="131" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A131" s="112"/>
-      <c r="B131" s="115"/>
-      <c r="C131" s="120"/>
-      <c r="D131" s="120"/>
-      <c r="E131" s="120"/>
-      <c r="F131" s="120"/>
-      <c r="G131" s="120"/>
-      <c r="H131" s="120" t="s">
+      <c r="L130" s="108"/>
+      <c r="M130" s="108"/>
+      <c r="N130" s="108"/>
+    </row>
+    <row r="131" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="107"/>
+      <c r="B131" s="108"/>
+      <c r="C131" s="112"/>
+      <c r="D131" s="112"/>
+      <c r="E131" s="112"/>
+      <c r="F131" s="112"/>
+      <c r="G131" s="112"/>
+      <c r="H131" s="112" t="s">
         <v>411</v>
       </c>
-      <c r="I131" s="120" t="s">
+      <c r="I131" s="112" t="s">
         <v>414</v>
       </c>
-      <c r="J131" s="120"/>
-      <c r="K131" s="120"/>
-      <c r="L131" s="120"/>
-      <c r="M131" s="120"/>
-      <c r="N131" s="120"/>
-    </row>
-    <row r="132" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A132" s="112"/>
-      <c r="B132" s="115"/>
-      <c r="C132" s="115"/>
-      <c r="D132" s="115"/>
-      <c r="E132" s="115"/>
-      <c r="F132" s="115"/>
-      <c r="G132" s="115" t="s">
+      <c r="J131" s="112"/>
+      <c r="K131" s="112"/>
+      <c r="L131" s="112"/>
+      <c r="M131" s="112"/>
+      <c r="N131" s="112"/>
+    </row>
+    <row r="132" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="107"/>
+      <c r="B132" s="108"/>
+      <c r="C132" s="108"/>
+      <c r="D132" s="108"/>
+      <c r="E132" s="108"/>
+      <c r="F132" s="108"/>
+      <c r="G132" s="108" t="s">
         <v>411</v>
       </c>
-      <c r="H132" s="115"/>
-      <c r="I132" s="115"/>
-      <c r="J132" s="115"/>
-      <c r="K132" s="115"/>
-      <c r="L132" s="115"/>
-      <c r="M132" s="115"/>
-      <c r="N132" s="115"/>
-    </row>
-    <row r="133" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A133" s="112"/>
-      <c r="B133" s="115"/>
-      <c r="C133" s="120"/>
-      <c r="D133" s="120"/>
-      <c r="E133" s="120" t="s">
+      <c r="H132" s="108"/>
+      <c r="I132" s="108"/>
+      <c r="J132" s="108"/>
+      <c r="K132" s="108"/>
+      <c r="L132" s="108"/>
+      <c r="M132" s="108"/>
+      <c r="N132" s="108"/>
+    </row>
+    <row r="133" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="107"/>
+      <c r="B133" s="108"/>
+      <c r="C133" s="112"/>
+      <c r="D133" s="112"/>
+      <c r="E133" s="112" t="s">
         <v>411</v>
       </c>
-      <c r="F133" s="120" t="s">
+      <c r="F133" s="112" t="s">
         <v>414</v>
       </c>
-      <c r="G133" s="120"/>
-      <c r="H133" s="120"/>
-      <c r="I133" s="120"/>
-      <c r="J133" s="120"/>
-      <c r="K133" s="120"/>
-      <c r="L133" s="120"/>
-      <c r="M133" s="120"/>
-      <c r="N133" s="120"/>
-    </row>
-    <row r="134" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A134" s="112"/>
-      <c r="B134" s="115" t="s">
+      <c r="G133" s="112"/>
+      <c r="H133" s="112"/>
+      <c r="I133" s="112"/>
+      <c r="J133" s="112"/>
+      <c r="K133" s="112"/>
+      <c r="L133" s="112"/>
+      <c r="M133" s="112"/>
+      <c r="N133" s="112"/>
+    </row>
+    <row r="134" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="107"/>
+      <c r="B134" s="108" t="s">
         <v>482</v>
       </c>
-      <c r="C134" s="115" t="s">
+      <c r="C134" s="108" t="s">
         <v>411</v>
       </c>
-      <c r="D134" s="115" t="s">
+      <c r="D134" s="108" t="s">
         <v>414</v>
       </c>
-      <c r="E134" s="115"/>
-      <c r="F134" s="115"/>
-      <c r="G134" s="115"/>
-      <c r="H134" s="115"/>
-      <c r="I134" s="115"/>
-      <c r="J134" s="115"/>
-      <c r="K134" s="115"/>
-      <c r="L134" s="115"/>
-      <c r="M134" s="115"/>
-      <c r="N134" s="115"/>
-    </row>
-    <row r="135" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A135" s="112"/>
-      <c r="B135" s="115"/>
-      <c r="C135" s="120"/>
-      <c r="D135" s="120"/>
-      <c r="E135" s="120"/>
-      <c r="F135" s="120"/>
-      <c r="G135" s="120"/>
-      <c r="H135" s="120"/>
-      <c r="I135" s="120"/>
-      <c r="J135" s="120"/>
-      <c r="K135" s="120"/>
-      <c r="L135" s="120"/>
-      <c r="M135" s="120"/>
-      <c r="N135" s="120"/>
-    </row>
-    <row r="136" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A136" s="112"/>
-      <c r="B136" s="115"/>
-      <c r="C136" s="115"/>
-      <c r="D136" s="115"/>
-      <c r="E136" s="115"/>
-      <c r="F136" s="115"/>
-      <c r="G136" s="115"/>
-      <c r="H136" s="115"/>
-      <c r="I136" s="115"/>
-      <c r="J136" s="115"/>
-      <c r="K136" s="115"/>
-      <c r="L136" s="115"/>
-      <c r="M136" s="115"/>
-      <c r="N136" s="115"/>
-    </row>
-    <row r="137" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A137" s="112"/>
-      <c r="B137" s="115"/>
-      <c r="C137" s="120"/>
-      <c r="D137" s="120"/>
-      <c r="E137" s="120"/>
-      <c r="F137" s="120"/>
-      <c r="G137" s="120"/>
-      <c r="H137" s="120"/>
-      <c r="I137" s="120"/>
-      <c r="J137" s="120"/>
-      <c r="K137" s="120"/>
-      <c r="L137" s="120"/>
-      <c r="M137" s="120"/>
-      <c r="N137" s="120"/>
-    </row>
-    <row r="138" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A138" s="112"/>
-      <c r="B138" s="115"/>
-      <c r="C138" s="115"/>
-      <c r="D138" s="115"/>
-      <c r="E138" s="115"/>
-      <c r="F138" s="115"/>
-      <c r="G138" s="115"/>
-      <c r="H138" s="115"/>
-      <c r="I138" s="115"/>
-      <c r="J138" s="115"/>
-      <c r="K138" s="115"/>
-      <c r="L138" s="115"/>
-      <c r="M138" s="115"/>
-      <c r="N138" s="115"/>
-    </row>
-    <row r="139" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A139" s="112"/>
-      <c r="B139" s="115"/>
-      <c r="C139" s="120"/>
-      <c r="D139" s="120"/>
-      <c r="E139" s="120"/>
-      <c r="F139" s="120"/>
-      <c r="G139" s="120"/>
-      <c r="H139" s="120"/>
-      <c r="I139" s="120"/>
-      <c r="J139" s="120"/>
-      <c r="K139" s="120"/>
-      <c r="L139" s="120"/>
-      <c r="M139" s="120"/>
-      <c r="N139" s="120"/>
-    </row>
-    <row r="140" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A140" s="112"/>
-      <c r="B140" s="115"/>
-      <c r="C140" s="115"/>
-      <c r="D140" s="115"/>
-      <c r="E140" s="115"/>
-      <c r="F140" s="115"/>
-      <c r="G140" s="115"/>
-      <c r="H140" s="115"/>
-      <c r="I140" s="115"/>
-      <c r="J140" s="115"/>
-      <c r="K140" s="115"/>
-      <c r="L140" s="115"/>
-      <c r="M140" s="115"/>
-      <c r="N140" s="115"/>
-    </row>
-    <row r="141" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A141" s="112"/>
-      <c r="B141" s="115"/>
-      <c r="C141" s="115"/>
-      <c r="D141" s="115"/>
-      <c r="E141" s="115"/>
-      <c r="F141" s="115"/>
-      <c r="G141" s="115"/>
-      <c r="H141" s="115"/>
-      <c r="I141" s="115"/>
-      <c r="J141" s="115"/>
-      <c r="K141" s="115"/>
-      <c r="L141" s="115"/>
-      <c r="M141" s="115"/>
-      <c r="N141" s="115"/>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A142" s="112"/>
-      <c r="B142" s="112"/>
-      <c r="C142" s="116" t="s">
+      <c r="E134" s="108"/>
+      <c r="F134" s="108"/>
+      <c r="G134" s="108"/>
+      <c r="H134" s="108"/>
+      <c r="I134" s="108"/>
+      <c r="J134" s="108"/>
+      <c r="K134" s="108"/>
+      <c r="L134" s="108"/>
+      <c r="M134" s="108"/>
+      <c r="N134" s="108"/>
+    </row>
+    <row r="135" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="107"/>
+      <c r="B135" s="108"/>
+      <c r="C135" s="112"/>
+      <c r="D135" s="112"/>
+      <c r="E135" s="112"/>
+      <c r="F135" s="112"/>
+      <c r="G135" s="112"/>
+      <c r="H135" s="112"/>
+      <c r="I135" s="112"/>
+      <c r="J135" s="112"/>
+      <c r="K135" s="112"/>
+      <c r="L135" s="112"/>
+      <c r="M135" s="112"/>
+      <c r="N135" s="112"/>
+    </row>
+    <row r="136" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="107"/>
+      <c r="B136" s="108"/>
+      <c r="C136" s="108"/>
+      <c r="D136" s="108"/>
+      <c r="E136" s="108"/>
+      <c r="F136" s="108"/>
+      <c r="G136" s="108"/>
+      <c r="H136" s="108"/>
+      <c r="I136" s="108"/>
+      <c r="J136" s="108"/>
+      <c r="K136" s="108"/>
+      <c r="L136" s="108"/>
+      <c r="M136" s="108"/>
+      <c r="N136" s="108"/>
+    </row>
+    <row r="137" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="107"/>
+      <c r="B137" s="108"/>
+      <c r="C137" s="112"/>
+      <c r="D137" s="112"/>
+      <c r="E137" s="112"/>
+      <c r="F137" s="112"/>
+      <c r="G137" s="112"/>
+      <c r="H137" s="112"/>
+      <c r="I137" s="112"/>
+      <c r="J137" s="112"/>
+      <c r="K137" s="112"/>
+      <c r="L137" s="112"/>
+      <c r="M137" s="112"/>
+      <c r="N137" s="112"/>
+    </row>
+    <row r="138" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="107"/>
+      <c r="B138" s="108"/>
+      <c r="C138" s="108"/>
+      <c r="D138" s="108"/>
+      <c r="E138" s="108"/>
+      <c r="F138" s="108"/>
+      <c r="G138" s="108"/>
+      <c r="H138" s="108"/>
+      <c r="I138" s="108"/>
+      <c r="J138" s="108"/>
+      <c r="K138" s="108"/>
+      <c r="L138" s="108"/>
+      <c r="M138" s="108"/>
+      <c r="N138" s="108"/>
+    </row>
+    <row r="139" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="107"/>
+      <c r="B139" s="108"/>
+      <c r="C139" s="112"/>
+      <c r="D139" s="112"/>
+      <c r="E139" s="112"/>
+      <c r="F139" s="112"/>
+      <c r="G139" s="112"/>
+      <c r="H139" s="112"/>
+      <c r="I139" s="112"/>
+      <c r="J139" s="112"/>
+      <c r="K139" s="112"/>
+      <c r="L139" s="112"/>
+      <c r="M139" s="112"/>
+      <c r="N139" s="112"/>
+    </row>
+    <row r="140" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="107"/>
+      <c r="B140" s="108"/>
+      <c r="C140" s="108"/>
+      <c r="D140" s="108"/>
+      <c r="E140" s="108"/>
+      <c r="F140" s="108"/>
+      <c r="G140" s="108"/>
+      <c r="H140" s="108"/>
+      <c r="I140" s="108"/>
+      <c r="J140" s="108"/>
+      <c r="K140" s="108"/>
+      <c r="L140" s="108"/>
+      <c r="M140" s="108"/>
+      <c r="N140" s="108"/>
+    </row>
+    <row r="141" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="107"/>
+      <c r="B141" s="108"/>
+      <c r="C141" s="108"/>
+      <c r="D141" s="108"/>
+      <c r="E141" s="108"/>
+      <c r="F141" s="108"/>
+      <c r="G141" s="108"/>
+      <c r="H141" s="108"/>
+      <c r="I141" s="108"/>
+      <c r="J141" s="108"/>
+      <c r="K141" s="108"/>
+      <c r="L141" s="108"/>
+      <c r="M141" s="108"/>
+      <c r="N141" s="108"/>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A142" s="107"/>
+      <c r="B142" s="107"/>
+      <c r="C142" s="109" t="s">
         <v>483</v>
       </c>
-      <c r="D142" s="116" t="s">
+      <c r="D142" s="109" t="s">
         <v>484</v>
       </c>
-      <c r="E142" s="116" t="s">
+      <c r="E142" s="109" t="s">
         <v>485</v>
       </c>
-      <c r="F142" s="116" t="s">
+      <c r="F142" s="109" t="s">
         <v>486</v>
       </c>
-      <c r="G142" s="116" t="s">
+      <c r="G142" s="109" t="s">
         <v>487</v>
       </c>
-      <c r="H142" s="116" t="s">
+      <c r="H142" s="109" t="s">
         <v>488</v>
       </c>
-      <c r="I142" s="116" t="s">
+      <c r="I142" s="109" t="s">
         <v>489</v>
       </c>
-      <c r="J142" s="116" t="s">
+      <c r="J142" s="109" t="s">
         <v>490</v>
       </c>
-      <c r="K142" s="116" t="s">
+      <c r="K142" s="109" t="s">
         <v>491</v>
       </c>
-      <c r="L142" s="116" t="s">
+      <c r="L142" s="109" t="s">
         <v>492</v>
       </c>
-      <c r="M142" s="116" t="s">
+      <c r="M142" s="109" t="s">
         <v>493</v>
       </c>
-      <c r="N142" s="116" t="s">
+      <c r="N142" s="109" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A143" s="112"/>
-      <c r="B143" s="112"/>
-      <c r="C143" s="117">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A143" s="107"/>
+      <c r="B143" s="107"/>
+      <c r="C143" s="110">
         <v>1047</v>
       </c>
-      <c r="D143" s="117">
+      <c r="D143" s="110">
         <v>1109</v>
       </c>
-      <c r="E143" s="117">
+      <c r="E143" s="110">
         <v>1175</v>
       </c>
-      <c r="F143" s="117">
+      <c r="F143" s="110">
         <v>1245</v>
       </c>
-      <c r="G143" s="117">
+      <c r="G143" s="110">
         <v>1319</v>
       </c>
-      <c r="H143" s="117">
+      <c r="H143" s="110">
         <v>1397</v>
       </c>
-      <c r="I143" s="117">
+      <c r="I143" s="110">
         <v>1480</v>
       </c>
-      <c r="J143" s="117">
+      <c r="J143" s="110">
         <v>1568</v>
       </c>
-      <c r="K143" s="117">
+      <c r="K143" s="110">
         <v>1661</v>
       </c>
-      <c r="L143" s="117">
+      <c r="L143" s="110">
         <v>1760</v>
       </c>
-      <c r="M143" s="117">
+      <c r="M143" s="110">
         <v>1865</v>
       </c>
-      <c r="N143" s="117">
+      <c r="N143" s="110">
         <v>1976</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A144" s="112"/>
-      <c r="B144" s="112"/>
-      <c r="C144" s="112"/>
-      <c r="D144" s="112"/>
-      <c r="E144" s="112"/>
-      <c r="F144" s="112"/>
-      <c r="G144" s="112"/>
-      <c r="H144" s="112"/>
-      <c r="I144" s="112"/>
-      <c r="J144" s="112"/>
-      <c r="K144" s="112"/>
-      <c r="L144" s="112"/>
-      <c r="M144" s="112"/>
-      <c r="N144" s="112"/>
-    </row>
-    <row r="145" spans="1:14" ht="16.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A145" s="112"/>
-      <c r="B145" s="114" t="s">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A144" s="107"/>
+      <c r="B144" s="107"/>
+      <c r="C144" s="107"/>
+      <c r="D144" s="107"/>
+      <c r="E144" s="107"/>
+      <c r="F144" s="107"/>
+      <c r="G144" s="107"/>
+      <c r="H144" s="107"/>
+      <c r="I144" s="107"/>
+      <c r="J144" s="107"/>
+      <c r="K144" s="107"/>
+      <c r="L144" s="107"/>
+      <c r="M144" s="107"/>
+      <c r="N144" s="107"/>
+    </row>
+    <row r="145" spans="1:14" ht="16.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A145" s="107"/>
+      <c r="B145" s="119" t="s">
         <v>495</v>
       </c>
-      <c r="C145" s="114"/>
-      <c r="D145" s="114"/>
-      <c r="E145" s="114"/>
-      <c r="F145" s="114"/>
-      <c r="G145" s="114"/>
-      <c r="H145" s="114"/>
-      <c r="I145" s="114"/>
-      <c r="J145" s="114"/>
-      <c r="K145" s="114"/>
-      <c r="L145" s="114"/>
-      <c r="M145" s="114"/>
-      <c r="N145" s="114"/>
-    </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A146" s="112"/>
-      <c r="B146" s="112"/>
-      <c r="C146" s="112"/>
-      <c r="D146" s="112"/>
-      <c r="E146" s="112"/>
-      <c r="F146" s="112"/>
-      <c r="G146" s="112"/>
-      <c r="H146" s="112"/>
-      <c r="I146" s="112"/>
-      <c r="J146" s="112"/>
-      <c r="K146" s="112"/>
-      <c r="L146" s="112"/>
-      <c r="M146" s="112"/>
-      <c r="N146" s="112"/>
-    </row>
-    <row r="147" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A147" s="112"/>
-      <c r="B147" s="115"/>
-      <c r="C147" s="115"/>
-      <c r="D147" s="115"/>
-      <c r="E147" s="115"/>
-      <c r="F147" s="115"/>
-      <c r="G147" s="115"/>
-      <c r="H147" s="115"/>
-      <c r="I147" s="115"/>
-      <c r="J147" s="115"/>
-      <c r="K147" s="115"/>
-      <c r="L147" s="115"/>
-      <c r="M147" s="115"/>
-      <c r="N147" s="115"/>
-    </row>
-    <row r="148" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A148" s="112"/>
-      <c r="B148" s="115"/>
-      <c r="C148" s="115"/>
-      <c r="D148" s="115"/>
-      <c r="E148" s="115"/>
-      <c r="F148" s="115"/>
-      <c r="G148" s="115"/>
-      <c r="H148" s="115"/>
-      <c r="I148" s="115"/>
-      <c r="J148" s="115"/>
-      <c r="K148" s="115"/>
-      <c r="L148" s="115"/>
-      <c r="M148" s="115"/>
-      <c r="N148" s="115" t="s">
+      <c r="C145" s="119"/>
+      <c r="D145" s="119"/>
+      <c r="E145" s="119"/>
+      <c r="F145" s="119"/>
+      <c r="G145" s="119"/>
+      <c r="H145" s="119"/>
+      <c r="I145" s="119"/>
+      <c r="J145" s="119"/>
+      <c r="K145" s="119"/>
+      <c r="L145" s="119"/>
+      <c r="M145" s="119"/>
+      <c r="N145" s="119"/>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A146" s="107"/>
+      <c r="B146" s="107"/>
+      <c r="C146" s="107"/>
+      <c r="D146" s="107"/>
+      <c r="E146" s="107"/>
+      <c r="F146" s="107"/>
+      <c r="G146" s="107"/>
+      <c r="H146" s="107"/>
+      <c r="I146" s="107"/>
+      <c r="J146" s="107"/>
+      <c r="K146" s="107"/>
+      <c r="L146" s="107"/>
+      <c r="M146" s="107"/>
+      <c r="N146" s="107"/>
+    </row>
+    <row r="147" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A147" s="107"/>
+      <c r="B147" s="108"/>
+      <c r="C147" s="108"/>
+      <c r="D147" s="108"/>
+      <c r="E147" s="108"/>
+      <c r="F147" s="108"/>
+      <c r="G147" s="108"/>
+      <c r="H147" s="108"/>
+      <c r="I147" s="108"/>
+      <c r="J147" s="108"/>
+      <c r="K147" s="108"/>
+      <c r="L147" s="108"/>
+      <c r="M147" s="108"/>
+      <c r="N147" s="108"/>
+    </row>
+    <row r="148" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A148" s="107"/>
+      <c r="B148" s="108"/>
+      <c r="C148" s="108"/>
+      <c r="D148" s="108"/>
+      <c r="E148" s="108"/>
+      <c r="F148" s="108"/>
+      <c r="G148" s="108"/>
+      <c r="H148" s="108"/>
+      <c r="I148" s="108"/>
+      <c r="J148" s="108"/>
+      <c r="K148" s="108"/>
+      <c r="L148" s="108"/>
+      <c r="M148" s="108"/>
+      <c r="N148" s="108" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="149" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A149" s="112"/>
-      <c r="B149" s="115"/>
-      <c r="C149" s="115"/>
-      <c r="D149" s="115"/>
-      <c r="E149" s="115"/>
-      <c r="F149" s="115"/>
-      <c r="G149" s="115"/>
-      <c r="H149" s="115"/>
-      <c r="I149" s="115"/>
-      <c r="J149" s="115"/>
-      <c r="K149" s="115"/>
-      <c r="L149" s="120" t="s">
+    <row r="149" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="107"/>
+      <c r="B149" s="108"/>
+      <c r="C149" s="108"/>
+      <c r="D149" s="108"/>
+      <c r="E149" s="108"/>
+      <c r="F149" s="108"/>
+      <c r="G149" s="108"/>
+      <c r="H149" s="108"/>
+      <c r="I149" s="108"/>
+      <c r="J149" s="108"/>
+      <c r="K149" s="108"/>
+      <c r="L149" s="112" t="s">
         <v>411</v>
       </c>
-      <c r="M149" s="120" t="s">
+      <c r="M149" s="112" t="s">
         <v>414</v>
       </c>
-      <c r="N149" s="115"/>
-    </row>
-    <row r="150" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A150" s="112"/>
-      <c r="B150" s="115"/>
-      <c r="C150" s="115"/>
-      <c r="D150" s="115"/>
-      <c r="E150" s="115"/>
-      <c r="F150" s="115"/>
-      <c r="G150" s="115"/>
-      <c r="H150" s="115"/>
-      <c r="I150" s="115"/>
-      <c r="J150" s="115" t="s">
+      <c r="N149" s="108"/>
+    </row>
+    <row r="150" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="107"/>
+      <c r="B150" s="108"/>
+      <c r="C150" s="108"/>
+      <c r="D150" s="108"/>
+      <c r="E150" s="108"/>
+      <c r="F150" s="108"/>
+      <c r="G150" s="108"/>
+      <c r="H150" s="108"/>
+      <c r="I150" s="108"/>
+      <c r="J150" s="108" t="s">
         <v>411</v>
       </c>
-      <c r="K150" s="115" t="s">
+      <c r="K150" s="108" t="s">
         <v>414</v>
       </c>
-      <c r="L150" s="115"/>
-      <c r="M150" s="115"/>
-      <c r="N150" s="115"/>
-    </row>
-    <row r="151" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A151" s="112"/>
-      <c r="B151" s="115"/>
-      <c r="C151" s="120"/>
-      <c r="D151" s="120"/>
-      <c r="E151" s="120"/>
-      <c r="F151" s="120"/>
-      <c r="G151" s="120"/>
-      <c r="H151" s="120" t="s">
+      <c r="L150" s="108"/>
+      <c r="M150" s="108"/>
+      <c r="N150" s="108"/>
+    </row>
+    <row r="151" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="107"/>
+      <c r="B151" s="108"/>
+      <c r="C151" s="112"/>
+      <c r="D151" s="112"/>
+      <c r="E151" s="112"/>
+      <c r="F151" s="112"/>
+      <c r="G151" s="112"/>
+      <c r="H151" s="112" t="s">
         <v>411</v>
       </c>
-      <c r="I151" s="120" t="s">
+      <c r="I151" s="112" t="s">
         <v>414</v>
       </c>
-      <c r="J151" s="120"/>
-      <c r="K151" s="120"/>
-      <c r="L151" s="120"/>
-      <c r="M151" s="120"/>
-      <c r="N151" s="120"/>
-    </row>
-    <row r="152" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A152" s="112"/>
-      <c r="B152" s="115"/>
-      <c r="C152" s="115"/>
-      <c r="D152" s="115"/>
-      <c r="E152" s="115"/>
-      <c r="F152" s="115"/>
-      <c r="G152" s="115" t="s">
+      <c r="J151" s="112"/>
+      <c r="K151" s="112"/>
+      <c r="L151" s="112"/>
+      <c r="M151" s="112"/>
+      <c r="N151" s="112"/>
+    </row>
+    <row r="152" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="107"/>
+      <c r="B152" s="108"/>
+      <c r="C152" s="108"/>
+      <c r="D152" s="108"/>
+      <c r="E152" s="108"/>
+      <c r="F152" s="108"/>
+      <c r="G152" s="108" t="s">
         <v>411</v>
       </c>
-      <c r="H152" s="115"/>
-      <c r="I152" s="115"/>
-      <c r="J152" s="115"/>
-      <c r="K152" s="115"/>
-      <c r="L152" s="115"/>
-      <c r="M152" s="115"/>
-      <c r="N152" s="115"/>
-    </row>
-    <row r="153" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A153" s="112"/>
-      <c r="B153" s="115"/>
-      <c r="C153" s="120"/>
-      <c r="D153" s="120"/>
-      <c r="E153" s="120" t="s">
+      <c r="H152" s="108"/>
+      <c r="I152" s="108"/>
+      <c r="J152" s="108"/>
+      <c r="K152" s="108"/>
+      <c r="L152" s="108"/>
+      <c r="M152" s="108"/>
+      <c r="N152" s="108"/>
+    </row>
+    <row r="153" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="107"/>
+      <c r="B153" s="108"/>
+      <c r="C153" s="112"/>
+      <c r="D153" s="112"/>
+      <c r="E153" s="112" t="s">
         <v>411</v>
       </c>
-      <c r="F153" s="120" t="s">
+      <c r="F153" s="112" t="s">
         <v>414</v>
       </c>
-      <c r="G153" s="120"/>
-      <c r="H153" s="120"/>
-      <c r="I153" s="120"/>
-      <c r="J153" s="120"/>
-      <c r="K153" s="120"/>
-      <c r="L153" s="120"/>
-      <c r="M153" s="120"/>
-      <c r="N153" s="120"/>
-    </row>
-    <row r="154" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A154" s="112"/>
-      <c r="B154" s="115" t="s">
+      <c r="G153" s="112"/>
+      <c r="H153" s="112"/>
+      <c r="I153" s="112"/>
+      <c r="J153" s="112"/>
+      <c r="K153" s="112"/>
+      <c r="L153" s="112"/>
+      <c r="M153" s="112"/>
+      <c r="N153" s="112"/>
+    </row>
+    <row r="154" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A154" s="107"/>
+      <c r="B154" s="108" t="s">
         <v>496</v>
       </c>
-      <c r="C154" s="115" t="s">
+      <c r="C154" s="108" t="s">
         <v>411</v>
       </c>
-      <c r="D154" s="115" t="s">
+      <c r="D154" s="108" t="s">
         <v>414</v>
       </c>
-      <c r="E154" s="115"/>
-      <c r="F154" s="115"/>
-      <c r="G154" s="115"/>
-      <c r="H154" s="115"/>
-      <c r="I154" s="115"/>
-      <c r="J154" s="115"/>
-      <c r="K154" s="115"/>
-      <c r="L154" s="115"/>
-      <c r="M154" s="115"/>
-      <c r="N154" s="115"/>
-    </row>
-    <row r="155" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A155" s="112"/>
-      <c r="B155" s="115"/>
-      <c r="C155" s="120"/>
-      <c r="D155" s="120"/>
-      <c r="E155" s="120"/>
-      <c r="F155" s="120"/>
-      <c r="G155" s="120"/>
-      <c r="H155" s="120"/>
-      <c r="I155" s="120"/>
-      <c r="J155" s="120"/>
-      <c r="K155" s="120"/>
-      <c r="L155" s="120"/>
-      <c r="M155" s="120"/>
-      <c r="N155" s="120"/>
-    </row>
-    <row r="156" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A156" s="112"/>
-      <c r="B156" s="115"/>
-      <c r="C156" s="115"/>
-      <c r="D156" s="115"/>
-      <c r="E156" s="115"/>
-      <c r="F156" s="115"/>
-      <c r="G156" s="115"/>
-      <c r="H156" s="115"/>
-      <c r="I156" s="115"/>
-      <c r="J156" s="115"/>
-      <c r="K156" s="115"/>
-      <c r="L156" s="115"/>
-      <c r="M156" s="115"/>
-      <c r="N156" s="115"/>
-    </row>
-    <row r="157" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A157" s="112"/>
-      <c r="B157" s="115"/>
-      <c r="C157" s="120"/>
-      <c r="D157" s="120"/>
-      <c r="E157" s="120"/>
-      <c r="F157" s="120"/>
-      <c r="G157" s="120"/>
-      <c r="H157" s="120"/>
-      <c r="I157" s="120"/>
-      <c r="J157" s="120"/>
-      <c r="K157" s="120"/>
-      <c r="L157" s="120"/>
-      <c r="M157" s="120"/>
-      <c r="N157" s="120"/>
-    </row>
-    <row r="158" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A158" s="112"/>
-      <c r="B158" s="115"/>
-      <c r="C158" s="115"/>
-      <c r="D158" s="115"/>
-      <c r="E158" s="115"/>
-      <c r="F158" s="115"/>
-      <c r="G158" s="115"/>
-      <c r="H158" s="115"/>
-      <c r="I158" s="115"/>
-      <c r="J158" s="115"/>
-      <c r="K158" s="115"/>
-      <c r="L158" s="115"/>
-      <c r="M158" s="115"/>
-      <c r="N158" s="115"/>
-    </row>
-    <row r="159" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A159" s="112"/>
-      <c r="B159" s="115"/>
-      <c r="C159" s="120"/>
-      <c r="D159" s="120"/>
-      <c r="E159" s="120"/>
-      <c r="F159" s="120"/>
-      <c r="G159" s="120"/>
-      <c r="H159" s="120"/>
-      <c r="I159" s="120"/>
-      <c r="J159" s="120"/>
-      <c r="K159" s="120"/>
-      <c r="L159" s="120"/>
-      <c r="M159" s="120"/>
-      <c r="N159" s="120"/>
-    </row>
-    <row r="160" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A160" s="112"/>
-      <c r="B160" s="115"/>
-      <c r="C160" s="115"/>
-      <c r="D160" s="115"/>
-      <c r="E160" s="115"/>
-      <c r="F160" s="115"/>
-      <c r="G160" s="115"/>
-      <c r="H160" s="115"/>
-      <c r="I160" s="115"/>
-      <c r="J160" s="115"/>
-      <c r="K160" s="115"/>
-      <c r="L160" s="115"/>
-      <c r="M160" s="115"/>
-      <c r="N160" s="115"/>
-    </row>
-    <row r="161" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A161" s="112"/>
-      <c r="B161" s="115"/>
-      <c r="C161" s="115"/>
-      <c r="D161" s="115"/>
-      <c r="E161" s="115"/>
-      <c r="F161" s="115"/>
-      <c r="G161" s="115"/>
-      <c r="H161" s="115"/>
-      <c r="I161" s="115"/>
-      <c r="J161" s="115"/>
-      <c r="K161" s="115"/>
-      <c r="L161" s="115"/>
-      <c r="M161" s="115"/>
-      <c r="N161" s="115"/>
-    </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A162" s="112"/>
-      <c r="B162" s="112"/>
-      <c r="C162" s="116" t="s">
+      <c r="E154" s="108"/>
+      <c r="F154" s="108"/>
+      <c r="G154" s="108"/>
+      <c r="H154" s="108"/>
+      <c r="I154" s="108"/>
+      <c r="J154" s="108"/>
+      <c r="K154" s="108"/>
+      <c r="L154" s="108"/>
+      <c r="M154" s="108"/>
+      <c r="N154" s="108"/>
+    </row>
+    <row r="155" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A155" s="107"/>
+      <c r="B155" s="108"/>
+      <c r="C155" s="112"/>
+      <c r="D155" s="112"/>
+      <c r="E155" s="112"/>
+      <c r="F155" s="112"/>
+      <c r="G155" s="112"/>
+      <c r="H155" s="112"/>
+      <c r="I155" s="112"/>
+      <c r="J155" s="112"/>
+      <c r="K155" s="112"/>
+      <c r="L155" s="112"/>
+      <c r="M155" s="112"/>
+      <c r="N155" s="112"/>
+    </row>
+    <row r="156" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A156" s="107"/>
+      <c r="B156" s="108"/>
+      <c r="C156" s="108"/>
+      <c r="D156" s="108"/>
+      <c r="E156" s="108"/>
+      <c r="F156" s="108"/>
+      <c r="G156" s="108"/>
+      <c r="H156" s="108"/>
+      <c r="I156" s="108"/>
+      <c r="J156" s="108"/>
+      <c r="K156" s="108"/>
+      <c r="L156" s="108"/>
+      <c r="M156" s="108"/>
+      <c r="N156" s="108"/>
+    </row>
+    <row r="157" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A157" s="107"/>
+      <c r="B157" s="108"/>
+      <c r="C157" s="112"/>
+      <c r="D157" s="112"/>
+      <c r="E157" s="112"/>
+      <c r="F157" s="112"/>
+      <c r="G157" s="112"/>
+      <c r="H157" s="112"/>
+      <c r="I157" s="112"/>
+      <c r="J157" s="112"/>
+      <c r="K157" s="112"/>
+      <c r="L157" s="112"/>
+      <c r="M157" s="112"/>
+      <c r="N157" s="112"/>
+    </row>
+    <row r="158" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A158" s="107"/>
+      <c r="B158" s="108"/>
+      <c r="C158" s="108"/>
+      <c r="D158" s="108"/>
+      <c r="E158" s="108"/>
+      <c r="F158" s="108"/>
+      <c r="G158" s="108"/>
+      <c r="H158" s="108"/>
+      <c r="I158" s="108"/>
+      <c r="J158" s="108"/>
+      <c r="K158" s="108"/>
+      <c r="L158" s="108"/>
+      <c r="M158" s="108"/>
+      <c r="N158" s="108"/>
+    </row>
+    <row r="159" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="107"/>
+      <c r="B159" s="108"/>
+      <c r="C159" s="112"/>
+      <c r="D159" s="112"/>
+      <c r="E159" s="112"/>
+      <c r="F159" s="112"/>
+      <c r="G159" s="112"/>
+      <c r="H159" s="112"/>
+      <c r="I159" s="112"/>
+      <c r="J159" s="112"/>
+      <c r="K159" s="112"/>
+      <c r="L159" s="112"/>
+      <c r="M159" s="112"/>
+      <c r="N159" s="112"/>
+    </row>
+    <row r="160" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="107"/>
+      <c r="B160" s="108"/>
+      <c r="C160" s="108"/>
+      <c r="D160" s="108"/>
+      <c r="E160" s="108"/>
+      <c r="F160" s="108"/>
+      <c r="G160" s="108"/>
+      <c r="H160" s="108"/>
+      <c r="I160" s="108"/>
+      <c r="J160" s="108"/>
+      <c r="K160" s="108"/>
+      <c r="L160" s="108"/>
+      <c r="M160" s="108"/>
+      <c r="N160" s="108"/>
+    </row>
+    <row r="161" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A161" s="107"/>
+      <c r="B161" s="108"/>
+      <c r="C161" s="108"/>
+      <c r="D161" s="108"/>
+      <c r="E161" s="108"/>
+      <c r="F161" s="108"/>
+      <c r="G161" s="108"/>
+      <c r="H161" s="108"/>
+      <c r="I161" s="108"/>
+      <c r="J161" s="108"/>
+      <c r="K161" s="108"/>
+      <c r="L161" s="108"/>
+      <c r="M161" s="108"/>
+      <c r="N161" s="108"/>
+    </row>
+    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A162" s="107"/>
+      <c r="B162" s="107"/>
+      <c r="C162" s="109" t="s">
         <v>497</v>
       </c>
-      <c r="D162" s="116" t="s">
+      <c r="D162" s="109" t="s">
         <v>498</v>
       </c>
-      <c r="E162" s="116" t="s">
+      <c r="E162" s="109" t="s">
         <v>499</v>
       </c>
-      <c r="F162" s="116" t="s">
+      <c r="F162" s="109" t="s">
         <v>500</v>
       </c>
-      <c r="G162" s="116" t="s">
+      <c r="G162" s="109" t="s">
         <v>501</v>
       </c>
-      <c r="H162" s="116" t="s">
+      <c r="H162" s="109" t="s">
         <v>502</v>
       </c>
-      <c r="I162" s="116" t="s">
+      <c r="I162" s="109" t="s">
         <v>503</v>
       </c>
-      <c r="J162" s="116" t="s">
+      <c r="J162" s="109" t="s">
         <v>504</v>
       </c>
-      <c r="K162" s="116" t="s">
+      <c r="K162" s="109" t="s">
         <v>505</v>
       </c>
-      <c r="L162" s="116" t="s">
+      <c r="L162" s="109" t="s">
         <v>506</v>
       </c>
-      <c r="M162" s="116" t="s">
+      <c r="M162" s="109" t="s">
         <v>507</v>
       </c>
-      <c r="N162" s="116" t="s">
+      <c r="N162" s="109" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A163" s="112"/>
-      <c r="B163" s="112"/>
-      <c r="C163" s="117">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A163" s="107"/>
+      <c r="B163" s="107"/>
+      <c r="C163" s="110">
         <v>2093</v>
       </c>
-      <c r="D163" s="117">
+      <c r="D163" s="110">
         <v>2217</v>
       </c>
-      <c r="E163" s="117">
+      <c r="E163" s="110">
         <v>2349</v>
       </c>
-      <c r="F163" s="117">
+      <c r="F163" s="110">
         <v>2489</v>
       </c>
-      <c r="G163" s="117">
+      <c r="G163" s="110">
         <v>2637</v>
       </c>
-      <c r="H163" s="117">
+      <c r="H163" s="110">
         <v>2794</v>
       </c>
-      <c r="I163" s="117">
+      <c r="I163" s="110">
         <v>2960</v>
       </c>
-      <c r="J163" s="117">
+      <c r="J163" s="110">
         <v>3136</v>
       </c>
-      <c r="K163" s="117">
+      <c r="K163" s="110">
         <v>3322</v>
       </c>
-      <c r="L163" s="117">
+      <c r="L163" s="110">
         <v>3520</v>
       </c>
-      <c r="M163" s="117">
+      <c r="M163" s="110">
         <v>3729</v>
       </c>
-      <c r="N163" s="117">
+      <c r="N163" s="110">
         <v>3951</v>
       </c>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A164" s="112"/>
-      <c r="B164" s="112"/>
-      <c r="C164" s="112"/>
-      <c r="D164" s="112"/>
-      <c r="E164" s="112"/>
-      <c r="F164" s="112"/>
-      <c r="G164" s="112"/>
-      <c r="H164" s="112"/>
-      <c r="I164" s="112"/>
-      <c r="J164" s="112"/>
-      <c r="K164" s="112"/>
-      <c r="L164" s="112"/>
-      <c r="M164" s="112"/>
-      <c r="N164" s="112"/>
-    </row>
-    <row r="165" spans="1:14" ht="16.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A165" s="112"/>
-      <c r="B165" s="114" t="s">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A164" s="107"/>
+      <c r="B164" s="107"/>
+      <c r="C164" s="107"/>
+      <c r="D164" s="107"/>
+      <c r="E164" s="107"/>
+      <c r="F164" s="107"/>
+      <c r="G164" s="107"/>
+      <c r="H164" s="107"/>
+      <c r="I164" s="107"/>
+      <c r="J164" s="107"/>
+      <c r="K164" s="107"/>
+      <c r="L164" s="107"/>
+      <c r="M164" s="107"/>
+      <c r="N164" s="107"/>
+    </row>
+    <row r="165" spans="1:14" ht="16.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A165" s="107"/>
+      <c r="B165" s="119" t="s">
         <v>509</v>
       </c>
-      <c r="C165" s="114"/>
-      <c r="D165" s="114"/>
-      <c r="E165" s="114"/>
-      <c r="F165" s="114"/>
-      <c r="G165" s="114"/>
-      <c r="H165" s="114"/>
-      <c r="I165" s="114"/>
-      <c r="J165" s="114"/>
-      <c r="K165" s="114"/>
-      <c r="L165" s="114"/>
-      <c r="M165" s="114"/>
-      <c r="N165" s="114"/>
-    </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A166" s="112"/>
-      <c r="B166" s="112"/>
-      <c r="C166" s="112"/>
-      <c r="D166" s="112"/>
-      <c r="E166" s="112"/>
-      <c r="F166" s="112"/>
-      <c r="G166" s="112"/>
-      <c r="H166" s="112"/>
-      <c r="I166" s="112"/>
-      <c r="J166" s="112"/>
-      <c r="K166" s="112"/>
-      <c r="L166" s="112"/>
-      <c r="M166" s="112"/>
-      <c r="N166" s="112"/>
-    </row>
-    <row r="167" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A167" s="112"/>
-      <c r="B167" s="115"/>
-      <c r="C167" s="115"/>
-      <c r="D167" s="115"/>
-      <c r="E167" s="115"/>
-      <c r="F167" s="115"/>
-      <c r="G167" s="115"/>
-      <c r="H167" s="115"/>
-      <c r="I167" s="115"/>
-      <c r="J167" s="115"/>
-      <c r="K167" s="115"/>
-      <c r="L167" s="115"/>
-      <c r="M167" s="115"/>
-      <c r="N167" s="115"/>
-    </row>
-    <row r="168" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A168" s="112"/>
-      <c r="B168" s="115"/>
-      <c r="C168" s="115"/>
-      <c r="D168" s="115"/>
-      <c r="E168" s="115"/>
-      <c r="F168" s="115"/>
-      <c r="G168" s="115"/>
-      <c r="H168" s="115"/>
-      <c r="I168" s="115"/>
-      <c r="J168" s="115"/>
-      <c r="K168" s="115"/>
-      <c r="L168" s="115"/>
-      <c r="M168" s="115"/>
-      <c r="N168" s="115"/>
-    </row>
-    <row r="169" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A169" s="112"/>
-      <c r="B169" s="115"/>
-      <c r="C169" s="115"/>
-      <c r="D169" s="115"/>
-      <c r="E169" s="115"/>
-      <c r="F169" s="115"/>
-      <c r="G169" s="115"/>
-      <c r="H169" s="115"/>
-      <c r="I169" s="115"/>
-      <c r="J169" s="115"/>
-      <c r="K169" s="115"/>
-      <c r="L169" s="115"/>
-      <c r="M169" s="115"/>
-      <c r="N169" s="115"/>
-    </row>
-    <row r="170" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A170" s="112"/>
-      <c r="B170" s="115"/>
-      <c r="C170" s="115"/>
-      <c r="D170" s="115"/>
-      <c r="E170" s="115"/>
-      <c r="F170" s="115"/>
-      <c r="G170" s="115"/>
-      <c r="H170" s="115"/>
-      <c r="I170" s="115"/>
-      <c r="J170" s="115"/>
-      <c r="K170" s="115"/>
-      <c r="L170" s="115"/>
-      <c r="M170" s="115"/>
-      <c r="N170" s="115"/>
-    </row>
-    <row r="171" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A171" s="112"/>
-      <c r="B171" s="115"/>
-      <c r="C171" s="120"/>
-      <c r="D171" s="120"/>
-      <c r="E171" s="120"/>
-      <c r="F171" s="120"/>
-      <c r="G171" s="120"/>
-      <c r="H171" s="120"/>
-      <c r="I171" s="120"/>
-      <c r="J171" s="120"/>
-      <c r="K171" s="120"/>
-      <c r="L171" s="120"/>
-      <c r="M171" s="120"/>
-      <c r="N171" s="120"/>
-    </row>
-    <row r="172" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A172" s="112"/>
-      <c r="B172" s="115"/>
-      <c r="C172" s="115"/>
-      <c r="D172" s="115"/>
-      <c r="E172" s="115"/>
-      <c r="F172" s="115"/>
-      <c r="G172" s="115"/>
-      <c r="H172" s="115"/>
-      <c r="I172" s="115"/>
-      <c r="J172" s="115"/>
-      <c r="K172" s="115"/>
-      <c r="L172" s="115"/>
-      <c r="M172" s="115"/>
-      <c r="N172" s="115"/>
-    </row>
-    <row r="173" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A173" s="112"/>
-      <c r="B173" s="115"/>
-      <c r="C173" s="120"/>
-      <c r="D173" s="120"/>
-      <c r="E173" s="120" t="s">
+      <c r="C165" s="119"/>
+      <c r="D165" s="119"/>
+      <c r="E165" s="119"/>
+      <c r="F165" s="119"/>
+      <c r="G165" s="119"/>
+      <c r="H165" s="119"/>
+      <c r="I165" s="119"/>
+      <c r="J165" s="119"/>
+      <c r="K165" s="119"/>
+      <c r="L165" s="119"/>
+      <c r="M165" s="119"/>
+      <c r="N165" s="119"/>
+    </row>
+    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A166" s="107"/>
+      <c r="B166" s="107"/>
+      <c r="C166" s="107"/>
+      <c r="D166" s="107"/>
+      <c r="E166" s="107"/>
+      <c r="F166" s="107"/>
+      <c r="G166" s="107"/>
+      <c r="H166" s="107"/>
+      <c r="I166" s="107"/>
+      <c r="J166" s="107"/>
+      <c r="K166" s="107"/>
+      <c r="L166" s="107"/>
+      <c r="M166" s="107"/>
+      <c r="N166" s="107"/>
+    </row>
+    <row r="167" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A167" s="107"/>
+      <c r="B167" s="108"/>
+      <c r="C167" s="108"/>
+      <c r="D167" s="108"/>
+      <c r="E167" s="108"/>
+      <c r="F167" s="108"/>
+      <c r="G167" s="108"/>
+      <c r="H167" s="108"/>
+      <c r="I167" s="108"/>
+      <c r="J167" s="108"/>
+      <c r="K167" s="108"/>
+      <c r="L167" s="108"/>
+      <c r="M167" s="108"/>
+      <c r="N167" s="108"/>
+    </row>
+    <row r="168" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A168" s="107"/>
+      <c r="B168" s="108"/>
+      <c r="C168" s="108"/>
+      <c r="D168" s="108"/>
+      <c r="E168" s="108"/>
+      <c r="F168" s="108"/>
+      <c r="G168" s="108"/>
+      <c r="H168" s="108"/>
+      <c r="I168" s="108"/>
+      <c r="J168" s="108"/>
+      <c r="K168" s="108"/>
+      <c r="L168" s="108"/>
+      <c r="M168" s="108"/>
+      <c r="N168" s="108"/>
+    </row>
+    <row r="169" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A169" s="107"/>
+      <c r="B169" s="108"/>
+      <c r="C169" s="108"/>
+      <c r="D169" s="108"/>
+      <c r="E169" s="108"/>
+      <c r="F169" s="108"/>
+      <c r="G169" s="108"/>
+      <c r="H169" s="108"/>
+      <c r="I169" s="108"/>
+      <c r="J169" s="108"/>
+      <c r="K169" s="108"/>
+      <c r="L169" s="108"/>
+      <c r="M169" s="108"/>
+      <c r="N169" s="108"/>
+    </row>
+    <row r="170" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A170" s="107"/>
+      <c r="B170" s="108"/>
+      <c r="C170" s="108"/>
+      <c r="D170" s="108"/>
+      <c r="E170" s="108"/>
+      <c r="F170" s="108"/>
+      <c r="G170" s="108"/>
+      <c r="H170" s="108"/>
+      <c r="I170" s="108"/>
+      <c r="J170" s="108"/>
+      <c r="K170" s="108"/>
+      <c r="L170" s="108"/>
+      <c r="M170" s="108"/>
+      <c r="N170" s="108"/>
+    </row>
+    <row r="171" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A171" s="107"/>
+      <c r="B171" s="108"/>
+      <c r="C171" s="112"/>
+      <c r="D171" s="112"/>
+      <c r="E171" s="112"/>
+      <c r="F171" s="112"/>
+      <c r="G171" s="112"/>
+      <c r="H171" s="112"/>
+      <c r="I171" s="112"/>
+      <c r="J171" s="112"/>
+      <c r="K171" s="112"/>
+      <c r="L171" s="112"/>
+      <c r="M171" s="112"/>
+      <c r="N171" s="112"/>
+    </row>
+    <row r="172" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A172" s="107"/>
+      <c r="B172" s="108"/>
+      <c r="C172" s="108"/>
+      <c r="D172" s="108"/>
+      <c r="E172" s="108"/>
+      <c r="F172" s="108"/>
+      <c r="G172" s="108"/>
+      <c r="H172" s="108"/>
+      <c r="I172" s="108"/>
+      <c r="J172" s="108"/>
+      <c r="K172" s="108"/>
+      <c r="L172" s="108"/>
+      <c r="M172" s="108"/>
+      <c r="N172" s="108"/>
+    </row>
+    <row r="173" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A173" s="107"/>
+      <c r="B173" s="108"/>
+      <c r="C173" s="112"/>
+      <c r="D173" s="112"/>
+      <c r="E173" s="112" t="s">
         <v>411</v>
       </c>
-      <c r="F173" s="120" t="s">
+      <c r="F173" s="112" t="s">
         <v>414</v>
       </c>
-      <c r="G173" s="120"/>
-      <c r="H173" s="120"/>
-      <c r="I173" s="120"/>
-      <c r="J173" s="120"/>
-      <c r="K173" s="120"/>
-      <c r="L173" s="120"/>
-      <c r="M173" s="120"/>
-      <c r="N173" s="120"/>
-    </row>
-    <row r="174" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A174" s="112"/>
-      <c r="B174" s="115" t="s">
+      <c r="G173" s="112"/>
+      <c r="H173" s="112"/>
+      <c r="I173" s="112"/>
+      <c r="J173" s="112"/>
+      <c r="K173" s="112"/>
+      <c r="L173" s="112"/>
+      <c r="M173" s="112"/>
+      <c r="N173" s="112"/>
+    </row>
+    <row r="174" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A174" s="107"/>
+      <c r="B174" s="108" t="s">
         <v>510</v>
       </c>
-      <c r="C174" s="115" t="s">
+      <c r="C174" s="108" t="s">
         <v>411</v>
       </c>
-      <c r="D174" s="115" t="s">
+      <c r="D174" s="108" t="s">
         <v>414</v>
       </c>
-      <c r="E174" s="115"/>
-      <c r="F174" s="115"/>
-      <c r="G174" s="115"/>
-      <c r="H174" s="115"/>
-      <c r="I174" s="115"/>
-      <c r="J174" s="115"/>
-      <c r="K174" s="115"/>
-      <c r="L174" s="115"/>
-      <c r="M174" s="115"/>
-      <c r="N174" s="115"/>
-    </row>
-    <row r="175" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A175" s="112"/>
-      <c r="B175" s="115"/>
-      <c r="C175" s="120"/>
-      <c r="D175" s="120"/>
-      <c r="E175" s="120"/>
-      <c r="F175" s="120"/>
-      <c r="G175" s="120"/>
-      <c r="H175" s="120"/>
-      <c r="I175" s="120"/>
-      <c r="J175" s="120"/>
-      <c r="K175" s="120"/>
-      <c r="L175" s="120"/>
-      <c r="M175" s="120"/>
-      <c r="N175" s="120"/>
-    </row>
-    <row r="176" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A176" s="112"/>
-      <c r="B176" s="115"/>
-      <c r="C176" s="115"/>
-      <c r="D176" s="115"/>
-      <c r="E176" s="115"/>
-      <c r="F176" s="115"/>
-      <c r="G176" s="115"/>
-      <c r="H176" s="115"/>
-      <c r="I176" s="115"/>
-      <c r="J176" s="115"/>
-      <c r="K176" s="115"/>
-      <c r="L176" s="115"/>
-      <c r="M176" s="115"/>
-      <c r="N176" s="115"/>
-    </row>
-    <row r="177" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A177" s="112"/>
-      <c r="B177" s="115"/>
-      <c r="C177" s="120"/>
-      <c r="D177" s="120"/>
-      <c r="E177" s="120"/>
-      <c r="F177" s="120"/>
-      <c r="G177" s="120"/>
-      <c r="H177" s="120"/>
-      <c r="I177" s="120"/>
-      <c r="J177" s="120"/>
-      <c r="K177" s="120"/>
-      <c r="L177" s="120"/>
-      <c r="M177" s="120"/>
-      <c r="N177" s="120"/>
-    </row>
-    <row r="178" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A178" s="112"/>
-      <c r="B178" s="115"/>
-      <c r="C178" s="115"/>
-      <c r="D178" s="115"/>
-      <c r="E178" s="115"/>
-      <c r="F178" s="115"/>
-      <c r="G178" s="115"/>
-      <c r="H178" s="115"/>
-      <c r="I178" s="115"/>
-      <c r="J178" s="115"/>
-      <c r="K178" s="115"/>
-      <c r="L178" s="115"/>
-      <c r="M178" s="115"/>
-      <c r="N178" s="115"/>
-    </row>
-    <row r="179" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A179" s="112"/>
-      <c r="B179" s="115"/>
-      <c r="C179" s="120"/>
-      <c r="D179" s="120"/>
-      <c r="E179" s="120"/>
-      <c r="F179" s="120"/>
-      <c r="G179" s="120"/>
-      <c r="H179" s="120"/>
-      <c r="I179" s="120"/>
-      <c r="J179" s="120"/>
-      <c r="K179" s="120"/>
-      <c r="L179" s="120"/>
-      <c r="M179" s="120"/>
-      <c r="N179" s="120"/>
-    </row>
-    <row r="180" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A180" s="112"/>
-      <c r="B180" s="115"/>
-      <c r="C180" s="115"/>
-      <c r="D180" s="115"/>
-      <c r="E180" s="115"/>
-      <c r="F180" s="115"/>
-      <c r="G180" s="115"/>
-      <c r="H180" s="115"/>
-      <c r="I180" s="115"/>
-      <c r="J180" s="115"/>
-      <c r="K180" s="115"/>
-      <c r="L180" s="115"/>
-      <c r="M180" s="115"/>
-      <c r="N180" s="115"/>
-    </row>
-    <row r="181" spans="1:14" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A181" s="112"/>
-      <c r="B181" s="115"/>
-      <c r="C181" s="115"/>
-      <c r="D181" s="115"/>
-      <c r="E181" s="115"/>
-      <c r="F181" s="115"/>
-      <c r="G181" s="115"/>
-      <c r="H181" s="115"/>
-      <c r="I181" s="115"/>
-      <c r="J181" s="115"/>
-      <c r="K181" s="115"/>
-      <c r="L181" s="115"/>
-      <c r="M181" s="115"/>
-      <c r="N181" s="115"/>
-    </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A182" s="112"/>
-      <c r="B182" s="112"/>
-      <c r="C182" s="116" t="s">
+      <c r="E174" s="108"/>
+      <c r="F174" s="108"/>
+      <c r="G174" s="108"/>
+      <c r="H174" s="108"/>
+      <c r="I174" s="108"/>
+      <c r="J174" s="108"/>
+      <c r="K174" s="108"/>
+      <c r="L174" s="108"/>
+      <c r="M174" s="108"/>
+      <c r="N174" s="108"/>
+    </row>
+    <row r="175" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A175" s="107"/>
+      <c r="B175" s="108"/>
+      <c r="C175" s="112"/>
+      <c r="D175" s="112"/>
+      <c r="E175" s="112"/>
+      <c r="F175" s="112"/>
+      <c r="G175" s="112"/>
+      <c r="H175" s="112"/>
+      <c r="I175" s="112"/>
+      <c r="J175" s="112"/>
+      <c r="K175" s="112"/>
+      <c r="L175" s="112"/>
+      <c r="M175" s="112"/>
+      <c r="N175" s="112"/>
+    </row>
+    <row r="176" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A176" s="107"/>
+      <c r="B176" s="108"/>
+      <c r="C176" s="108"/>
+      <c r="D176" s="108"/>
+      <c r="E176" s="108"/>
+      <c r="F176" s="108"/>
+      <c r="G176" s="108"/>
+      <c r="H176" s="108"/>
+      <c r="I176" s="108"/>
+      <c r="J176" s="108"/>
+      <c r="K176" s="108"/>
+      <c r="L176" s="108"/>
+      <c r="M176" s="108"/>
+      <c r="N176" s="108"/>
+    </row>
+    <row r="177" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A177" s="107"/>
+      <c r="B177" s="108"/>
+      <c r="C177" s="112"/>
+      <c r="D177" s="112"/>
+      <c r="E177" s="112"/>
+      <c r="F177" s="112"/>
+      <c r="G177" s="112"/>
+      <c r="H177" s="112"/>
+      <c r="I177" s="112"/>
+      <c r="J177" s="112"/>
+      <c r="K177" s="112"/>
+      <c r="L177" s="112"/>
+      <c r="M177" s="112"/>
+      <c r="N177" s="112"/>
+    </row>
+    <row r="178" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A178" s="107"/>
+      <c r="B178" s="108"/>
+      <c r="C178" s="108"/>
+      <c r="D178" s="108"/>
+      <c r="E178" s="108"/>
+      <c r="F178" s="108"/>
+      <c r="G178" s="108"/>
+      <c r="H178" s="108"/>
+      <c r="I178" s="108"/>
+      <c r="J178" s="108"/>
+      <c r="K178" s="108"/>
+      <c r="L178" s="108"/>
+      <c r="M178" s="108"/>
+      <c r="N178" s="108"/>
+    </row>
+    <row r="179" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A179" s="107"/>
+      <c r="B179" s="108"/>
+      <c r="C179" s="112"/>
+      <c r="D179" s="112"/>
+      <c r="E179" s="112"/>
+      <c r="F179" s="112"/>
+      <c r="G179" s="112"/>
+      <c r="H179" s="112"/>
+      <c r="I179" s="112"/>
+      <c r="J179" s="112"/>
+      <c r="K179" s="112"/>
+      <c r="L179" s="112"/>
+      <c r="M179" s="112"/>
+      <c r="N179" s="112"/>
+    </row>
+    <row r="180" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A180" s="107"/>
+      <c r="B180" s="108"/>
+      <c r="C180" s="108"/>
+      <c r="D180" s="108"/>
+      <c r="E180" s="108"/>
+      <c r="F180" s="108"/>
+      <c r="G180" s="108"/>
+      <c r="H180" s="108"/>
+      <c r="I180" s="108"/>
+      <c r="J180" s="108"/>
+      <c r="K180" s="108"/>
+      <c r="L180" s="108"/>
+      <c r="M180" s="108"/>
+      <c r="N180" s="108"/>
+    </row>
+    <row r="181" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A181" s="107"/>
+      <c r="B181" s="108"/>
+      <c r="C181" s="108"/>
+      <c r="D181" s="108"/>
+      <c r="E181" s="108"/>
+      <c r="F181" s="108"/>
+      <c r="G181" s="108"/>
+      <c r="H181" s="108"/>
+      <c r="I181" s="108"/>
+      <c r="J181" s="108"/>
+      <c r="K181" s="108"/>
+      <c r="L181" s="108"/>
+      <c r="M181" s="108"/>
+      <c r="N181" s="108"/>
+    </row>
+    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A182" s="107"/>
+      <c r="B182" s="107"/>
+      <c r="C182" s="109" t="s">
         <v>511</v>
       </c>
-      <c r="D182" s="116" t="s">
+      <c r="D182" s="109" t="s">
         <v>512</v>
       </c>
-      <c r="E182" s="116" t="s">
+      <c r="E182" s="109" t="s">
         <v>513</v>
       </c>
-      <c r="F182" s="116" t="s">
+      <c r="F182" s="109" t="s">
         <v>514</v>
       </c>
-      <c r="G182" s="116"/>
-      <c r="H182" s="116"/>
-      <c r="I182" s="116"/>
-      <c r="J182" s="116"/>
-      <c r="K182" s="116"/>
-      <c r="L182" s="116"/>
-      <c r="M182" s="116"/>
-      <c r="N182" s="116"/>
-    </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A183" s="112"/>
-      <c r="B183" s="112"/>
-      <c r="C183" s="117">
+      <c r="G182" s="109"/>
+      <c r="H182" s="109"/>
+      <c r="I182" s="109"/>
+      <c r="J182" s="109"/>
+      <c r="K182" s="109"/>
+      <c r="L182" s="109"/>
+      <c r="M182" s="109"/>
+      <c r="N182" s="109"/>
+    </row>
+    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A183" s="107"/>
+      <c r="B183" s="107"/>
+      <c r="C183" s="110">
         <v>4186</v>
       </c>
-      <c r="D183" s="117">
+      <c r="D183" s="110">
         <v>4435</v>
       </c>
-      <c r="E183" s="117">
+      <c r="E183" s="110">
         <v>4699</v>
       </c>
-      <c r="F183" s="117">
+      <c r="F183" s="110">
         <v>4978</v>
       </c>
-      <c r="G183" s="117"/>
-      <c r="H183" s="117"/>
-      <c r="I183" s="117"/>
-      <c r="J183" s="117"/>
-      <c r="K183" s="117"/>
-      <c r="L183" s="117"/>
-      <c r="M183" s="117"/>
-      <c r="N183" s="117"/>
-    </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A184" s="112"/>
-      <c r="B184" s="112"/>
-      <c r="C184" s="112"/>
-      <c r="D184" s="112"/>
-      <c r="E184" s="112"/>
-      <c r="F184" s="112"/>
-      <c r="G184" s="112"/>
-      <c r="H184" s="112"/>
-      <c r="I184" s="112"/>
-      <c r="J184" s="112"/>
-      <c r="K184" s="112"/>
-      <c r="L184" s="112"/>
-      <c r="M184" s="112"/>
-      <c r="N184" s="112"/>
+      <c r="G183" s="110"/>
+      <c r="H183" s="110"/>
+      <c r="I183" s="110"/>
+      <c r="J183" s="110"/>
+      <c r="K183" s="110"/>
+      <c r="L183" s="110"/>
+      <c r="M183" s="110"/>
+      <c r="N183" s="110"/>
+    </row>
+    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A184" s="107"/>
+      <c r="B184" s="107"/>
+      <c r="C184" s="107"/>
+      <c r="D184" s="107"/>
+      <c r="E184" s="107"/>
+      <c r="F184" s="107"/>
+      <c r="G184" s="107"/>
+      <c r="H184" s="107"/>
+      <c r="I184" s="107"/>
+      <c r="J184" s="107"/>
+      <c r="K184" s="107"/>
+      <c r="L184" s="107"/>
+      <c r="M184" s="107"/>
+      <c r="N184" s="107"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B65:N65"/>
-    <mergeCell ref="B85:N85"/>
-    <mergeCell ref="B105:N105"/>
-    <mergeCell ref="B125:N125"/>
-    <mergeCell ref="B145:N145"/>
     <mergeCell ref="B165:N165"/>
     <mergeCell ref="B1:N1"/>
     <mergeCell ref="B2:N2"/>
@@ -10208,7 +10269,87 @@
     <mergeCell ref="B5:N5"/>
     <mergeCell ref="B25:N25"/>
     <mergeCell ref="B45:N45"/>
+    <mergeCell ref="B65:N65"/>
+    <mergeCell ref="B85:N85"/>
+    <mergeCell ref="B105:N105"/>
+    <mergeCell ref="B125:N125"/>
+    <mergeCell ref="B145:N145"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A28E216A-01CA-45B4-84A5-D6774A84A3B1}">
+  <sheetPr>
+    <tabColor rgb="FF7030A0"/>
+  </sheetPr>
+  <dimension ref="N10:O73"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="13" width="8.6328125" customWidth="1"/>
+    <col min="14" max="14" width="21.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="75.36328125" style="1" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="10" spans="14:15" x14ac:dyDescent="0.4">
+      <c r="N10" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="O10" s="117" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="20" spans="14:15" x14ac:dyDescent="0.4">
+      <c r="N20" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="O20" s="118" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="30" spans="14:15" x14ac:dyDescent="0.4">
+      <c r="N30" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="O30" s="118" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="41" spans="14:15" x14ac:dyDescent="0.4">
+      <c r="N41" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="O41" s="118" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="57" spans="14:15" x14ac:dyDescent="0.4">
+      <c r="N57" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="O57" s="117" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="73" spans="14:15" x14ac:dyDescent="0.4">
+      <c r="N73" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="O73" s="118" t="s">
+        <v>519</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="O41" r:id="rId1" xr:uid="{7B81E68B-75A0-4D55-8A69-D5E50AF6AFE4}"/>
+    <hyperlink ref="O73" r:id="rId2" xr:uid="{6E1D29C1-43C0-4A5D-A547-5F99BB725019}"/>
+    <hyperlink ref="O57" r:id="rId3" xr:uid="{4B3AC0C3-133F-49A2-8FB6-B6966CFFBAC3}"/>
+    <hyperlink ref="O10" r:id="rId4" xr:uid="{12478B99-6BE7-478E-9015-FCB587862DF7}"/>
+    <hyperlink ref="O20" r:id="rId5" xr:uid="{F1073DDB-9558-4649-9940-FEBD1E286546}"/>
+    <hyperlink ref="O30" r:id="rId6" xr:uid="{8FBE1531-DAEF-4D7E-B3C2-B17532A3C5D9}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId7"/>
+</worksheet>
 </file>